--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -5,13 +5,14 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Invalid Date" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="2021-02-16" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="483">
   <si>
     <t>标题</t>
   </si>
@@ -1397,6 +1398,69 @@
   </si>
   <si>
     <t>https://reactjs.org/blog/2013/06/02/jsfiddle-integration.html</t>
+  </si>
+  <si>
+    <t>Improving DevTools startup time</t>
+  </si>
+  <si>
+    <t>Chrome</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Migrating Puppeteer to TypeScript</t>
+  </si>
+  <si>
+    <t>2021-01-21</t>
+  </si>
+  <si>
+    <t>What's New In DevTools (Chrome 89)</t>
+  </si>
+  <si>
+    <t>2021-01-19</t>
+  </si>
+  <si>
+    <t>Debugging WebAssembly with modern tools</t>
+  </si>
+  <si>
+    <t>2020-12-10</t>
+  </si>
+  <si>
+    <t>DevTools architecture refresh: migrating to Web Components</t>
+  </si>
+  <si>
+    <t>2020-12-08</t>
+  </si>
+  <si>
+    <t>Deprecations and removals in Chrome 88</t>
+  </si>
+  <si>
+    <t>2020-12-04</t>
+  </si>
+  <si>
+    <t>Simulating color vision deficiencies in the Blink Renderer</t>
+  </si>
+  <si>
+    <t>What's New In DevTools (Chrome 88)</t>
+  </si>
+  <si>
+    <t>2020-11-12</t>
+  </si>
+  <si>
+    <t>Puppetaria: accessibility-first Puppeteer scripts</t>
+  </si>
+  <si>
+    <t>2020-11-10</t>
+  </si>
+  <si>
+    <t>How we built the Chrome DevTools WebAuthn tab</t>
+  </si>
+  <si>
+    <t>2020-10-22</t>
   </si>
 </sst>
 </file>
@@ -3929,6 +3993,180 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>466</v>
+      </c>
+      <c r="B3" t="s">
+        <v>463</v>
+      </c>
+      <c r="C3" t="s">
+        <v>467</v>
+      </c>
+      <c r="E3" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>468</v>
+      </c>
+      <c r="B4" t="s">
+        <v>463</v>
+      </c>
+      <c r="C4" t="s">
+        <v>469</v>
+      </c>
+      <c r="E4" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>470</v>
+      </c>
+      <c r="B5" t="s">
+        <v>463</v>
+      </c>
+      <c r="C5" t="s">
+        <v>471</v>
+      </c>
+      <c r="E5" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>472</v>
+      </c>
+      <c r="B6" t="s">
+        <v>463</v>
+      </c>
+      <c r="C6" t="s">
+        <v>473</v>
+      </c>
+      <c r="E6" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>474</v>
+      </c>
+      <c r="B7" t="s">
+        <v>463</v>
+      </c>
+      <c r="C7" t="s">
+        <v>475</v>
+      </c>
+      <c r="E7" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>476</v>
+      </c>
+      <c r="B8" t="s">
+        <v>463</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>477</v>
+      </c>
+      <c r="B9" t="s">
+        <v>463</v>
+      </c>
+      <c r="C9" t="s">
+        <v>478</v>
+      </c>
+      <c r="E9" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>479</v>
+      </c>
+      <c r="B10" t="s">
+        <v>463</v>
+      </c>
+      <c r="C10" t="s">
+        <v>480</v>
+      </c>
+      <c r="E10" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>481</v>
+      </c>
+      <c r="B11" t="s">
+        <v>463</v>
+      </c>
+      <c r="C11" t="s">
+        <v>482</v>
+      </c>
+      <c r="E11" t="s">
+        <v>465</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="492">
   <si>
     <t>标题</t>
   </si>
@@ -1409,7 +1409,7 @@
     <t>2021-02-04</t>
   </si>
   <si>
-    <t/>
+    <t>https://developers.google.com/web/updates/2021/02/faster-devtools-startup?utm_source=feed&amp;utm_medium=feed&amp;utm_campaign=updates_feed</t>
   </si>
   <si>
     <t>Migrating Puppeteer to TypeScript</t>
@@ -1418,49 +1418,76 @@
     <t>2021-01-21</t>
   </si>
   <si>
+    <t>https://developers.google.com/web/updates/2021/01/puppeteer-typescript?utm_source=feed&amp;utm_medium=feed&amp;utm_campaign=updates_feed</t>
+  </si>
+  <si>
     <t>What's New In DevTools (Chrome 89)</t>
   </si>
   <si>
     <t>2021-01-19</t>
   </si>
   <si>
+    <t>https://developers.google.com/web/updates/2021/01/devtools?utm_source=feed&amp;utm_medium=feed&amp;utm_campaign=updates_feed</t>
+  </si>
+  <si>
     <t>Debugging WebAssembly with modern tools</t>
   </si>
   <si>
     <t>2020-12-10</t>
   </si>
   <si>
+    <t>https://developers.google.com/web/updates/2020/12/webassembly?utm_source=feed&amp;utm_medium=feed&amp;utm_campaign=updates_feed</t>
+  </si>
+  <si>
     <t>DevTools architecture refresh: migrating to Web Components</t>
   </si>
   <si>
     <t>2020-12-08</t>
   </si>
   <si>
+    <t>https://developers.google.com/web/updates/2020/12/migrating-to-web-components?utm_source=feed&amp;utm_medium=feed&amp;utm_campaign=updates_feed</t>
+  </si>
+  <si>
     <t>Deprecations and removals in Chrome 88</t>
   </si>
   <si>
     <t>2020-12-04</t>
   </si>
   <si>
+    <t>https://developers.google.com/web/updates/2020/12/chrome-88-deps-rems?utm_source=feed&amp;utm_medium=feed&amp;utm_campaign=updates_feed</t>
+  </si>
+  <si>
     <t>Simulating color vision deficiencies in the Blink Renderer</t>
   </si>
   <si>
+    <t>https://developers.google.com/web/updates/2020/11/cvd?utm_source=feed&amp;utm_medium=feed&amp;utm_campaign=updates_feed</t>
+  </si>
+  <si>
     <t>What's New In DevTools (Chrome 88)</t>
   </si>
   <si>
     <t>2020-11-12</t>
   </si>
   <si>
+    <t>https://developers.google.com/web/updates/2020/11/devtools?utm_source=feed&amp;utm_medium=feed&amp;utm_campaign=updates_feed</t>
+  </si>
+  <si>
     <t>Puppetaria: accessibility-first Puppeteer scripts</t>
   </si>
   <si>
     <t>2020-11-10</t>
   </si>
   <si>
+    <t>https://developers.google.com/web/updates/2020/11/puppetaria?utm_source=feed&amp;utm_medium=feed&amp;utm_campaign=updates_feed</t>
+  </si>
+  <si>
     <t>How we built the Chrome DevTools WebAuthn tab</t>
   </si>
   <si>
     <t>2020-10-22</t>
+  </si>
+  <si>
+    <t>https://developers.google.com/web/updates/2020/10/webauthn-tab?utm_source=feed&amp;utm_medium=feed&amp;utm_campaign=updates_feed</t>
   </si>
 </sst>
 </file>
@@ -4050,68 +4077,68 @@
         <v>467</v>
       </c>
       <c r="E3" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B4" t="s">
         <v>463</v>
       </c>
       <c r="C4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E4" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B5" t="s">
         <v>463</v>
       </c>
       <c r="C5" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E5" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B6" t="s">
         <v>463</v>
       </c>
       <c r="C6" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E6" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B7" t="s">
         <v>463</v>
       </c>
       <c r="C7" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="E7" t="s">
-        <v>465</v>
+        <v>480</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="B8" t="s">
         <v>463</v>
@@ -4120,49 +4147,49 @@
         <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>465</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="B9" t="s">
         <v>463</v>
       </c>
       <c r="C9" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="E9" t="s">
-        <v>465</v>
+        <v>485</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="B10" t="s">
         <v>463</v>
       </c>
       <c r="C10" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="E10" t="s">
-        <v>465</v>
+        <v>488</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="B11" t="s">
         <v>463</v>
       </c>
       <c r="C11" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="E11" t="s">
-        <v>465</v>
+        <v>491</v>
       </c>
     </row>
   </sheetData>

--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -4,17 +4,19 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="-3" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="-1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="2021-02-22-chinese" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="2021-02-23-english" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="2021-02-23-chinese" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="973">
   <si>
     <t>标题</t>
   </si>
@@ -59,6 +61,2880 @@
   </si>
   <si>
     <t>https://www.infoq.cn/article/kBFYqqwjRXkhgEYk1abx</t>
+  </si>
+  <si>
+    <t>Announcing TypeScript 4.2 RC</t>
+  </si>
+  <si>
+    <t>Typescript</t>
+  </si>
+  <si>
+    <t>2021-02-11</t>
+  </si>
+  <si>
+    <t>https://devblogs.microsoft.com/typescript/announcing-typescript-4-2-rc/</t>
+  </si>
+  <si>
+    <t>Announcing TypeScript 4.2 Beta</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>https://devblogs.microsoft.com/typescript/announcing-typescript-4-2-beta/</t>
+  </si>
+  <si>
+    <t>Announcing TypeScript 4.1</t>
+  </si>
+  <si>
+    <t>2020-11-19</t>
+  </si>
+  <si>
+    <t>https://devblogs.microsoft.com/typescript/announcing-typescript-4-1/</t>
+  </si>
+  <si>
+    <t>Announcing TypeScript 4.1 RC</t>
+  </si>
+  <si>
+    <t>2020-11-03</t>
+  </si>
+  <si>
+    <t>https://devblogs.microsoft.com/typescript/announcing-typescript-4-1-rc/</t>
+  </si>
+  <si>
+    <t>Announcing TypeScript 4.1 Beta</t>
+  </si>
+  <si>
+    <t>2020-09-18</t>
+  </si>
+  <si>
+    <t>https://devblogs.microsoft.com/typescript/announcing-typescript-4-1-beta/</t>
+  </si>
+  <si>
+    <t>Announcing TypeScript 4.0</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>https://devblogs.microsoft.com/typescript/announcing-typescript-4-0/</t>
+  </si>
+  <si>
+    <t>Announcing TypeScript 4.0 RC</t>
+  </si>
+  <si>
+    <t>2020-08-06</t>
+  </si>
+  <si>
+    <t>https://devblogs.microsoft.com/typescript/announcing-typescript-4-0-rc/</t>
+  </si>
+  <si>
+    <t>Announcing the new TypeScript Website</t>
+  </si>
+  <si>
+    <t>2020-08-04</t>
+  </si>
+  <si>
+    <t>https://devblogs.microsoft.com/typescript/announcing-the-new-typescript-website/</t>
+  </si>
+  <si>
+    <t>Announcing TypeScript 4.0 Beta</t>
+  </si>
+  <si>
+    <t>2020-06-26</t>
+  </si>
+  <si>
+    <t>https://devblogs.microsoft.com/typescript/announcing-typescript-4-0-beta/</t>
+  </si>
+  <si>
+    <t>Changes to How We Manage DefinitelyTyped</t>
+  </si>
+  <si>
+    <t>2020-05-29</t>
+  </si>
+  <si>
+    <t>https://devblogs.microsoft.com/typescript/changes-to-how-we-manage-definitelytyped/</t>
+  </si>
+  <si>
+    <t>Introducing Zero-Bundle-Size React Server Components</t>
+  </si>
+  <si>
+    <t>React</t>
+  </si>
+  <si>
+    <t>2020-12-21</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2020/12/21/data-fetching-with-react-server-components.html</t>
+  </si>
+  <si>
+    <t>React v17.0</t>
+  </si>
+  <si>
+    <t>2020-10-20</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2020/10/20/react-v17.html</t>
+  </si>
+  <si>
+    <t>Introducing the New JSX Transform</t>
+  </si>
+  <si>
+    <t>2020-09-22</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2020/09/22/introducing-the-new-jsx-transform.html</t>
+  </si>
+  <si>
+    <t>React v17.0 Release Candidate: No New Features</t>
+  </si>
+  <si>
+    <t>2020-08-10</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2020/08/10/react-v17-rc.html</t>
+  </si>
+  <si>
+    <t>React v16.13.0</t>
+  </si>
+  <si>
+    <t>2020-02-26</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2020/02/26/react-v16.13.0.html</t>
+  </si>
+  <si>
+    <t>Building Great User Experiences with Concurrent Mode and Suspense</t>
+  </si>
+  <si>
+    <t>2019-11-06</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2019/11/06/building-great-user-experiences-with-concurrent-mode-and-suspense.html</t>
+  </si>
+  <si>
+    <t>Preparing for the Future with React Prereleases</t>
+  </si>
+  <si>
+    <t>2019-10-22</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2019/10/22/react-release-channels.html</t>
+  </si>
+  <si>
+    <t>Introducing the New React DevTools</t>
+  </si>
+  <si>
+    <t>2019-08-15</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2019/08/15/new-react-devtools.html</t>
+  </si>
+  <si>
+    <t>React v16.9.0 and the Roadmap Update</t>
+  </si>
+  <si>
+    <t>2019-08-08</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2019/08/08/react-v16.9.0.html</t>
+  </si>
+  <si>
+    <t>Is React Translated Yet? ¡Sí! Sim! はい！</t>
+  </si>
+  <si>
+    <t>2019-02-23</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2019/02/23/is-react-translated-yet.html</t>
+  </si>
+  <si>
+    <t>React v16.8: The One With Hooks</t>
+  </si>
+  <si>
+    <t>2019-02-06</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2019/02/06/react-v16.8.0.html</t>
+  </si>
+  <si>
+    <t>React v16.7: No, This Is Not the One With Hooks</t>
+  </si>
+  <si>
+    <t>2018-12-19</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2018/12/19/react-v-16-7.html</t>
+  </si>
+  <si>
+    <t>React 16.x Roadmap</t>
+  </si>
+  <si>
+    <t>2018-11-27</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2018/11/27/react-16-roadmap.html</t>
+  </si>
+  <si>
+    <t>React Conf recap: Hooks, Suspense, and Concurrent Rendering</t>
+  </si>
+  <si>
+    <t>2018-11-13</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2018/11/13/react-conf-recap.html</t>
+  </si>
+  <si>
+    <t>React v16.6.0: lazy, memo and contextType</t>
+  </si>
+  <si>
+    <t>2018-10-23</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2018/10/23/react-v-16-6.html</t>
+  </si>
+  <si>
+    <t>Create React App 2.0: Babel 7, Sass, and More</t>
+  </si>
+  <si>
+    <t>2018-10-01</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2018/10/01/create-react-app-v2.html</t>
+  </si>
+  <si>
+    <t>Introducing the React Profiler</t>
+  </si>
+  <si>
+    <t>2018-09-10</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2018/09/10/introducing-the-react-profiler.html</t>
+  </si>
+  <si>
+    <t>React v16.4.2: Server-side vulnerability fix</t>
+  </si>
+  <si>
+    <t>2018-08-01</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2018/08/01/react-v-16-4-2.html</t>
+  </si>
+  <si>
+    <t>You Probably Don't Need Derived State</t>
+  </si>
+  <si>
+    <t>2018-06-07</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2018/06/07/you-probably-dont-need-derived-state.html</t>
+  </si>
+  <si>
+    <t>React v16.4.0: Pointer Events</t>
+  </si>
+  <si>
+    <t>2018-05-23</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2018/05/23/react-v-16-4.html</t>
+  </si>
+  <si>
+    <t>React v16.3.0: New lifecycles and context API</t>
+  </si>
+  <si>
+    <t>2018-03-29</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2018/03/29/react-v-16-3.html</t>
+  </si>
+  <si>
+    <t>Update on Async Rendering</t>
+  </si>
+  <si>
+    <t>2018-03-27</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2018/03/27/update-on-async-rendering.html</t>
+  </si>
+  <si>
+    <t>Sneak Peek: Beyond React 16</t>
+  </si>
+  <si>
+    <t>2018-03-01</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2018/03/01/sneak-peek-beyond-react-16.html</t>
+  </si>
+  <si>
+    <t>Behind the Scenes: Improving the Repository Infrastructure</t>
+  </si>
+  <si>
+    <t>2017-12-15</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2017/12/15/improving-the-repository-infrastructure.html</t>
+  </si>
+  <si>
+    <t>Introducing the React RFC Process</t>
+  </si>
+  <si>
+    <t>2017-12-07</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2017/12/07/introducing-the-react-rfc-process.html</t>
+  </si>
+  <si>
+    <t>React v16.2.0: Improved Support for Fragments</t>
+  </si>
+  <si>
+    <t>2017-11-28</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2017/11/28/react-v16.2.0-fragment-support.html</t>
+  </si>
+  <si>
+    <t>React v16.0</t>
+  </si>
+  <si>
+    <t>2017-09-26</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2017/09/26/react-v16.0.html</t>
+  </si>
+  <si>
+    <t>React v15.6.2</t>
+  </si>
+  <si>
+    <t>2017-09-25</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2017/09/25/react-v15.6.2.html</t>
+  </si>
+  <si>
+    <t>DOM Attributes in React 16</t>
+  </si>
+  <si>
+    <t>2017-09-08</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2017/09/08/dom-attributes-in-react-16.html</t>
+  </si>
+  <si>
+    <t>Error Handling in React 16</t>
+  </si>
+  <si>
+    <t>2017-07-26</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2017/07/26/error-handling-in-react-16.html</t>
+  </si>
+  <si>
+    <t>React v15.6.0</t>
+  </si>
+  <si>
+    <t>2017-06-13</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2017/06/13/react-v15.6.0.html</t>
+  </si>
+  <si>
+    <t>What's New in Create React App</t>
+  </si>
+  <si>
+    <t>2017-05-18</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2017/05/18/whats-new-in-create-react-app.html</t>
+  </si>
+  <si>
+    <t>React v15.5.0</t>
+  </si>
+  <si>
+    <t>2017-04-07</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2017/04/07/react-v15.5.0.html</t>
+  </si>
+  <si>
+    <t>React v15.4.0</t>
+  </si>
+  <si>
+    <t>2016-11-16</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2016/11/16/react-v15.4.0.html</t>
+  </si>
+  <si>
+    <t>Our First 50,000 Stars</t>
+  </si>
+  <si>
+    <t>2016-09-28</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2016/09/28/our-first-50000-stars.html</t>
+  </si>
+  <si>
+    <t>Relay: State of the State</t>
+  </si>
+  <si>
+    <t>2016-08-05</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2016/08/05/relay-state-of-the-state.html</t>
+  </si>
+  <si>
+    <t>Create Apps with No Configuration</t>
+  </si>
+  <si>
+    <t>2016-07-22</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2016/07/22/create-apps-with-no-configuration.html</t>
+  </si>
+  <si>
+    <t>Mixins Considered Harmful</t>
+  </si>
+  <si>
+    <t>2016-07-13</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2016/07/13/mixins-considered-harmful.html</t>
+  </si>
+  <si>
+    <t>Introducing React's Error Code System</t>
+  </si>
+  <si>
+    <t>2016-07-11</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2016/07/11/introducing-reacts-error-code-system.html</t>
+  </si>
+  <si>
+    <t>React v15.0.1</t>
+  </si>
+  <si>
+    <t>2016-04-08</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2016/04/08/react-v15.0.1.html</t>
+  </si>
+  <si>
+    <t>React v15.0</t>
+  </si>
+  <si>
+    <t>2016-04-07</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2016/04/07/react-v15.html</t>
+  </si>
+  <si>
+    <t>React v0.14.8</t>
+  </si>
+  <si>
+    <t>2016-03-29</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2016/03/29/react-v0.14.8.html</t>
+  </si>
+  <si>
+    <t>React v15.0 Release Candidate 2</t>
+  </si>
+  <si>
+    <t>2016-03-16</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2016/03/16/react-v15-rc2.html</t>
+  </si>
+  <si>
+    <t>React v15.0 Release Candidate</t>
+  </si>
+  <si>
+    <t>2016-03-07</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2016/03/07/react-v15-rc1.html</t>
+  </si>
+  <si>
+    <t>New Versioning Scheme</t>
+  </si>
+  <si>
+    <t>2016-02-19</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2016/02/19/new-versioning-scheme.html</t>
+  </si>
+  <si>
+    <t>Discontinuing IE 8 Support in React DOM</t>
+  </si>
+  <si>
+    <t>2016-01-12</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2016/01/12/discontinuing-ie8-support.html</t>
+  </si>
+  <si>
+    <t>(A =&gt; B) !=&gt; (B =&gt; A)</t>
+  </si>
+  <si>
+    <t>2016-01-08</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2016/01/08/A-implies-B-does-not-imply-B-implies-A.html</t>
+  </si>
+  <si>
+    <t>React v0.14.4</t>
+  </si>
+  <si>
+    <t>2015-12-29</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/12/29/react-v0.14.4.html</t>
+  </si>
+  <si>
+    <t>React Components, Elements, and Instances</t>
+  </si>
+  <si>
+    <t>2015-12-18</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/12/18/react-components-elements-and-instances.html</t>
+  </si>
+  <si>
+    <t>isMounted is an Antipattern</t>
+  </si>
+  <si>
+    <t>2015-12-16</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/12/16/ismounted-antipattern.html</t>
+  </si>
+  <si>
+    <t>React.js Conf 2016 Diversity Scholarship</t>
+  </si>
+  <si>
+    <t>2015-12-04</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/12/04/react-js-conf-2016-diversity-scholarship.html</t>
+  </si>
+  <si>
+    <t>React v0.14.3</t>
+  </si>
+  <si>
+    <t>2015-11-18</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/11/18/react-v0.14.3.html</t>
+  </si>
+  <si>
+    <t>React v0.14.2</t>
+  </si>
+  <si>
+    <t>2015-11-02</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/11/02/react-v0.14.2.html</t>
+  </si>
+  <si>
+    <t>React v0.14.1</t>
+  </si>
+  <si>
+    <t>2015-10-28</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/10/28/react-v0.14.1.html</t>
+  </si>
+  <si>
+    <t>Reactiflux is moving to Discord</t>
+  </si>
+  <si>
+    <t>2015-10-19</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/10/19/reactiflux-is-moving-to-discord.html</t>
+  </si>
+  <si>
+    <t>React v0.14</t>
+  </si>
+  <si>
+    <t>2015-10-07</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/10/07/react-v0.14.html</t>
+  </si>
+  <si>
+    <t>ReactDOM.render and the Top Level React API</t>
+  </si>
+  <si>
+    <t>2015-10-01</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/10/01/react-render-and-top-level-api.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #27 – Relay Edition</t>
+  </si>
+  <si>
+    <t>2015-09-14</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/09/14/community-roundup-27.html</t>
+  </si>
+  <si>
+    <t>React v0.14 Release Candidate</t>
+  </si>
+  <si>
+    <t>2015-09-10</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/09/10/react-v0.14-rc1.html</t>
+  </si>
+  <si>
+    <t>New React Developer Tools</t>
+  </si>
+  <si>
+    <t>2015-09-02</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/09/02/new-react-developer-tools.html</t>
+  </si>
+  <si>
+    <t>ReactEurope Round-up</t>
+  </si>
+  <si>
+    <t>2015-08-13</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/08/13/reacteurope-roundup.html</t>
+  </si>
+  <si>
+    <t>Relay Technical Preview</t>
+  </si>
+  <si>
+    <t>2015-08-11</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/08/11/relay-technical-preview.html</t>
+  </si>
+  <si>
+    <t>New React Devtools Beta</t>
+  </si>
+  <si>
+    <t>2015-08-03</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/08/03/new-react-devtools-beta.html</t>
+  </si>
+  <si>
+    <t>React v0.14 Beta 1</t>
+  </si>
+  <si>
+    <t>2015-07-03</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/07/03/react-v0.14-beta-1.html</t>
+  </si>
+  <si>
+    <t>Deprecating JSTransform and react-tools</t>
+  </si>
+  <si>
+    <t>2015-06-12</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/06/12/deprecating-jstransform-and-react-tools.html</t>
+  </si>
+  <si>
+    <t>React Native Release Process</t>
+  </si>
+  <si>
+    <t>2015-05-22</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/05/22/react-native-release-process.html</t>
+  </si>
+  <si>
+    <t>React v0.13.3</t>
+  </si>
+  <si>
+    <t>2015-05-08</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/05/08/react-v0.13.3.html</t>
+  </si>
+  <si>
+    <t>GraphQL Introduction</t>
+  </si>
+  <si>
+    <t>2015-05-01</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/05/01/graphql-introduction.html</t>
+  </si>
+  <si>
+    <t>React v0.13.2</t>
+  </si>
+  <si>
+    <t>2015-04-18</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/04/18/react-v0.13.2.html</t>
+  </si>
+  <si>
+    <t>React Native v0.4</t>
+  </si>
+  <si>
+    <t>2015-04-17</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/04/17/react-native-v0.4.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #26</t>
+  </si>
+  <si>
+    <t>2015-03-30</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/03/30/community-roundup-26.html</t>
+  </si>
+  <si>
+    <t>Introducing React Native</t>
+  </si>
+  <si>
+    <t>2015-03-26</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/03/26/introducing-react-native.html</t>
+  </si>
+  <si>
+    <t>Building The Facebook News Feed With Relay</t>
+  </si>
+  <si>
+    <t>2015-03-19</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/03/19/building-the-facebook-news-feed-with-relay.html</t>
+  </si>
+  <si>
+    <t>React v0.13.1</t>
+  </si>
+  <si>
+    <t>2015-03-16</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/03/16/react-v0.13.1.html</t>
+  </si>
+  <si>
+    <t>React v0.13</t>
+  </si>
+  <si>
+    <t>2015-03-10</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/03/10/react-v0.13.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #25</t>
+  </si>
+  <si>
+    <t>2015-03-04</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/03/04/community-roundup-25.html</t>
+  </si>
+  <si>
+    <t>React v0.13 RC2</t>
+  </si>
+  <si>
+    <t>2015-03-03</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/03/03/react-v0.13-rc2.html</t>
+  </si>
+  <si>
+    <t>Streamlining React Elements</t>
+  </si>
+  <si>
+    <t>2015-02-24</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/02/24/streamlining-react-elements.html</t>
+  </si>
+  <si>
+    <t>React v0.13 RC</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/02/24/react-v0.13-rc1.html</t>
+  </si>
+  <si>
+    <t>Introducing Relay and GraphQL</t>
+  </si>
+  <si>
+    <t>2015-02-20</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/02/20/introducing-relay-and-graphql.html</t>
+  </si>
+  <si>
+    <t>React.js Conf Round-up 2015</t>
+  </si>
+  <si>
+    <t>2015-02-18</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/02/18/react-conf-roundup-2015.html</t>
+  </si>
+  <si>
+    <t>React v0.13.0 Beta 1</t>
+  </si>
+  <si>
+    <t>2015-01-27</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2015/01/27/react-v0.13.0-beta-1.html</t>
+  </si>
+  <si>
+    <t>React.js Conf Diversity Scholarship</t>
+  </si>
+  <si>
+    <t>2014-12-19</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/12/19/react-js-conf-diversity-scholarship.html</t>
+  </si>
+  <si>
+    <t>React v0.12.2</t>
+  </si>
+  <si>
+    <t>2014-12-18</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/12/18/react-v0.12.2.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #24</t>
+  </si>
+  <si>
+    <t>2014-11-25</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/11/25/community-roundup-24.html</t>
+  </si>
+  <si>
+    <t>React.js Conf Updates</t>
+  </si>
+  <si>
+    <t>2014-11-24</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/11/24/react-js-conf-updates.html</t>
+  </si>
+  <si>
+    <t>React v0.12</t>
+  </si>
+  <si>
+    <t>2014-10-28</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/10/28/react-v0.12.html</t>
+  </si>
+  <si>
+    <t>React.js Conf</t>
+  </si>
+  <si>
+    <t>2014-10-27</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/10/27/react-js-conf.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #23</t>
+  </si>
+  <si>
+    <t>2014-10-17</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/10/17/community-roundup-23.html</t>
+  </si>
+  <si>
+    <t>React v0.12 RC</t>
+  </si>
+  <si>
+    <t>2014-10-16</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/10/16/react-v0.12-rc1.html</t>
+  </si>
+  <si>
+    <t>Introducing React Elements</t>
+  </si>
+  <si>
+    <t>2014-10-14</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/10/14/introducing-react-elements.html</t>
+  </si>
+  <si>
+    <t>Testing Flux Applications</t>
+  </si>
+  <si>
+    <t>2014-09-24</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/09/24/testing-flux-applications.html</t>
+  </si>
+  <si>
+    <t>React v0.11.2</t>
+  </si>
+  <si>
+    <t>2014-09-16</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/09/16/react-v0.11.2.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #22</t>
+  </si>
+  <si>
+    <t>2014-09-12</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/09/12/community-round-up-22.html</t>
+  </si>
+  <si>
+    <t>Introducing the JSX Specification</t>
+  </si>
+  <si>
+    <t>2014-09-03</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/09/03/introducing-the-jsx-specification.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #21</t>
+  </si>
+  <si>
+    <t>2014-08-03</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/08/03/community-roundup-21.html</t>
+  </si>
+  <si>
+    <t>Flux: Actions and the Dispatcher</t>
+  </si>
+  <si>
+    <t>2014-07-30</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/07/30/flux-actions-and-the-dispatcher.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #20</t>
+  </si>
+  <si>
+    <t>2014-07-28</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/07/28/community-roundup-20.html</t>
+  </si>
+  <si>
+    <t>React v0.11.1</t>
+  </si>
+  <si>
+    <t>2014-07-25</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/07/25/react-v0.11.1.html</t>
+  </si>
+  <si>
+    <t>React v0.11</t>
+  </si>
+  <si>
+    <t>2014-07-17</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/07/17/react-v0.11.html</t>
+  </si>
+  <si>
+    <t>React v0.11 RC</t>
+  </si>
+  <si>
+    <t>2014-07-13</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/07/13/react-v0.11-rc1.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #19</t>
+  </si>
+  <si>
+    <t>2014-06-27</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/06/27/community-roundup-19.html</t>
+  </si>
+  <si>
+    <t>One Year of Open-Source React</t>
+  </si>
+  <si>
+    <t>2014-05-29</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/05/29/one-year-of-open-source-react.html</t>
+  </si>
+  <si>
+    <t>Flux: An Application Architecture for React</t>
+  </si>
+  <si>
+    <t>2014-05-06</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/05/06/flux.html</t>
+  </si>
+  <si>
+    <t>Use React and JSX in ASP.NET MVC</t>
+  </si>
+  <si>
+    <t>2014-04-04</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/04/04/reactnet.html</t>
+  </si>
+  <si>
+    <t>The Road to 1.0</t>
+  </si>
+  <si>
+    <t>2014-03-28</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/03/28/the-road-to-1.0.html</t>
+  </si>
+  <si>
+    <t>React v0.10</t>
+  </si>
+  <si>
+    <t>2014-03-21</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/03/21/react-v0.10.html</t>
+  </si>
+  <si>
+    <t>React v0.10 RC</t>
+  </si>
+  <si>
+    <t>2014-03-19</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/03/19/react-v0.10-rc1.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #18</t>
+  </si>
+  <si>
+    <t>2014-03-14</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/03/14/community-roundup-18.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #17</t>
+  </si>
+  <si>
+    <t>2014-02-24</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/02/24/community-roundup-17.html</t>
+  </si>
+  <si>
+    <t>React v0.9</t>
+  </si>
+  <si>
+    <t>2014-02-20</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/02/20/react-v0.9.html</t>
+  </si>
+  <si>
+    <t>React v0.9 RC</t>
+  </si>
+  <si>
+    <t>2014-02-16</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/02/16/react-v0.9-rc1.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #16</t>
+  </si>
+  <si>
+    <t>2014-02-15</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/02/15/community-roundup-16.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #15</t>
+  </si>
+  <si>
+    <t>2014-02-05</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/02/05/community-roundup-15.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #14</t>
+  </si>
+  <si>
+    <t>2014-01-06</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/01/06/community-roundup-14.html</t>
+  </si>
+  <si>
+    <t>React Chrome Developer Tools</t>
+  </si>
+  <si>
+    <t>2014-01-02</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2014/01/02/react-chrome-developer-tools.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #13</t>
+  </si>
+  <si>
+    <t>2013-12-30</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2013/12/30/community-roundup-13.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #12</t>
+  </si>
+  <si>
+    <t>2013-12-23</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2013/12/23/community-roundup-12.html</t>
+  </si>
+  <si>
+    <t>React v0.8</t>
+  </si>
+  <si>
+    <t>2013-12-19</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2013/12/19/react-v0.8.0.html</t>
+  </si>
+  <si>
+    <t>React v0.5.2, v0.4.2</t>
+  </si>
+  <si>
+    <t>2013-12-18</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2013/12/18/react-v0.5.2-v0.4.2.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #11</t>
+  </si>
+  <si>
+    <t>2013-11-18</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2013/11/18/community-roundup-11.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #10</t>
+  </si>
+  <si>
+    <t>2013-11-06</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2013/11/06/community-roundup-10.html</t>
+  </si>
+  <si>
+    <t>React v0.5.1</t>
+  </si>
+  <si>
+    <t>2013-10-29</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2013/10/29/react-v0-5-1.html</t>
+  </si>
+  <si>
+    <t>React v0.5</t>
+  </si>
+  <si>
+    <t>2013-10-16</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2013/10/16/react-v0.5.0.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #9</t>
+  </si>
+  <si>
+    <t>2013-10-03</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2013/10/3/community-roundup-9.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #8</t>
+  </si>
+  <si>
+    <t>2013-09-24</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2013/09/24/community-roundup-8.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #7</t>
+  </si>
+  <si>
+    <t>2013-08-26</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2013/08/26/community-roundup-7.html</t>
+  </si>
+  <si>
+    <t>Use React and JSX in Python Applications</t>
+  </si>
+  <si>
+    <t>2013-08-19</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2013/08/19/use-react-and-jsx-in-python-applications.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #6</t>
+  </si>
+  <si>
+    <t>2013-08-05</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2013/08/05/community-roundup-6.html</t>
+  </si>
+  <si>
+    <t>Use React and JSX in Ruby on Rails</t>
+  </si>
+  <si>
+    <t>2013-07-30</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2013/07/30/use-react-and-jsx-in-ruby-on-rails.html</t>
+  </si>
+  <si>
+    <t>React v0.4.1</t>
+  </si>
+  <si>
+    <t>2013-07-26</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2013/07/26/react-v0-4-1.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #5</t>
+  </si>
+  <si>
+    <t>2013-07-23</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2013/07/23/community-roundup-5.html</t>
+  </si>
+  <si>
+    <t>React v0.4.0</t>
+  </si>
+  <si>
+    <t>2013-07-17</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2013/07/17/react-v0-4-0.html</t>
+  </si>
+  <si>
+    <t>New in React v0.4: Prop Validation and Default Values</t>
+  </si>
+  <si>
+    <t>2013-07-11</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2013/07/11/react-v0-4-prop-validation-and-default-values.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #4</t>
+  </si>
+  <si>
+    <t>2013-07-03</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2013/07/03/community-roundup-4.html</t>
+  </si>
+  <si>
+    <t>New in React v0.4: Autobind by Default</t>
+  </si>
+  <si>
+    <t>2013-07-02</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2013/07/02/react-v0-4-autobind-by-default.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #3</t>
+  </si>
+  <si>
+    <t>2013-06-27</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2013/06/27/community-roundup-3.html</t>
+  </si>
+  <si>
+    <t>React v0.3.3</t>
+  </si>
+  <si>
+    <t>2013-06-21</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2013/06/21/react-v0-3-3.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #2</t>
+  </si>
+  <si>
+    <t>2013-06-19</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2013/06/19/community-roundup-2.html</t>
+  </si>
+  <si>
+    <t>Community Round-up #1</t>
+  </si>
+  <si>
+    <t>2013-06-12</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2013/06/12/community-roundup.html</t>
+  </si>
+  <si>
+    <t>Why did we build React?</t>
+  </si>
+  <si>
+    <t>2013-06-05</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2013/06/05/why-react.html</t>
+  </si>
+  <si>
+    <t>JSFiddle Integration</t>
+  </si>
+  <si>
+    <t>2013-06-02</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/blog/2013/06/02/jsfiddle-integration.html</t>
+  </si>
+  <si>
+    <t>Super fast super property accessJavaScript</t>
+  </si>
+  <si>
+    <t>v8.dev</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/fast-super</t>
+  </si>
+  <si>
+    <t>Faster JavaScript callsinternals</t>
+  </si>
+  <si>
+    <t>2021-02-15</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/adaptor-frame</t>
+  </si>
+  <si>
+    <t>V8 release v8.9release</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-89</t>
+  </si>
+  <si>
+    <t>An additional non-backtracking RegExp engineinternalsRegExp</t>
+  </si>
+  <si>
+    <t>2021-01-11</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/non-backtracking-regexp</t>
+  </si>
+  <si>
+    <t>V8 release v8.7release</t>
+  </si>
+  <si>
+    <t>2020-10-23</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-87</t>
+  </si>
+  <si>
+    <t>Indicium: V8 runtime tracer tooltoolssystem-analyzer</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/system-analyzer</t>
+  </si>
+  <si>
+    <t>Slack tracking in V8internals</t>
+  </si>
+  <si>
+    <t>2020-09-24</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/slack-tracking</t>
+  </si>
+  <si>
+    <t>V8 release v8.6release</t>
+  </si>
+  <si>
+    <t>2020-09-21</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-86</t>
+  </si>
+  <si>
+    <t>V8 release v8.5release</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-85</t>
+  </si>
+  <si>
+    <t>V8 release v8.4release</t>
+  </si>
+  <si>
+    <t>2020-06-30</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-84</t>
+  </si>
+  <si>
+    <t>High-performance garbage collection for C++internalsmemorycppgc</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/high-performance-cpp-gc</t>
+  </si>
+  <si>
+    <t>Understanding the ECMAScript spec, part 4ECMAScriptUnderstanding ECMAScript</t>
+  </si>
+  <si>
+    <t>2020-05-19</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/understanding-ecmascript-part-4</t>
+  </si>
+  <si>
+    <t>Up to 4GB of memory in WebAssemblyWebAssemblyJavaScripttooling</t>
+  </si>
+  <si>
+    <t>2020-05-14</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/4gb-wasm-memory</t>
+  </si>
+  <si>
+    <t>V8 release v8.3release</t>
+  </si>
+  <si>
+    <t>2020-05-04</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-83</t>
+  </si>
+  <si>
+    <t>What’s in that .wasm? Introducing: wasm-decompileWebAssemblytooling</t>
+  </si>
+  <si>
+    <t>2020-04-27</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/wasm-decompile</t>
+  </si>
+  <si>
+    <t>Understanding the ECMAScript spec, part 3ECMAScriptUnderstanding ECMAScript</t>
+  </si>
+  <si>
+    <t>2020-04-01</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/understanding-ecmascript-part-3</t>
+  </si>
+  <si>
+    <t>Pointer Compression in V8internalsmemory</t>
+  </si>
+  <si>
+    <t>2020-03-30</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/pointer-compression</t>
+  </si>
+  <si>
+    <t>Understanding the ECMAScript spec, part 2ECMAScriptUnderstanding ECMAScript</t>
+  </si>
+  <si>
+    <t>2020-03-02</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/understanding-ecmascript-part-2</t>
+  </si>
+  <si>
+    <t>V8 release v8.1release</t>
+  </si>
+  <si>
+    <t>2020-02-25</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-81</t>
+  </si>
+  <si>
+    <t>Understanding the ECMAScript spec, part 1ECMAScriptUnderstanding ECMAScript</t>
+  </si>
+  <si>
+    <t>2020-02-03</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/understanding-ecmascript-part-1</t>
+  </si>
+  <si>
+    <t>V8 release v8.0release</t>
+  </si>
+  <si>
+    <t>2019-12-18</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-80</t>
+  </si>
+  <si>
+    <t>Outside the web: standalone WebAssembly binaries using EmscriptenWebAssemblytooling</t>
+  </si>
+  <si>
+    <t>2019-11-21</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/emscripten-standalone-wasm</t>
+  </si>
+  <si>
+    <t>V8 release v7.9release</t>
+  </si>
+  <si>
+    <t>2019-11-20</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-79</t>
+  </si>
+  <si>
+    <t>Improving V8 regular expressionsinternalsRegExp</t>
+  </si>
+  <si>
+    <t>2019-10-04</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/regexp-tier-up</t>
+  </si>
+  <si>
+    <t>V8 release v7.8release</t>
+  </si>
+  <si>
+    <t>2019-09-27</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-78</t>
+  </si>
+  <si>
+    <t>A lighter V8internalsmemorypresentations</t>
+  </si>
+  <si>
+    <t>2019-09-12</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-lite</t>
+  </si>
+  <si>
+    <t>The story of a V8 performance cliff in Reactinternalspresentations</t>
+  </si>
+  <si>
+    <t>2019-08-28</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/react-cliff</t>
+  </si>
+  <si>
+    <t>V8 release v7.7release</t>
+  </si>
+  <si>
+    <t>2019-08-13</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-77</t>
+  </si>
+  <si>
+    <t>Emscripten and the LLVM WebAssembly backendWebAssemblytooling</t>
+  </si>
+  <si>
+    <t>2019-07-01</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/emscripten-llvm-wasm</t>
+  </si>
+  <si>
+    <t>The cost of JavaScript in 2019internalsparsing</t>
+  </si>
+  <si>
+    <t>2019-06-25</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/cost-of-javascript-2019</t>
+  </si>
+  <si>
+    <t>V8 release v7.6release</t>
+  </si>
+  <si>
+    <t>2019-06-19</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-76</t>
+  </si>
+  <si>
+    <t>Code caching for WebAssembly developersWebAssemblyinternals</t>
+  </si>
+  <si>
+    <t>2019-06-17</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/wasm-code-caching</t>
+  </si>
+  <si>
+    <t>V8 release v7.5release</t>
+  </si>
+  <si>
+    <t>2019-05-16</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-75</t>
+  </si>
+  <si>
+    <t>Faster and more feature-rich internationalization APIsECMAScriptIntl</t>
+  </si>
+  <si>
+    <t>2019-04-25</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/intl</t>
+  </si>
+  <si>
+    <t>A year with Spectre: a V8 perspectivesecurity</t>
+  </si>
+  <si>
+    <t>2019-04-23</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/spectre</t>
+  </si>
+  <si>
+    <t>Blazingly fast parsing, part 2: lazy parsinginternalsparsing</t>
+  </si>
+  <si>
+    <t>2019-04-15</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/preparser</t>
+  </si>
+  <si>
+    <t>Code caching for JavaScript developersinternals</t>
+  </si>
+  <si>
+    <t>2019-04-08</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/code-caching-for-devs</t>
+  </si>
+  <si>
+    <t>Blazingly fast parsing, part 1: optimizing the scannerinternalsparsing</t>
+  </si>
+  <si>
+    <t>2019-03-25</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/scanner</t>
+  </si>
+  <si>
+    <t>V8 release v7.4release</t>
+  </si>
+  <si>
+    <t>2019-03-22</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-74</t>
+  </si>
+  <si>
+    <t>JIT-less V8internals</t>
+  </si>
+  <si>
+    <t>2019-03-13</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/jitless</t>
+  </si>
+  <si>
+    <t>V8 release v7.3release</t>
+  </si>
+  <si>
+    <t>2019-02-07</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-73</t>
+  </si>
+  <si>
+    <t>Trash talk: the Orinoco garbage collectorinternalsmemorypresentations</t>
+  </si>
+  <si>
+    <t>2019-01-03</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/trash-talk</t>
+  </si>
+  <si>
+    <t>V8 release v7.2release</t>
+  </si>
+  <si>
+    <t>2018-12-18</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-72</t>
+  </si>
+  <si>
+    <t>Speeding up spread elementsECMAScriptbenchmarks</t>
+  </si>
+  <si>
+    <t>2018-12-04</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/spread-elements</t>
+  </si>
+  <si>
+    <t>Faster async functions and promisesECMAScriptbenchmarkspresentations</t>
+  </si>
+  <si>
+    <t>2018-11-12</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/fast-async</t>
+  </si>
+  <si>
+    <t>V8 release v7.1release</t>
+  </si>
+  <si>
+    <t>2018-10-31</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-71</t>
+  </si>
+  <si>
+    <t>V8 release v7.0release</t>
+  </si>
+  <si>
+    <t>2018-10-15</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-70</t>
+  </si>
+  <si>
+    <t>Getting things sorted in V8ECMAScriptinternals</t>
+  </si>
+  <si>
+    <t>2018-09-28</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/array-sort</t>
+  </si>
+  <si>
+    <t>Improving DataView performance in V8ECMAScriptbenchmarks</t>
+  </si>
+  <si>
+    <t>2018-09-18</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/dataview</t>
+  </si>
+  <si>
+    <t>Celebrating 10 years of V8benchmarks</t>
+  </si>
+  <si>
+    <t>2018-09-11</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/10-years</t>
+  </si>
+  <si>
+    <t>Liftoff: a new baseline compiler for WebAssembly in V8WebAssemblyinternals</t>
+  </si>
+  <si>
+    <t>2018-08-20</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/liftoff</t>
+  </si>
+  <si>
+    <t>Embedded builtinsinternals</t>
+  </si>
+  <si>
+    <t>2018-08-14</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/embedded-builtins</t>
+  </si>
+  <si>
+    <t>V8 release v6.9release</t>
+  </si>
+  <si>
+    <t>2018-08-07</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-69</t>
+  </si>
+  <si>
+    <t>V8 release v6.8release</t>
+  </si>
+  <si>
+    <t>2018-06-21</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-68</t>
+  </si>
+  <si>
+    <t>Concurrent marking in V8internalsmemory</t>
+  </si>
+  <si>
+    <t>2018-06-11</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/concurrent-marking</t>
+  </si>
+  <si>
+    <t>V8 release v6.7release</t>
+  </si>
+  <si>
+    <t>2018-05-04</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-67</t>
+  </si>
+  <si>
+    <t>Adding BigInts to V8ECMAScript</t>
+  </si>
+  <si>
+    <t>2018-05-02</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/bigint</t>
+  </si>
+  <si>
+    <t>Improved code cachinginternals</t>
+  </si>
+  <si>
+    <t>2018-04-24</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/improved-code-caching</t>
+  </si>
+  <si>
+    <t>V8 release v6.6release</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-66</t>
+  </si>
+  <si>
+    <t>Background compilationinternals</t>
+  </si>
+  <si>
+    <t>2018-03-26</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/background-compilation</t>
+  </si>
+  <si>
+    <t>Tracing from JS to the DOM and back againinternalsmemory</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/tracing-js-dom</t>
+  </si>
+  <si>
+    <t>Lazy deserializationinternals</t>
+  </si>
+  <si>
+    <t>2018-02-12</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/lazy-deserialization</t>
+  </si>
+  <si>
+    <t>V8 release v6.5release</t>
+  </si>
+  <si>
+    <t>2018-02-01</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-65</t>
+  </si>
+  <si>
+    <t>Optimizing hash tables: hiding the hash codeinternals</t>
+  </si>
+  <si>
+    <t>2018-01-29</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/hash-code</t>
+  </si>
+  <si>
+    <t>Chrome welcomes Speedometer 2.0!benchmarks</t>
+  </si>
+  <si>
+    <t>2018-01-24</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/speedometer-2</t>
+  </si>
+  <si>
+    <t>V8 release v6.4release</t>
+  </si>
+  <si>
+    <t>2017-12-19</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-64</t>
+  </si>
+  <si>
+    <t>JavaScript code coverageinternals</t>
+  </si>
+  <si>
+    <t>2017-12-13</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/javascript-code-coverage</t>
+  </si>
+  <si>
+    <t>Orinoco: young generation garbage collectioninternalsmemory</t>
+  </si>
+  <si>
+    <t>2017-11-29</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/orinoco-parallel-scavenger</t>
+  </si>
+  <si>
+    <t>Taming architecture complexity in V8 — the CodeStubAssemblerinternals</t>
+  </si>
+  <si>
+    <t>2017-11-16</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/csa</t>
+  </si>
+  <si>
+    <t>Announcing the Web Tooling BenchmarkbenchmarksNode.js</t>
+  </si>
+  <si>
+    <t>2017-11-06</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/web-tooling-benchmark</t>
+  </si>
+  <si>
+    <t>V8 release v6.3release</t>
+  </si>
+  <si>
+    <t>2017-10-25</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-63</t>
+  </si>
+  <si>
+    <t>Optimizing ES2015 proxies in V8ECMAScriptbenchmarksinternals</t>
+  </si>
+  <si>
+    <t>2017-10-05</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/optimizing-proxies</t>
+  </si>
+  <si>
+    <t>An internship on laziness: lazy unlinking of deoptimized functionsmemoryinternals</t>
+  </si>
+  <si>
+    <t>2017-10-04</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/lazy-unlinking</t>
+  </si>
+  <si>
+    <t>Temporarily disabling escape analysissecurity</t>
+  </si>
+  <si>
+    <t>2017-09-22</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/disabling-escape-analysis</t>
+  </si>
+  <si>
+    <t>Elements kinds in V8internalspresentations</t>
+  </si>
+  <si>
+    <t>2017-09-12</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/elements-kinds</t>
+  </si>
+  <si>
+    <t>V8 release v6.2release</t>
+  </si>
+  <si>
+    <t>2017-09-11</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-62</t>
+  </si>
+  <si>
+    <t>Fast properties in V8internals</t>
+  </si>
+  <si>
+    <t>2017-08-30</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/fast-properties</t>
+  </si>
+  <si>
+    <t>About that hash flooding vulnerability in Node.js…security</t>
+  </si>
+  <si>
+    <t>2017-08-11</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/hash-flooding</t>
+  </si>
+  <si>
+    <t>V8 release v6.1release</t>
+  </si>
+  <si>
+    <t>2017-08-03</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-61</t>
+  </si>
+  <si>
+    <t>V8 release v6.0release</t>
+  </si>
+  <si>
+    <t>2017-06-09</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-60</t>
+  </si>
+  <si>
+    <t>Launching Ignition and TurboFaninternals</t>
+  </si>
+  <si>
+    <t>2017-05-15</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/launching-ignition-and-turbofan</t>
+  </si>
+  <si>
+    <t>V8 release v5.9release</t>
+  </si>
+  <si>
+    <t>2017-04-27</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-59</t>
+  </si>
+  <si>
+    <t>Retiring Octanebenchmarks</t>
+  </si>
+  <si>
+    <t>2017-04-12</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/retiring-octane</t>
+  </si>
+  <si>
+    <t>V8 release v5.8release</t>
+  </si>
+  <si>
+    <t>2017-03-20</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-58</t>
+  </si>
+  <si>
+    <t>Fast for-in in V8internals</t>
+  </si>
+  <si>
+    <t>2017-03-01</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/fast-for-in</t>
+  </si>
+  <si>
+    <t>High-performance ES2015 and beyondECMAScript</t>
+  </si>
+  <si>
+    <t>2017-02-17</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/high-performance-es2015</t>
+  </si>
+  <si>
+    <t>Help us test the future of V8!internals</t>
+  </si>
+  <si>
+    <t>2017-02-14</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/test-the-future</t>
+  </si>
+  <si>
+    <t>One small step for Chrome, one giant heap for V8memory</t>
+  </si>
+  <si>
+    <t>2017-02-09</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/heap-size-limit</t>
+  </si>
+  <si>
+    <t>V8 release v5.7release</t>
+  </si>
+  <si>
+    <t>2017-02-06</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-57</t>
+  </si>
+  <si>
+    <t>Speeding up V8 regular expressionsinternalsRegExp</t>
+  </si>
+  <si>
+    <t>2017-01-10</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/speeding-up-regular-expressions</t>
+  </si>
+  <si>
+    <t>How V8 measures real-world performancebenchmarks</t>
+  </si>
+  <si>
+    <t>2016-12-21</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/real-world-performance</t>
+  </si>
+  <si>
+    <t>V8 ❤️ Node.jsNode.js</t>
+  </si>
+  <si>
+    <t>2016-12-15</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-nodejs</t>
+  </si>
+  <si>
+    <t>V8 release v5.6release</t>
+  </si>
+  <si>
+    <t>2016-12-02</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-56</t>
+  </si>
+  <si>
+    <t>WebAssembly browser previewWebAssembly</t>
+  </si>
+  <si>
+    <t>2016-10-31</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/webassembly-browser-preview</t>
+  </si>
+  <si>
+    <t>V8 release v5.5release</t>
+  </si>
+  <si>
+    <t>2016-10-24</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-55</t>
+  </si>
+  <si>
+    <t>Optimizing V8 memory consumptionmemorybenchmarks</t>
+  </si>
+  <si>
+    <t>2016-10-07</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/optimizing-v8-memory</t>
+  </si>
+  <si>
+    <t>V8 release v5.4release</t>
+  </si>
+  <si>
+    <t>2016-09-09</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-54</t>
+  </si>
+  <si>
+    <t>Firing up the Ignition interpreterinternals</t>
+  </si>
+  <si>
+    <t>2016-08-23</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/ignition-interpreter</t>
+  </si>
+  <si>
+    <t>V8 at the BlinkOn 6 conferencepresentations</t>
+  </si>
+  <si>
+    <t>2016-07-21</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/blinkon-6</t>
+  </si>
+  <si>
+    <t>V8 release v5.3release</t>
+  </si>
+  <si>
+    <t>2016-07-18</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-53</t>
+  </si>
+  <si>
+    <t>V8 release v5.2release</t>
+  </si>
+  <si>
+    <t>2016-06-04</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-52</t>
+  </si>
+  <si>
+    <t>ES2015, ES2016, and beyondECMAScript</t>
+  </si>
+  <si>
+    <t>2016-04-29</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/modern-javascript</t>
+  </si>
+  <si>
+    <t>V8 release v5.1release</t>
+  </si>
+  <si>
+    <t>2016-04-23</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-51</t>
+  </si>
+  <si>
+    <t>Jank Busters Part Two: Orinocointernalsmemory</t>
+  </si>
+  <si>
+    <t>2016-04-12</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/orinoco</t>
+  </si>
+  <si>
+    <t>V8 release v5.0release</t>
+  </si>
+  <si>
+    <t>2016-03-15</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-50</t>
+  </si>
+  <si>
+    <t>Experimental support for WebAssembly in V8WebAssembly</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/webassembly-experimental</t>
+  </si>
+  <si>
+    <t>RegExp lookbehind assertionsECMAScriptRegExp</t>
+  </si>
+  <si>
+    <t>2016-02-26</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/regexp-lookbehind-assertions</t>
+  </si>
+  <si>
+    <t>V8 extrasinternals</t>
+  </si>
+  <si>
+    <t>2016-02-04</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-extras</t>
+  </si>
+  <si>
+    <t>V8 release v4.9release</t>
+  </si>
+  <si>
+    <t>2016-01-26</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-49</t>
+  </si>
+  <si>
+    <t>There’s Math.random(), and then there’s Math.random()ECMAScriptinternals</t>
+  </si>
+  <si>
+    <t>2015-12-17</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/math-random</t>
+  </si>
+  <si>
+    <t>V8 release v4.8release</t>
+  </si>
+  <si>
+    <t>2015-11-25</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-48</t>
+  </si>
+  <si>
+    <t>Jank Busters Part Onememory</t>
+  </si>
+  <si>
+    <t>2015-10-30</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/jank-busters</t>
+  </si>
+  <si>
+    <t>V8 release v4.7release</t>
+  </si>
+  <si>
+    <t>2015-10-14</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-47</t>
+  </si>
+  <si>
+    <t>Custom startup snapshotsinternals</t>
+  </si>
+  <si>
+    <t>2015-09-25</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/custom-startup-snapshots</t>
+  </si>
+  <si>
+    <t>V8 release v4.6release</t>
+  </si>
+  <si>
+    <t>2015-08-28</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-46</t>
+  </si>
+  <si>
+    <t>Getting garbage collection for freeinternalsmemory</t>
+  </si>
+  <si>
+    <t>2015-08-07</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/free-garbage-collection</t>
+  </si>
+  <si>
+    <t>Code cachinginternals</t>
+  </si>
+  <si>
+    <t>2015-07-27</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/code-caching</t>
+  </si>
+  <si>
+    <t>V8 release v4.5release</t>
+  </si>
+  <si>
+    <t>2015-07-17</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/v8-release-45</t>
+  </si>
+  <si>
+    <t>Digging into the TurboFan JITinternals</t>
+  </si>
+  <si>
+    <t>2015-07-13</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/turbofan-jit</t>
+  </si>
+  <si>
+    <t>Hello, world!</t>
+  </si>
+  <si>
+    <t>2015-07-10</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/hello-world</t>
+  </si>
+  <si>
+    <t>Should we really use useMemo?</t>
+  </si>
+  <si>
+    <t>React Status</t>
+  </si>
+  <si>
+    <t>2021-02-17</t>
+  </si>
+  <si>
+    <t>https://react.statuscode.com/issues/226</t>
+  </si>
+  <si>
+    <t>Making videos, slides, or terminal UIs with React</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>https://react.statuscode.com/issues/225</t>
+  </si>
+  <si>
+    <t>Using AWS Lambda for React SSR</t>
+  </si>
+  <si>
+    <t>2021-02-03</t>
+  </si>
+  <si>
+    <t>https://react.statuscode.com/issues/224</t>
+  </si>
+  <si>
+    <t>The Tao of React</t>
+  </si>
+  <si>
+    <t>2021-01-27</t>
+  </si>
+  <si>
+    <t>https://react.statuscode.com/issues/223</t>
+  </si>
+  <si>
+    <t>How V8 continues to get faster</t>
+  </si>
+  <si>
+    <t>2021-02-19</t>
+  </si>
+  <si>
+    <t>https://javascriptweekly.com/issues/526</t>
+  </si>
+  <si>
+    <t>Eich shares his full JavaScript story</t>
+  </si>
+  <si>
+    <t>2021-02-12</t>
+  </si>
+  <si>
+    <t>https://javascriptweekly.com/issues/525</t>
+  </si>
+  <si>
+    <t>How GitHub keeps its new homepage fast</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>https://javascriptweekly.com/issues/524</t>
+  </si>
+  <si>
+    <t>undefined vs null in JavaScript</t>
+  </si>
+  <si>
+    <t>2021-01-29</t>
+  </si>
+  <si>
+    <t>https://javascriptweekly.com/issues/523</t>
+  </si>
+  <si>
+    <t>移动应用不再是初创企业的好主意</t>
+  </si>
+  <si>
+    <t>2021-02-21</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/mkD8q4IQDlVUUXTsQ1tS</t>
+  </si>
+  <si>
+    <t>Deno现能够编译为独立的自包含二进制文件</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/0lsGR6lGWctq5NogpNrw</t>
+  </si>
+  <si>
+    <t>15 个常见的 Node.js 面试问题及答案</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/qbjXf0413REecA2EXGWd</t>
+  </si>
+  <si>
+    <t>2021年前端发展预测</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/qZ5gKxoS8VZDKOcyedjR</t>
+  </si>
+  <si>
+    <t>大数据+云：Kylin/Spark/Clickhouse/Hudi 的大佬们怎么看？</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/BjovMJUOiIzESTv1fgoZ</t>
+  </si>
+  <si>
+    <t>干货 | 前端跨端业务整合的探索与实践</t>
+  </si>
+  <si>
+    <t>2021-02-20</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/dsBDeLEohK3IHe8MblFB</t>
+  </si>
+  <si>
+    <t>抛弃V8参数适配器框架：JavaScript调用提速40%的实践</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/xJ6f3Uu2M7hEglEqmyNa</t>
+  </si>
+  <si>
+    <t>Deno 2020 年大事记</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/PFW9j6TzIZpNd0tJ24JG</t>
+  </si>
+  <si>
+    <t>从推荐算法到前端开发，这是字节跳动技术Leader们最中意的40项学习资源 ｜ 资源推荐</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/oO4VrzEj5XQtzLZSR2WA</t>
+  </si>
+  <si>
+    <t>无意间发现 Google 代码模板，分享给大家！</t>
+  </si>
+  <si>
+    <t>2021-02-07</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/1c0e4bb1b146ed0ffd55ce05e</t>
+  </si>
+  <si>
+    <t>长篇总结之JavaScript，巩固前端基础</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/b6a6b31fa2d890d5e89fee4cb</t>
+  </si>
+  <si>
+    <t>Vuex 4 正式发布：打包现在与 Vue 3 一致</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/MAXNFlc24wNh80hIhsSv</t>
+  </si>
+  <si>
+    <t>CSS开发过程中的20个快速提升技巧</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/9a34581102d4b7b38070b83b1</t>
+  </si>
+  <si>
+    <t>Wasmer发布GA版本的WebAssembly运行时</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/f2Vml9f1KHIfTwGi5g1b</t>
+  </si>
+  <si>
+    <t>爱奇艺知识WEB前端组件化实践</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/5HirT1NNZYZmVwOUHaJG</t>
+  </si>
+  <si>
+    <t>浅析 Node 进程与线程</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/gF5xh4zt6mNwirLBSKpE</t>
+  </si>
+  <si>
+    <t>前阿里P8专家winter：怎么打造一支能力过硬的前端团队？</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/lvUOrbAu4PjdkSMRZOIQ</t>
+  </si>
+  <si>
+    <t>茶余饭后聊聊 Vue3.0 响应式数据那些事儿</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/HzMBaOLyEQANup0ycpzX</t>
+  </si>
+  <si>
+    <t>乾坤大挪移！React 也能 “用上” computed 属性</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/vCgBfwGCayKVIHoZ2i1s</t>
+  </si>
+  <si>
+    <t>webpack | 谈谈webpack的本质</t>
+  </si>
+  <si>
+    <t>2021-01-30</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/c48403d68f6b75356c02edb69</t>
+  </si>
+  <si>
+    <t>读2020年Javascript趋势报告展望ES2020</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/8779819d0cd6ed24140f0e9b9</t>
+  </si>
+  <si>
+    <t>0到1：闲鱼高复杂度高性能社区圈子开发实录</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/RaGWMMAhkBl0DIqyCZpS</t>
+  </si>
+  <si>
+    <t>一种简单无副作用的同源跨页面数据同步方案</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/oNphTLBXC1EVwJzGjQBb</t>
+  </si>
+  <si>
+    <t>浏览器里的本地数据库：IndexedDB</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/jglgydX0S0OMRlANvzXP</t>
+  </si>
+  <si>
+    <t>DIY VSCode 插件，让你的开发效率突飞猛进</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/gMil7xj0JPBBhcYZHfWW</t>
+  </si>
+  <si>
+    <t>#视频# 2020年度十大创新先行者创新成果案例展示-瞬玩科技</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/VPh40FIY0b5sVpOUPHIu</t>
+  </si>
+  <si>
+    <t>WKWebView 请求拦截探索与实践</t>
+  </si>
+  <si>
+    <t>知乎-专栏-网易云音乐大前端团队</t>
+  </si>
+  <si>
+    <t>2021-01-28</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/347592487</t>
+  </si>
+  <si>
+    <t>函数式编程进阶：Monad 与 异步函数的组合</t>
+  </si>
+  <si>
+    <t>2021-01-19</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/345339684</t>
+  </si>
+  <si>
+    <t>Flutter 图片控件适配之路</t>
+  </si>
+  <si>
+    <t>2021-01-13</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/343932734</t>
+  </si>
+  <si>
+    <t>剖析 lottie-web 动画实现原理</t>
+  </si>
+  <si>
+    <t>2021-01-07</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/342477231</t>
+  </si>
+  <si>
+    <t>Poplayer 云音乐优化实践</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/340595290</t>
+  </si>
+  <si>
+    <t>React 事件系统工作原理</t>
+  </si>
+  <si>
+    <t>2020-12-23</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/338904728</t>
+  </si>
+  <si>
+    <t>漫谈 React Fiber</t>
+  </si>
+  <si>
+    <t>2020-12-16</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/337275795</t>
+  </si>
+  <si>
+    <t>云音乐 Android 视频「无缝」播放实现总结</t>
+  </si>
+  <si>
+    <t>2020-12-09</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/335015746</t>
+  </si>
+  <si>
+    <t>聊聊 RN 中 Android 提供 View 的那些坑</t>
+  </si>
+  <si>
+    <t>2020-12-02</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/325802528</t>
+  </si>
+  <si>
+    <t>如何基于 TypeScript 实现控制反转</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/311184005</t>
+  </si>
+  <si>
+    <t>Node开发实践总结-定时脚本的设计与实现</t>
+  </si>
+  <si>
+    <t>知乎-专栏-IMWeb前端社区</t>
+  </si>
+  <si>
+    <t>2021-01-05</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/342090208</t>
+  </si>
+  <si>
+    <t>看前端如何通过WebAssembly实现播放器预览能力</t>
+  </si>
+  <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/341001951</t>
+  </si>
+  <si>
+    <t>2020年大前端技术趋势解读</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/338813991</t>
+  </si>
+  <si>
+    <t>【前端实时音视频系列】WebRTC入门概览</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/163280838</t>
+  </si>
+  <si>
+    <t>Serverless 中文社区采访</t>
+  </si>
+  <si>
+    <t>2020-06-24</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/150510751</t>
+  </si>
+  <si>
+    <t>SVG 菜鸟的 Recharts 自定义图表实战</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/122477905</t>
+  </si>
+  <si>
+    <t>十分钟了解git那些“不常用”命令</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/122474549</t>
+  </si>
+  <si>
+    <t>nohost — 远程环境配置及抓包调试最佳实践</t>
+  </si>
+  <si>
+    <t>2019-12-27</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/99811711</t>
+  </si>
+  <si>
+    <t>企鹅辅导H5直播点播实践</t>
+  </si>
+  <si>
+    <t>2019-10-30</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/89301347</t>
+  </si>
+  <si>
+    <t>【TWeb前端盛会】腾讯前端技术大会，11月16日重磅来袭！</t>
+  </si>
+  <si>
+    <t>2019-10-16</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/86939486</t>
   </si>
 </sst>
 </file>
@@ -519,6 +3395,4694 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E281"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" t="s">
+        <v>93</v>
+      </c>
+      <c r="E27" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>95</v>
+      </c>
+      <c r="B28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" t="s">
+        <v>96</v>
+      </c>
+      <c r="E28" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" t="s">
+        <v>99</v>
+      </c>
+      <c r="E29" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>101</v>
+      </c>
+      <c r="B30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" t="s">
+        <v>102</v>
+      </c>
+      <c r="E30" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>104</v>
+      </c>
+      <c r="B31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" t="s">
+        <v>105</v>
+      </c>
+      <c r="E31" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" t="s">
+        <v>108</v>
+      </c>
+      <c r="E32" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>110</v>
+      </c>
+      <c r="B33" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" t="s">
+        <v>111</v>
+      </c>
+      <c r="E33" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>113</v>
+      </c>
+      <c r="B34" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" t="s">
+        <v>114</v>
+      </c>
+      <c r="E34" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>116</v>
+      </c>
+      <c r="B35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35" t="s">
+        <v>117</v>
+      </c>
+      <c r="E35" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>119</v>
+      </c>
+      <c r="B36" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" t="s">
+        <v>120</v>
+      </c>
+      <c r="E36" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>122</v>
+      </c>
+      <c r="B37" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" t="s">
+        <v>123</v>
+      </c>
+      <c r="E37" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>125</v>
+      </c>
+      <c r="B38" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38" t="s">
+        <v>126</v>
+      </c>
+      <c r="E38" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>128</v>
+      </c>
+      <c r="B39" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39" t="s">
+        <v>129</v>
+      </c>
+      <c r="E39" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>131</v>
+      </c>
+      <c r="B40" t="s">
+        <v>47</v>
+      </c>
+      <c r="C40" t="s">
+        <v>132</v>
+      </c>
+      <c r="E40" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>134</v>
+      </c>
+      <c r="B41" t="s">
+        <v>47</v>
+      </c>
+      <c r="C41" t="s">
+        <v>135</v>
+      </c>
+      <c r="E41" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>137</v>
+      </c>
+      <c r="B42" t="s">
+        <v>47</v>
+      </c>
+      <c r="C42" t="s">
+        <v>138</v>
+      </c>
+      <c r="E42" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>140</v>
+      </c>
+      <c r="B43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C43" t="s">
+        <v>141</v>
+      </c>
+      <c r="E43" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>143</v>
+      </c>
+      <c r="B44" t="s">
+        <v>47</v>
+      </c>
+      <c r="C44" t="s">
+        <v>144</v>
+      </c>
+      <c r="E44" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>146</v>
+      </c>
+      <c r="B45" t="s">
+        <v>47</v>
+      </c>
+      <c r="C45" t="s">
+        <v>147</v>
+      </c>
+      <c r="E45" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>149</v>
+      </c>
+      <c r="B46" t="s">
+        <v>47</v>
+      </c>
+      <c r="C46" t="s">
+        <v>150</v>
+      </c>
+      <c r="E46" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>152</v>
+      </c>
+      <c r="B47" t="s">
+        <v>47</v>
+      </c>
+      <c r="C47" t="s">
+        <v>153</v>
+      </c>
+      <c r="E47" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>155</v>
+      </c>
+      <c r="B48" t="s">
+        <v>47</v>
+      </c>
+      <c r="C48" t="s">
+        <v>156</v>
+      </c>
+      <c r="E48" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>158</v>
+      </c>
+      <c r="B49" t="s">
+        <v>47</v>
+      </c>
+      <c r="C49" t="s">
+        <v>159</v>
+      </c>
+      <c r="E49" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>161</v>
+      </c>
+      <c r="B50" t="s">
+        <v>47</v>
+      </c>
+      <c r="C50" t="s">
+        <v>162</v>
+      </c>
+      <c r="E50" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>164</v>
+      </c>
+      <c r="B51" t="s">
+        <v>47</v>
+      </c>
+      <c r="C51" t="s">
+        <v>165</v>
+      </c>
+      <c r="E51" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>167</v>
+      </c>
+      <c r="B52" t="s">
+        <v>47</v>
+      </c>
+      <c r="C52" t="s">
+        <v>168</v>
+      </c>
+      <c r="E52" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>170</v>
+      </c>
+      <c r="B53" t="s">
+        <v>47</v>
+      </c>
+      <c r="C53" t="s">
+        <v>171</v>
+      </c>
+      <c r="E53" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>173</v>
+      </c>
+      <c r="B54" t="s">
+        <v>47</v>
+      </c>
+      <c r="C54" t="s">
+        <v>174</v>
+      </c>
+      <c r="E54" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>176</v>
+      </c>
+      <c r="B55" t="s">
+        <v>47</v>
+      </c>
+      <c r="C55" t="s">
+        <v>177</v>
+      </c>
+      <c r="E55" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>179</v>
+      </c>
+      <c r="B56" t="s">
+        <v>47</v>
+      </c>
+      <c r="C56" t="s">
+        <v>180</v>
+      </c>
+      <c r="E56" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>182</v>
+      </c>
+      <c r="B57" t="s">
+        <v>47</v>
+      </c>
+      <c r="C57" t="s">
+        <v>183</v>
+      </c>
+      <c r="E57" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>185</v>
+      </c>
+      <c r="B58" t="s">
+        <v>47</v>
+      </c>
+      <c r="C58" t="s">
+        <v>186</v>
+      </c>
+      <c r="E58" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>188</v>
+      </c>
+      <c r="B59" t="s">
+        <v>47</v>
+      </c>
+      <c r="C59" t="s">
+        <v>189</v>
+      </c>
+      <c r="E59" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>191</v>
+      </c>
+      <c r="B60" t="s">
+        <v>47</v>
+      </c>
+      <c r="C60" t="s">
+        <v>192</v>
+      </c>
+      <c r="E60" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>194</v>
+      </c>
+      <c r="B61" t="s">
+        <v>47</v>
+      </c>
+      <c r="C61" t="s">
+        <v>195</v>
+      </c>
+      <c r="E61" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>197</v>
+      </c>
+      <c r="B62" t="s">
+        <v>47</v>
+      </c>
+      <c r="C62" t="s">
+        <v>198</v>
+      </c>
+      <c r="E62" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>200</v>
+      </c>
+      <c r="B63" t="s">
+        <v>47</v>
+      </c>
+      <c r="C63" t="s">
+        <v>201</v>
+      </c>
+      <c r="E63" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>203</v>
+      </c>
+      <c r="B64" t="s">
+        <v>47</v>
+      </c>
+      <c r="C64" t="s">
+        <v>204</v>
+      </c>
+      <c r="E64" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>206</v>
+      </c>
+      <c r="B65" t="s">
+        <v>47</v>
+      </c>
+      <c r="C65" t="s">
+        <v>207</v>
+      </c>
+      <c r="E65" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>209</v>
+      </c>
+      <c r="B66" t="s">
+        <v>47</v>
+      </c>
+      <c r="C66" t="s">
+        <v>210</v>
+      </c>
+      <c r="E66" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>212</v>
+      </c>
+      <c r="B67" t="s">
+        <v>47</v>
+      </c>
+      <c r="C67" t="s">
+        <v>213</v>
+      </c>
+      <c r="E67" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>215</v>
+      </c>
+      <c r="B68" t="s">
+        <v>47</v>
+      </c>
+      <c r="C68" t="s">
+        <v>216</v>
+      </c>
+      <c r="E68" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>218</v>
+      </c>
+      <c r="B69" t="s">
+        <v>47</v>
+      </c>
+      <c r="C69" t="s">
+        <v>219</v>
+      </c>
+      <c r="E69" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>221</v>
+      </c>
+      <c r="B70" t="s">
+        <v>47</v>
+      </c>
+      <c r="C70" t="s">
+        <v>222</v>
+      </c>
+      <c r="E70" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>224</v>
+      </c>
+      <c r="B71" t="s">
+        <v>47</v>
+      </c>
+      <c r="C71" t="s">
+        <v>225</v>
+      </c>
+      <c r="E71" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>227</v>
+      </c>
+      <c r="B72" t="s">
+        <v>47</v>
+      </c>
+      <c r="C72" t="s">
+        <v>228</v>
+      </c>
+      <c r="E72" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>230</v>
+      </c>
+      <c r="B73" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" t="s">
+        <v>231</v>
+      </c>
+      <c r="E73" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>233</v>
+      </c>
+      <c r="B74" t="s">
+        <v>47</v>
+      </c>
+      <c r="C74" t="s">
+        <v>234</v>
+      </c>
+      <c r="E74" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>236</v>
+      </c>
+      <c r="B75" t="s">
+        <v>47</v>
+      </c>
+      <c r="C75" t="s">
+        <v>237</v>
+      </c>
+      <c r="E75" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>239</v>
+      </c>
+      <c r="B76" t="s">
+        <v>47</v>
+      </c>
+      <c r="C76" t="s">
+        <v>240</v>
+      </c>
+      <c r="E76" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>242</v>
+      </c>
+      <c r="B77" t="s">
+        <v>47</v>
+      </c>
+      <c r="C77" t="s">
+        <v>243</v>
+      </c>
+      <c r="E77" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>245</v>
+      </c>
+      <c r="B78" t="s">
+        <v>47</v>
+      </c>
+      <c r="C78" t="s">
+        <v>246</v>
+      </c>
+      <c r="E78" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>248</v>
+      </c>
+      <c r="B79" t="s">
+        <v>47</v>
+      </c>
+      <c r="C79" t="s">
+        <v>249</v>
+      </c>
+      <c r="E79" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>251</v>
+      </c>
+      <c r="B80" t="s">
+        <v>47</v>
+      </c>
+      <c r="C80" t="s">
+        <v>252</v>
+      </c>
+      <c r="E80" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>254</v>
+      </c>
+      <c r="B81" t="s">
+        <v>47</v>
+      </c>
+      <c r="C81" t="s">
+        <v>255</v>
+      </c>
+      <c r="E81" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>257</v>
+      </c>
+      <c r="B82" t="s">
+        <v>47</v>
+      </c>
+      <c r="C82" t="s">
+        <v>258</v>
+      </c>
+      <c r="E82" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>260</v>
+      </c>
+      <c r="B83" t="s">
+        <v>47</v>
+      </c>
+      <c r="C83" t="s">
+        <v>261</v>
+      </c>
+      <c r="E83" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>263</v>
+      </c>
+      <c r="B84" t="s">
+        <v>47</v>
+      </c>
+      <c r="C84" t="s">
+        <v>264</v>
+      </c>
+      <c r="E84" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>266</v>
+      </c>
+      <c r="B85" t="s">
+        <v>47</v>
+      </c>
+      <c r="C85" t="s">
+        <v>267</v>
+      </c>
+      <c r="E85" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>269</v>
+      </c>
+      <c r="B86" t="s">
+        <v>47</v>
+      </c>
+      <c r="C86" t="s">
+        <v>270</v>
+      </c>
+      <c r="E86" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>272</v>
+      </c>
+      <c r="B87" t="s">
+        <v>47</v>
+      </c>
+      <c r="C87" t="s">
+        <v>273</v>
+      </c>
+      <c r="E87" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>275</v>
+      </c>
+      <c r="B88" t="s">
+        <v>47</v>
+      </c>
+      <c r="C88" t="s">
+        <v>276</v>
+      </c>
+      <c r="E88" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>278</v>
+      </c>
+      <c r="B89" t="s">
+        <v>47</v>
+      </c>
+      <c r="C89" t="s">
+        <v>279</v>
+      </c>
+      <c r="E89" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>281</v>
+      </c>
+      <c r="B90" t="s">
+        <v>47</v>
+      </c>
+      <c r="C90" t="s">
+        <v>279</v>
+      </c>
+      <c r="E90" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>283</v>
+      </c>
+      <c r="B91" t="s">
+        <v>47</v>
+      </c>
+      <c r="C91" t="s">
+        <v>284</v>
+      </c>
+      <c r="E91" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>286</v>
+      </c>
+      <c r="B92" t="s">
+        <v>47</v>
+      </c>
+      <c r="C92" t="s">
+        <v>287</v>
+      </c>
+      <c r="E92" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>289</v>
+      </c>
+      <c r="B93" t="s">
+        <v>47</v>
+      </c>
+      <c r="C93" t="s">
+        <v>290</v>
+      </c>
+      <c r="E93" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>292</v>
+      </c>
+      <c r="B94" t="s">
+        <v>47</v>
+      </c>
+      <c r="C94" t="s">
+        <v>293</v>
+      </c>
+      <c r="E94" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>295</v>
+      </c>
+      <c r="B95" t="s">
+        <v>47</v>
+      </c>
+      <c r="C95" t="s">
+        <v>296</v>
+      </c>
+      <c r="E95" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>298</v>
+      </c>
+      <c r="B96" t="s">
+        <v>47</v>
+      </c>
+      <c r="C96" t="s">
+        <v>299</v>
+      </c>
+      <c r="E96" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>301</v>
+      </c>
+      <c r="B97" t="s">
+        <v>47</v>
+      </c>
+      <c r="C97" t="s">
+        <v>302</v>
+      </c>
+      <c r="E97" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>304</v>
+      </c>
+      <c r="B98" t="s">
+        <v>47</v>
+      </c>
+      <c r="C98" t="s">
+        <v>305</v>
+      </c>
+      <c r="E98" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>307</v>
+      </c>
+      <c r="B99" t="s">
+        <v>47</v>
+      </c>
+      <c r="C99" t="s">
+        <v>308</v>
+      </c>
+      <c r="E99" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>310</v>
+      </c>
+      <c r="B100" t="s">
+        <v>47</v>
+      </c>
+      <c r="C100" t="s">
+        <v>311</v>
+      </c>
+      <c r="E100" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>313</v>
+      </c>
+      <c r="B101" t="s">
+        <v>47</v>
+      </c>
+      <c r="C101" t="s">
+        <v>314</v>
+      </c>
+      <c r="E101" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>316</v>
+      </c>
+      <c r="B102" t="s">
+        <v>47</v>
+      </c>
+      <c r="C102" t="s">
+        <v>317</v>
+      </c>
+      <c r="E102" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>319</v>
+      </c>
+      <c r="B103" t="s">
+        <v>47</v>
+      </c>
+      <c r="C103" t="s">
+        <v>320</v>
+      </c>
+      <c r="E103" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>322</v>
+      </c>
+      <c r="B104" t="s">
+        <v>47</v>
+      </c>
+      <c r="C104" t="s">
+        <v>323</v>
+      </c>
+      <c r="E104" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>325</v>
+      </c>
+      <c r="B105" t="s">
+        <v>47</v>
+      </c>
+      <c r="C105" t="s">
+        <v>326</v>
+      </c>
+      <c r="E105" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>328</v>
+      </c>
+      <c r="B106" t="s">
+        <v>47</v>
+      </c>
+      <c r="C106" t="s">
+        <v>329</v>
+      </c>
+      <c r="E106" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>331</v>
+      </c>
+      <c r="B107" t="s">
+        <v>47</v>
+      </c>
+      <c r="C107" t="s">
+        <v>332</v>
+      </c>
+      <c r="E107" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>334</v>
+      </c>
+      <c r="B108" t="s">
+        <v>47</v>
+      </c>
+      <c r="C108" t="s">
+        <v>335</v>
+      </c>
+      <c r="E108" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>337</v>
+      </c>
+      <c r="B109" t="s">
+        <v>47</v>
+      </c>
+      <c r="C109" t="s">
+        <v>338</v>
+      </c>
+      <c r="E109" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>340</v>
+      </c>
+      <c r="B110" t="s">
+        <v>47</v>
+      </c>
+      <c r="C110" t="s">
+        <v>341</v>
+      </c>
+      <c r="E110" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>343</v>
+      </c>
+      <c r="B111" t="s">
+        <v>47</v>
+      </c>
+      <c r="C111" t="s">
+        <v>344</v>
+      </c>
+      <c r="E111" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>346</v>
+      </c>
+      <c r="B112" t="s">
+        <v>47</v>
+      </c>
+      <c r="C112" t="s">
+        <v>347</v>
+      </c>
+      <c r="E112" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>349</v>
+      </c>
+      <c r="B113" t="s">
+        <v>47</v>
+      </c>
+      <c r="C113" t="s">
+        <v>350</v>
+      </c>
+      <c r="E113" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>352</v>
+      </c>
+      <c r="B114" t="s">
+        <v>47</v>
+      </c>
+      <c r="C114" t="s">
+        <v>353</v>
+      </c>
+      <c r="E114" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>355</v>
+      </c>
+      <c r="B115" t="s">
+        <v>47</v>
+      </c>
+      <c r="C115" t="s">
+        <v>356</v>
+      </c>
+      <c r="E115" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>358</v>
+      </c>
+      <c r="B116" t="s">
+        <v>47</v>
+      </c>
+      <c r="C116" t="s">
+        <v>359</v>
+      </c>
+      <c r="E116" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>361</v>
+      </c>
+      <c r="B117" t="s">
+        <v>47</v>
+      </c>
+      <c r="C117" t="s">
+        <v>362</v>
+      </c>
+      <c r="E117" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>364</v>
+      </c>
+      <c r="B118" t="s">
+        <v>47</v>
+      </c>
+      <c r="C118" t="s">
+        <v>365</v>
+      </c>
+      <c r="E118" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>367</v>
+      </c>
+      <c r="B119" t="s">
+        <v>47</v>
+      </c>
+      <c r="C119" t="s">
+        <v>368</v>
+      </c>
+      <c r="E119" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>370</v>
+      </c>
+      <c r="B120" t="s">
+        <v>47</v>
+      </c>
+      <c r="C120" t="s">
+        <v>371</v>
+      </c>
+      <c r="E120" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>373</v>
+      </c>
+      <c r="B121" t="s">
+        <v>47</v>
+      </c>
+      <c r="C121" t="s">
+        <v>374</v>
+      </c>
+      <c r="E121" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>376</v>
+      </c>
+      <c r="B122" t="s">
+        <v>47</v>
+      </c>
+      <c r="C122" t="s">
+        <v>377</v>
+      </c>
+      <c r="E122" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>379</v>
+      </c>
+      <c r="B123" t="s">
+        <v>47</v>
+      </c>
+      <c r="C123" t="s">
+        <v>380</v>
+      </c>
+      <c r="E123" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>382</v>
+      </c>
+      <c r="B124" t="s">
+        <v>47</v>
+      </c>
+      <c r="C124" t="s">
+        <v>383</v>
+      </c>
+      <c r="E124" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>385</v>
+      </c>
+      <c r="B125" t="s">
+        <v>47</v>
+      </c>
+      <c r="C125" t="s">
+        <v>386</v>
+      </c>
+      <c r="E125" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>388</v>
+      </c>
+      <c r="B126" t="s">
+        <v>47</v>
+      </c>
+      <c r="C126" t="s">
+        <v>389</v>
+      </c>
+      <c r="E126" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>391</v>
+      </c>
+      <c r="B127" t="s">
+        <v>47</v>
+      </c>
+      <c r="C127" t="s">
+        <v>392</v>
+      </c>
+      <c r="E127" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>394</v>
+      </c>
+      <c r="B128" t="s">
+        <v>47</v>
+      </c>
+      <c r="C128" t="s">
+        <v>395</v>
+      </c>
+      <c r="E128" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>397</v>
+      </c>
+      <c r="B129" t="s">
+        <v>47</v>
+      </c>
+      <c r="C129" t="s">
+        <v>398</v>
+      </c>
+      <c r="E129" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>400</v>
+      </c>
+      <c r="B130" t="s">
+        <v>47</v>
+      </c>
+      <c r="C130" t="s">
+        <v>401</v>
+      </c>
+      <c r="E130" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>403</v>
+      </c>
+      <c r="B131" t="s">
+        <v>47</v>
+      </c>
+      <c r="C131" t="s">
+        <v>404</v>
+      </c>
+      <c r="E131" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>406</v>
+      </c>
+      <c r="B132" t="s">
+        <v>47</v>
+      </c>
+      <c r="C132" t="s">
+        <v>407</v>
+      </c>
+      <c r="E132" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>409</v>
+      </c>
+      <c r="B133" t="s">
+        <v>47</v>
+      </c>
+      <c r="C133" t="s">
+        <v>410</v>
+      </c>
+      <c r="E133" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>412</v>
+      </c>
+      <c r="B134" t="s">
+        <v>47</v>
+      </c>
+      <c r="C134" t="s">
+        <v>413</v>
+      </c>
+      <c r="E134" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>415</v>
+      </c>
+      <c r="B135" t="s">
+        <v>47</v>
+      </c>
+      <c r="C135" t="s">
+        <v>416</v>
+      </c>
+      <c r="E135" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>418</v>
+      </c>
+      <c r="B136" t="s">
+        <v>47</v>
+      </c>
+      <c r="C136" t="s">
+        <v>419</v>
+      </c>
+      <c r="E136" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>421</v>
+      </c>
+      <c r="B137" t="s">
+        <v>47</v>
+      </c>
+      <c r="C137" t="s">
+        <v>422</v>
+      </c>
+      <c r="E137" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>424</v>
+      </c>
+      <c r="B138" t="s">
+        <v>47</v>
+      </c>
+      <c r="C138" t="s">
+        <v>425</v>
+      </c>
+      <c r="E138" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>427</v>
+      </c>
+      <c r="B139" t="s">
+        <v>47</v>
+      </c>
+      <c r="C139" t="s">
+        <v>428</v>
+      </c>
+      <c r="E139" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>430</v>
+      </c>
+      <c r="B140" t="s">
+        <v>47</v>
+      </c>
+      <c r="C140" t="s">
+        <v>431</v>
+      </c>
+      <c r="E140" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>433</v>
+      </c>
+      <c r="B141" t="s">
+        <v>47</v>
+      </c>
+      <c r="C141" t="s">
+        <v>434</v>
+      </c>
+      <c r="E141" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>436</v>
+      </c>
+      <c r="B142" t="s">
+        <v>47</v>
+      </c>
+      <c r="C142" t="s">
+        <v>437</v>
+      </c>
+      <c r="E142" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>439</v>
+      </c>
+      <c r="B143" t="s">
+        <v>47</v>
+      </c>
+      <c r="C143" t="s">
+        <v>440</v>
+      </c>
+      <c r="E143" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>442</v>
+      </c>
+      <c r="B144" t="s">
+        <v>47</v>
+      </c>
+      <c r="C144" t="s">
+        <v>443</v>
+      </c>
+      <c r="E144" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>445</v>
+      </c>
+      <c r="B145" t="s">
+        <v>47</v>
+      </c>
+      <c r="C145" t="s">
+        <v>446</v>
+      </c>
+      <c r="E145" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>448</v>
+      </c>
+      <c r="B146" t="s">
+        <v>47</v>
+      </c>
+      <c r="C146" t="s">
+        <v>449</v>
+      </c>
+      <c r="E146" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>451</v>
+      </c>
+      <c r="B147" t="s">
+        <v>47</v>
+      </c>
+      <c r="C147" t="s">
+        <v>452</v>
+      </c>
+      <c r="E147" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>454</v>
+      </c>
+      <c r="B148" t="s">
+        <v>47</v>
+      </c>
+      <c r="C148" t="s">
+        <v>455</v>
+      </c>
+      <c r="E148" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>457</v>
+      </c>
+      <c r="B149" t="s">
+        <v>47</v>
+      </c>
+      <c r="C149" t="s">
+        <v>458</v>
+      </c>
+      <c r="E149" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>460</v>
+      </c>
+      <c r="B150" t="s">
+        <v>47</v>
+      </c>
+      <c r="C150" t="s">
+        <v>461</v>
+      </c>
+      <c r="E150" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>463</v>
+      </c>
+      <c r="B151" t="s">
+        <v>47</v>
+      </c>
+      <c r="C151" t="s">
+        <v>464</v>
+      </c>
+      <c r="E151" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>466</v>
+      </c>
+      <c r="B152" t="s">
+        <v>47</v>
+      </c>
+      <c r="C152" t="s">
+        <v>467</v>
+      </c>
+      <c r="E152" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>469</v>
+      </c>
+      <c r="B153" t="s">
+        <v>47</v>
+      </c>
+      <c r="C153" t="s">
+        <v>470</v>
+      </c>
+      <c r="E153" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>472</v>
+      </c>
+      <c r="B154" t="s">
+        <v>473</v>
+      </c>
+      <c r="C154" t="s">
+        <v>474</v>
+      </c>
+      <c r="E154" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>476</v>
+      </c>
+      <c r="B155" t="s">
+        <v>473</v>
+      </c>
+      <c r="C155" t="s">
+        <v>477</v>
+      </c>
+      <c r="E155" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>479</v>
+      </c>
+      <c r="B156" t="s">
+        <v>473</v>
+      </c>
+      <c r="C156" t="s">
+        <v>480</v>
+      </c>
+      <c r="E156" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>482</v>
+      </c>
+      <c r="B157" t="s">
+        <v>473</v>
+      </c>
+      <c r="C157" t="s">
+        <v>483</v>
+      </c>
+      <c r="E157" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>485</v>
+      </c>
+      <c r="B158" t="s">
+        <v>473</v>
+      </c>
+      <c r="C158" t="s">
+        <v>486</v>
+      </c>
+      <c r="E158" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>488</v>
+      </c>
+      <c r="B159" t="s">
+        <v>473</v>
+      </c>
+      <c r="C159" t="s">
+        <v>489</v>
+      </c>
+      <c r="E159" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>491</v>
+      </c>
+      <c r="B160" t="s">
+        <v>473</v>
+      </c>
+      <c r="C160" t="s">
+        <v>492</v>
+      </c>
+      <c r="E160" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>494</v>
+      </c>
+      <c r="B161" t="s">
+        <v>473</v>
+      </c>
+      <c r="C161" t="s">
+        <v>495</v>
+      </c>
+      <c r="E161" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>497</v>
+      </c>
+      <c r="B162" t="s">
+        <v>473</v>
+      </c>
+      <c r="C162" t="s">
+        <v>498</v>
+      </c>
+      <c r="E162" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>500</v>
+      </c>
+      <c r="B163" t="s">
+        <v>473</v>
+      </c>
+      <c r="C163" t="s">
+        <v>501</v>
+      </c>
+      <c r="E163" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>503</v>
+      </c>
+      <c r="B164" t="s">
+        <v>473</v>
+      </c>
+      <c r="C164" t="s">
+        <v>504</v>
+      </c>
+      <c r="E164" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>506</v>
+      </c>
+      <c r="B165" t="s">
+        <v>473</v>
+      </c>
+      <c r="C165" t="s">
+        <v>507</v>
+      </c>
+      <c r="E165" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>509</v>
+      </c>
+      <c r="B166" t="s">
+        <v>473</v>
+      </c>
+      <c r="C166" t="s">
+        <v>510</v>
+      </c>
+      <c r="E166" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>512</v>
+      </c>
+      <c r="B167" t="s">
+        <v>473</v>
+      </c>
+      <c r="C167" t="s">
+        <v>513</v>
+      </c>
+      <c r="E167" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>515</v>
+      </c>
+      <c r="B168" t="s">
+        <v>473</v>
+      </c>
+      <c r="C168" t="s">
+        <v>516</v>
+      </c>
+      <c r="E168" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>518</v>
+      </c>
+      <c r="B169" t="s">
+        <v>473</v>
+      </c>
+      <c r="C169" t="s">
+        <v>519</v>
+      </c>
+      <c r="E169" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>521</v>
+      </c>
+      <c r="B170" t="s">
+        <v>473</v>
+      </c>
+      <c r="C170" t="s">
+        <v>522</v>
+      </c>
+      <c r="E170" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>524</v>
+      </c>
+      <c r="B171" t="s">
+        <v>473</v>
+      </c>
+      <c r="C171" t="s">
+        <v>525</v>
+      </c>
+      <c r="E171" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>527</v>
+      </c>
+      <c r="B172" t="s">
+        <v>473</v>
+      </c>
+      <c r="C172" t="s">
+        <v>528</v>
+      </c>
+      <c r="E172" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>530</v>
+      </c>
+      <c r="B173" t="s">
+        <v>473</v>
+      </c>
+      <c r="C173" t="s">
+        <v>531</v>
+      </c>
+      <c r="E173" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>533</v>
+      </c>
+      <c r="B174" t="s">
+        <v>473</v>
+      </c>
+      <c r="C174" t="s">
+        <v>534</v>
+      </c>
+      <c r="E174" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>536</v>
+      </c>
+      <c r="B175" t="s">
+        <v>473</v>
+      </c>
+      <c r="C175" t="s">
+        <v>537</v>
+      </c>
+      <c r="E175" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>539</v>
+      </c>
+      <c r="B176" t="s">
+        <v>473</v>
+      </c>
+      <c r="C176" t="s">
+        <v>540</v>
+      </c>
+      <c r="E176" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>542</v>
+      </c>
+      <c r="B177" t="s">
+        <v>473</v>
+      </c>
+      <c r="C177" t="s">
+        <v>543</v>
+      </c>
+      <c r="E177" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>545</v>
+      </c>
+      <c r="B178" t="s">
+        <v>473</v>
+      </c>
+      <c r="C178" t="s">
+        <v>546</v>
+      </c>
+      <c r="E178" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>548</v>
+      </c>
+      <c r="B179" t="s">
+        <v>473</v>
+      </c>
+      <c r="C179" t="s">
+        <v>549</v>
+      </c>
+      <c r="E179" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>551</v>
+      </c>
+      <c r="B180" t="s">
+        <v>473</v>
+      </c>
+      <c r="C180" t="s">
+        <v>552</v>
+      </c>
+      <c r="E180" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>554</v>
+      </c>
+      <c r="B181" t="s">
+        <v>473</v>
+      </c>
+      <c r="C181" t="s">
+        <v>555</v>
+      </c>
+      <c r="E181" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>557</v>
+      </c>
+      <c r="B182" t="s">
+        <v>473</v>
+      </c>
+      <c r="C182" t="s">
+        <v>558</v>
+      </c>
+      <c r="E182" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>560</v>
+      </c>
+      <c r="B183" t="s">
+        <v>473</v>
+      </c>
+      <c r="C183" t="s">
+        <v>561</v>
+      </c>
+      <c r="E183" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>563</v>
+      </c>
+      <c r="B184" t="s">
+        <v>473</v>
+      </c>
+      <c r="C184" t="s">
+        <v>564</v>
+      </c>
+      <c r="E184" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>566</v>
+      </c>
+      <c r="B185" t="s">
+        <v>473</v>
+      </c>
+      <c r="C185" t="s">
+        <v>567</v>
+      </c>
+      <c r="E185" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>569</v>
+      </c>
+      <c r="B186" t="s">
+        <v>473</v>
+      </c>
+      <c r="C186" t="s">
+        <v>570</v>
+      </c>
+      <c r="E186" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>572</v>
+      </c>
+      <c r="B187" t="s">
+        <v>473</v>
+      </c>
+      <c r="C187" t="s">
+        <v>573</v>
+      </c>
+      <c r="E187" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>575</v>
+      </c>
+      <c r="B188" t="s">
+        <v>473</v>
+      </c>
+      <c r="C188" t="s">
+        <v>576</v>
+      </c>
+      <c r="E188" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>578</v>
+      </c>
+      <c r="B189" t="s">
+        <v>473</v>
+      </c>
+      <c r="C189" t="s">
+        <v>579</v>
+      </c>
+      <c r="E189" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>581</v>
+      </c>
+      <c r="B190" t="s">
+        <v>473</v>
+      </c>
+      <c r="C190" t="s">
+        <v>582</v>
+      </c>
+      <c r="E190" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>584</v>
+      </c>
+      <c r="B191" t="s">
+        <v>473</v>
+      </c>
+      <c r="C191" t="s">
+        <v>585</v>
+      </c>
+      <c r="E191" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>587</v>
+      </c>
+      <c r="B192" t="s">
+        <v>473</v>
+      </c>
+      <c r="C192" t="s">
+        <v>588</v>
+      </c>
+      <c r="E192" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>590</v>
+      </c>
+      <c r="B193" t="s">
+        <v>473</v>
+      </c>
+      <c r="C193" t="s">
+        <v>591</v>
+      </c>
+      <c r="E193" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>593</v>
+      </c>
+      <c r="B194" t="s">
+        <v>473</v>
+      </c>
+      <c r="C194" t="s">
+        <v>594</v>
+      </c>
+      <c r="E194" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>596</v>
+      </c>
+      <c r="B195" t="s">
+        <v>473</v>
+      </c>
+      <c r="C195" t="s">
+        <v>597</v>
+      </c>
+      <c r="E195" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>599</v>
+      </c>
+      <c r="B196" t="s">
+        <v>473</v>
+      </c>
+      <c r="C196" t="s">
+        <v>600</v>
+      </c>
+      <c r="E196" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>602</v>
+      </c>
+      <c r="B197" t="s">
+        <v>473</v>
+      </c>
+      <c r="C197" t="s">
+        <v>603</v>
+      </c>
+      <c r="E197" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>605</v>
+      </c>
+      <c r="B198" t="s">
+        <v>473</v>
+      </c>
+      <c r="C198" t="s">
+        <v>606</v>
+      </c>
+      <c r="E198" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>608</v>
+      </c>
+      <c r="B199" t="s">
+        <v>473</v>
+      </c>
+      <c r="C199" t="s">
+        <v>609</v>
+      </c>
+      <c r="E199" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>611</v>
+      </c>
+      <c r="B200" t="s">
+        <v>473</v>
+      </c>
+      <c r="C200" t="s">
+        <v>612</v>
+      </c>
+      <c r="E200" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>614</v>
+      </c>
+      <c r="B201" t="s">
+        <v>473</v>
+      </c>
+      <c r="C201" t="s">
+        <v>615</v>
+      </c>
+      <c r="E201" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>617</v>
+      </c>
+      <c r="B202" t="s">
+        <v>473</v>
+      </c>
+      <c r="C202" t="s">
+        <v>618</v>
+      </c>
+      <c r="E202" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>620</v>
+      </c>
+      <c r="B203" t="s">
+        <v>473</v>
+      </c>
+      <c r="C203" t="s">
+        <v>621</v>
+      </c>
+      <c r="E203" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>623</v>
+      </c>
+      <c r="B204" t="s">
+        <v>473</v>
+      </c>
+      <c r="C204" t="s">
+        <v>624</v>
+      </c>
+      <c r="E204" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>626</v>
+      </c>
+      <c r="B205" t="s">
+        <v>473</v>
+      </c>
+      <c r="C205" t="s">
+        <v>627</v>
+      </c>
+      <c r="E205" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>629</v>
+      </c>
+      <c r="B206" t="s">
+        <v>473</v>
+      </c>
+      <c r="C206" t="s">
+        <v>630</v>
+      </c>
+      <c r="E206" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>632</v>
+      </c>
+      <c r="B207" t="s">
+        <v>473</v>
+      </c>
+      <c r="C207" t="s">
+        <v>633</v>
+      </c>
+      <c r="E207" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>635</v>
+      </c>
+      <c r="B208" t="s">
+        <v>473</v>
+      </c>
+      <c r="C208" t="s">
+        <v>636</v>
+      </c>
+      <c r="E208" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>638</v>
+      </c>
+      <c r="B209" t="s">
+        <v>473</v>
+      </c>
+      <c r="C209" t="s">
+        <v>639</v>
+      </c>
+      <c r="E209" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>641</v>
+      </c>
+      <c r="B210" t="s">
+        <v>473</v>
+      </c>
+      <c r="C210" t="s">
+        <v>642</v>
+      </c>
+      <c r="E210" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>644</v>
+      </c>
+      <c r="B211" t="s">
+        <v>473</v>
+      </c>
+      <c r="C211" t="s">
+        <v>645</v>
+      </c>
+      <c r="E211" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>647</v>
+      </c>
+      <c r="B212" t="s">
+        <v>473</v>
+      </c>
+      <c r="C212" t="s">
+        <v>111</v>
+      </c>
+      <c r="E212" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>649</v>
+      </c>
+      <c r="B213" t="s">
+        <v>473</v>
+      </c>
+      <c r="C213" t="s">
+        <v>650</v>
+      </c>
+      <c r="E213" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>652</v>
+      </c>
+      <c r="B214" t="s">
+        <v>473</v>
+      </c>
+      <c r="C214" t="s">
+        <v>114</v>
+      </c>
+      <c r="E214" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>654</v>
+      </c>
+      <c r="B215" t="s">
+        <v>473</v>
+      </c>
+      <c r="C215" t="s">
+        <v>655</v>
+      </c>
+      <c r="E215" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>657</v>
+      </c>
+      <c r="B216" t="s">
+        <v>473</v>
+      </c>
+      <c r="C216" t="s">
+        <v>658</v>
+      </c>
+      <c r="E216" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>660</v>
+      </c>
+      <c r="B217" t="s">
+        <v>473</v>
+      </c>
+      <c r="C217" t="s">
+        <v>661</v>
+      </c>
+      <c r="E217" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>663</v>
+      </c>
+      <c r="B218" t="s">
+        <v>473</v>
+      </c>
+      <c r="C218" t="s">
+        <v>664</v>
+      </c>
+      <c r="E218" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>666</v>
+      </c>
+      <c r="B219" t="s">
+        <v>473</v>
+      </c>
+      <c r="C219" t="s">
+        <v>667</v>
+      </c>
+      <c r="E219" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>669</v>
+      </c>
+      <c r="B220" t="s">
+        <v>473</v>
+      </c>
+      <c r="C220" t="s">
+        <v>670</v>
+      </c>
+      <c r="E220" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>672</v>
+      </c>
+      <c r="B221" t="s">
+        <v>473</v>
+      </c>
+      <c r="C221" t="s">
+        <v>673</v>
+      </c>
+      <c r="E221" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>675</v>
+      </c>
+      <c r="B222" t="s">
+        <v>473</v>
+      </c>
+      <c r="C222" t="s">
+        <v>676</v>
+      </c>
+      <c r="E222" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>678</v>
+      </c>
+      <c r="B223" t="s">
+        <v>473</v>
+      </c>
+      <c r="C223" t="s">
+        <v>679</v>
+      </c>
+      <c r="E223" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>681</v>
+      </c>
+      <c r="B224" t="s">
+        <v>473</v>
+      </c>
+      <c r="C224" t="s">
+        <v>682</v>
+      </c>
+      <c r="E224" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>684</v>
+      </c>
+      <c r="B225" t="s">
+        <v>473</v>
+      </c>
+      <c r="C225" t="s">
+        <v>685</v>
+      </c>
+      <c r="E225" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>687</v>
+      </c>
+      <c r="B226" t="s">
+        <v>473</v>
+      </c>
+      <c r="C226" t="s">
+        <v>688</v>
+      </c>
+      <c r="E226" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>690</v>
+      </c>
+      <c r="B227" t="s">
+        <v>473</v>
+      </c>
+      <c r="C227" t="s">
+        <v>691</v>
+      </c>
+      <c r="E227" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>693</v>
+      </c>
+      <c r="B228" t="s">
+        <v>473</v>
+      </c>
+      <c r="C228" t="s">
+        <v>694</v>
+      </c>
+      <c r="E228" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>696</v>
+      </c>
+      <c r="B229" t="s">
+        <v>473</v>
+      </c>
+      <c r="C229" t="s">
+        <v>697</v>
+      </c>
+      <c r="E229" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>699</v>
+      </c>
+      <c r="B230" t="s">
+        <v>473</v>
+      </c>
+      <c r="C230" t="s">
+        <v>700</v>
+      </c>
+      <c r="E230" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>702</v>
+      </c>
+      <c r="B231" t="s">
+        <v>473</v>
+      </c>
+      <c r="C231" t="s">
+        <v>703</v>
+      </c>
+      <c r="E231" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>705</v>
+      </c>
+      <c r="B232" t="s">
+        <v>473</v>
+      </c>
+      <c r="C232" t="s">
+        <v>706</v>
+      </c>
+      <c r="E232" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>708</v>
+      </c>
+      <c r="B233" t="s">
+        <v>473</v>
+      </c>
+      <c r="C233" t="s">
+        <v>709</v>
+      </c>
+      <c r="E233" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>711</v>
+      </c>
+      <c r="B234" t="s">
+        <v>473</v>
+      </c>
+      <c r="C234" t="s">
+        <v>712</v>
+      </c>
+      <c r="E234" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>714</v>
+      </c>
+      <c r="B235" t="s">
+        <v>473</v>
+      </c>
+      <c r="C235" t="s">
+        <v>715</v>
+      </c>
+      <c r="E235" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>717</v>
+      </c>
+      <c r="B236" t="s">
+        <v>473</v>
+      </c>
+      <c r="C236" t="s">
+        <v>718</v>
+      </c>
+      <c r="E236" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>720</v>
+      </c>
+      <c r="B237" t="s">
+        <v>473</v>
+      </c>
+      <c r="C237" t="s">
+        <v>721</v>
+      </c>
+      <c r="E237" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>723</v>
+      </c>
+      <c r="B238" t="s">
+        <v>473</v>
+      </c>
+      <c r="C238" t="s">
+        <v>724</v>
+      </c>
+      <c r="E238" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>726</v>
+      </c>
+      <c r="B239" t="s">
+        <v>473</v>
+      </c>
+      <c r="C239" t="s">
+        <v>727</v>
+      </c>
+      <c r="E239" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>729</v>
+      </c>
+      <c r="B240" t="s">
+        <v>473</v>
+      </c>
+      <c r="C240" t="s">
+        <v>730</v>
+      </c>
+      <c r="E240" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>732</v>
+      </c>
+      <c r="B241" t="s">
+        <v>473</v>
+      </c>
+      <c r="C241" t="s">
+        <v>733</v>
+      </c>
+      <c r="E241" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>735</v>
+      </c>
+      <c r="B242" t="s">
+        <v>473</v>
+      </c>
+      <c r="C242" t="s">
+        <v>736</v>
+      </c>
+      <c r="E242" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>738</v>
+      </c>
+      <c r="B243" t="s">
+        <v>473</v>
+      </c>
+      <c r="C243" t="s">
+        <v>739</v>
+      </c>
+      <c r="E243" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>741</v>
+      </c>
+      <c r="B244" t="s">
+        <v>473</v>
+      </c>
+      <c r="C244" t="s">
+        <v>742</v>
+      </c>
+      <c r="E244" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>744</v>
+      </c>
+      <c r="B245" t="s">
+        <v>473</v>
+      </c>
+      <c r="C245" t="s">
+        <v>745</v>
+      </c>
+      <c r="E245" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>747</v>
+      </c>
+      <c r="B246" t="s">
+        <v>473</v>
+      </c>
+      <c r="C246" t="s">
+        <v>748</v>
+      </c>
+      <c r="E246" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>750</v>
+      </c>
+      <c r="B247" t="s">
+        <v>473</v>
+      </c>
+      <c r="C247" t="s">
+        <v>751</v>
+      </c>
+      <c r="E247" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>753</v>
+      </c>
+      <c r="B248" t="s">
+        <v>473</v>
+      </c>
+      <c r="C248" t="s">
+        <v>754</v>
+      </c>
+      <c r="E248" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>756</v>
+      </c>
+      <c r="B249" t="s">
+        <v>473</v>
+      </c>
+      <c r="C249" t="s">
+        <v>757</v>
+      </c>
+      <c r="E249" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>759</v>
+      </c>
+      <c r="B250" t="s">
+        <v>473</v>
+      </c>
+      <c r="C250" t="s">
+        <v>760</v>
+      </c>
+      <c r="E250" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>762</v>
+      </c>
+      <c r="B251" t="s">
+        <v>473</v>
+      </c>
+      <c r="C251" t="s">
+        <v>763</v>
+      </c>
+      <c r="E251" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>765</v>
+      </c>
+      <c r="B252" t="s">
+        <v>473</v>
+      </c>
+      <c r="C252" t="s">
+        <v>766</v>
+      </c>
+      <c r="E252" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>768</v>
+      </c>
+      <c r="B253" t="s">
+        <v>473</v>
+      </c>
+      <c r="C253" t="s">
+        <v>769</v>
+      </c>
+      <c r="E253" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>771</v>
+      </c>
+      <c r="B254" t="s">
+        <v>473</v>
+      </c>
+      <c r="C254" t="s">
+        <v>772</v>
+      </c>
+      <c r="E254" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>774</v>
+      </c>
+      <c r="B255" t="s">
+        <v>473</v>
+      </c>
+      <c r="C255" t="s">
+        <v>775</v>
+      </c>
+      <c r="E255" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>777</v>
+      </c>
+      <c r="B256" t="s">
+        <v>473</v>
+      </c>
+      <c r="C256" t="s">
+        <v>778</v>
+      </c>
+      <c r="E256" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>780</v>
+      </c>
+      <c r="B257" t="s">
+        <v>473</v>
+      </c>
+      <c r="C257" t="s">
+        <v>781</v>
+      </c>
+      <c r="E257" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>783</v>
+      </c>
+      <c r="B258" t="s">
+        <v>473</v>
+      </c>
+      <c r="C258" t="s">
+        <v>784</v>
+      </c>
+      <c r="E258" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>786</v>
+      </c>
+      <c r="B259" t="s">
+        <v>473</v>
+      </c>
+      <c r="C259" t="s">
+        <v>784</v>
+      </c>
+      <c r="E259" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>788</v>
+      </c>
+      <c r="B260" t="s">
+        <v>473</v>
+      </c>
+      <c r="C260" t="s">
+        <v>789</v>
+      </c>
+      <c r="E260" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>791</v>
+      </c>
+      <c r="B261" t="s">
+        <v>473</v>
+      </c>
+      <c r="C261" t="s">
+        <v>792</v>
+      </c>
+      <c r="E261" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>794</v>
+      </c>
+      <c r="B262" t="s">
+        <v>473</v>
+      </c>
+      <c r="C262" t="s">
+        <v>795</v>
+      </c>
+      <c r="E262" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>797</v>
+      </c>
+      <c r="B263" t="s">
+        <v>473</v>
+      </c>
+      <c r="C263" t="s">
+        <v>798</v>
+      </c>
+      <c r="E263" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>800</v>
+      </c>
+      <c r="B264" t="s">
+        <v>473</v>
+      </c>
+      <c r="C264" t="s">
+        <v>801</v>
+      </c>
+      <c r="E264" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>803</v>
+      </c>
+      <c r="B265" t="s">
+        <v>473</v>
+      </c>
+      <c r="C265" t="s">
+        <v>804</v>
+      </c>
+      <c r="E265" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>806</v>
+      </c>
+      <c r="B266" t="s">
+        <v>473</v>
+      </c>
+      <c r="C266" t="s">
+        <v>807</v>
+      </c>
+      <c r="E266" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>809</v>
+      </c>
+      <c r="B267" t="s">
+        <v>473</v>
+      </c>
+      <c r="C267" t="s">
+        <v>810</v>
+      </c>
+      <c r="E267" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>812</v>
+      </c>
+      <c r="B268" t="s">
+        <v>473</v>
+      </c>
+      <c r="C268" t="s">
+        <v>813</v>
+      </c>
+      <c r="E268" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>815</v>
+      </c>
+      <c r="B269" t="s">
+        <v>473</v>
+      </c>
+      <c r="C269" t="s">
+        <v>816</v>
+      </c>
+      <c r="E269" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>818</v>
+      </c>
+      <c r="B270" t="s">
+        <v>473</v>
+      </c>
+      <c r="C270" t="s">
+        <v>819</v>
+      </c>
+      <c r="E270" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>821</v>
+      </c>
+      <c r="B271" t="s">
+        <v>473</v>
+      </c>
+      <c r="C271" t="s">
+        <v>822</v>
+      </c>
+      <c r="E271" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>824</v>
+      </c>
+      <c r="B272" t="s">
+        <v>473</v>
+      </c>
+      <c r="C272" t="s">
+        <v>825</v>
+      </c>
+      <c r="E272" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>827</v>
+      </c>
+      <c r="B273" t="s">
+        <v>473</v>
+      </c>
+      <c r="C273" t="s">
+        <v>828</v>
+      </c>
+      <c r="E273" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>830</v>
+      </c>
+      <c r="B274" t="s">
+        <v>831</v>
+      </c>
+      <c r="C274" t="s">
+        <v>832</v>
+      </c>
+      <c r="E274" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>834</v>
+      </c>
+      <c r="B275" t="s">
+        <v>831</v>
+      </c>
+      <c r="C275" t="s">
+        <v>835</v>
+      </c>
+      <c r="E275" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>837</v>
+      </c>
+      <c r="B276" t="s">
+        <v>831</v>
+      </c>
+      <c r="C276" t="s">
+        <v>838</v>
+      </c>
+      <c r="E276" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>840</v>
+      </c>
+      <c r="B277" t="s">
+        <v>831</v>
+      </c>
+      <c r="C277" t="s">
+        <v>841</v>
+      </c>
+      <c r="E277" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>843</v>
+      </c>
+      <c r="B278" t="s">
+        <v>831</v>
+      </c>
+      <c r="C278" t="s">
+        <v>844</v>
+      </c>
+      <c r="E278" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>846</v>
+      </c>
+      <c r="B279" t="s">
+        <v>831</v>
+      </c>
+      <c r="C279" t="s">
+        <v>847</v>
+      </c>
+      <c r="E279" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>849</v>
+      </c>
+      <c r="B280" t="s">
+        <v>831</v>
+      </c>
+      <c r="C280" t="s">
+        <v>850</v>
+      </c>
+      <c r="E280" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>852</v>
+      </c>
+      <c r="B281" t="s">
+        <v>831</v>
+      </c>
+      <c r="C281" t="s">
+        <v>853</v>
+      </c>
+      <c r="E281" t="s">
+        <v>854</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E51"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>855</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>856</v>
+      </c>
+      <c r="E6" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>858</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>856</v>
+      </c>
+      <c r="E7" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>860</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>856</v>
+      </c>
+      <c r="E8" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>862</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>856</v>
+      </c>
+      <c r="E9" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>864</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>856</v>
+      </c>
+      <c r="E10" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>866</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>867</v>
+      </c>
+      <c r="E11" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>869</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>844</v>
+      </c>
+      <c r="E12" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>871</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>844</v>
+      </c>
+      <c r="E13" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>873</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>835</v>
+      </c>
+      <c r="E14" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>875</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>876</v>
+      </c>
+      <c r="E15" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>878</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>850</v>
+      </c>
+      <c r="E16" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>880</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
+        <v>850</v>
+      </c>
+      <c r="E17" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>882</v>
+      </c>
+      <c r="B18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" t="s">
+        <v>850</v>
+      </c>
+      <c r="E18" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>884</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
+        <v>838</v>
+      </c>
+      <c r="E19" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>886</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
+        <v>838</v>
+      </c>
+      <c r="E20" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>888</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" t="s">
+        <v>889</v>
+      </c>
+      <c r="E21" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>891</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>889</v>
+      </c>
+      <c r="E22" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>893</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" t="s">
+        <v>889</v>
+      </c>
+      <c r="E23" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>895</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" t="s">
+        <v>889</v>
+      </c>
+      <c r="E24" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>897</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" t="s">
+        <v>898</v>
+      </c>
+      <c r="E25" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>900</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" t="s">
+        <v>901</v>
+      </c>
+      <c r="E26" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>903</v>
+      </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" t="s">
+        <v>898</v>
+      </c>
+      <c r="E27" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>905</v>
+      </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" t="s">
+        <v>853</v>
+      </c>
+      <c r="E28" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>907</v>
+      </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" t="s">
+        <v>853</v>
+      </c>
+      <c r="E29" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>909</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" t="s">
+        <v>853</v>
+      </c>
+      <c r="E30" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>911</v>
+      </c>
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" t="s">
+        <v>853</v>
+      </c>
+      <c r="E31" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>913</v>
+      </c>
+      <c r="B32" t="s">
+        <v>914</v>
+      </c>
+      <c r="C32" t="s">
+        <v>915</v>
+      </c>
+      <c r="E32" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>917</v>
+      </c>
+      <c r="B33" t="s">
+        <v>914</v>
+      </c>
+      <c r="C33" t="s">
+        <v>918</v>
+      </c>
+      <c r="E33" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>920</v>
+      </c>
+      <c r="B34" t="s">
+        <v>914</v>
+      </c>
+      <c r="C34" t="s">
+        <v>921</v>
+      </c>
+      <c r="E34" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>923</v>
+      </c>
+      <c r="B35" t="s">
+        <v>914</v>
+      </c>
+      <c r="C35" t="s">
+        <v>924</v>
+      </c>
+      <c r="E35" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>926</v>
+      </c>
+      <c r="B36" t="s">
+        <v>914</v>
+      </c>
+      <c r="C36" t="s">
+        <v>927</v>
+      </c>
+      <c r="E36" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>929</v>
+      </c>
+      <c r="B37" t="s">
+        <v>914</v>
+      </c>
+      <c r="C37" t="s">
+        <v>930</v>
+      </c>
+      <c r="E37" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>932</v>
+      </c>
+      <c r="B38" t="s">
+        <v>914</v>
+      </c>
+      <c r="C38" t="s">
+        <v>933</v>
+      </c>
+      <c r="E38" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>935</v>
+      </c>
+      <c r="B39" t="s">
+        <v>914</v>
+      </c>
+      <c r="C39" t="s">
+        <v>936</v>
+      </c>
+      <c r="E39" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>938</v>
+      </c>
+      <c r="B40" t="s">
+        <v>914</v>
+      </c>
+      <c r="C40" t="s">
+        <v>939</v>
+      </c>
+      <c r="E40" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>941</v>
+      </c>
+      <c r="B41" t="s">
+        <v>914</v>
+      </c>
+      <c r="C41" t="s">
+        <v>942</v>
+      </c>
+      <c r="E41" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>944</v>
+      </c>
+      <c r="B42" t="s">
+        <v>945</v>
+      </c>
+      <c r="C42" t="s">
+        <v>946</v>
+      </c>
+      <c r="E42" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>948</v>
+      </c>
+      <c r="B43" t="s">
+        <v>945</v>
+      </c>
+      <c r="C43" t="s">
+        <v>949</v>
+      </c>
+      <c r="E43" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>951</v>
+      </c>
+      <c r="B44" t="s">
+        <v>945</v>
+      </c>
+      <c r="C44" t="s">
+        <v>952</v>
+      </c>
+      <c r="E44" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>954</v>
+      </c>
+      <c r="B45" t="s">
+        <v>945</v>
+      </c>
+      <c r="C45" t="s">
+        <v>955</v>
+      </c>
+      <c r="E45" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>957</v>
+      </c>
+      <c r="B46" t="s">
+        <v>945</v>
+      </c>
+      <c r="C46" t="s">
+        <v>958</v>
+      </c>
+      <c r="E46" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>960</v>
+      </c>
+      <c r="B47" t="s">
+        <v>945</v>
+      </c>
+      <c r="C47" t="s">
+        <v>519</v>
+      </c>
+      <c r="E47" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>962</v>
+      </c>
+      <c r="B48" t="s">
+        <v>945</v>
+      </c>
+      <c r="C48" t="s">
+        <v>519</v>
+      </c>
+      <c r="E48" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>964</v>
+      </c>
+      <c r="B49" t="s">
+        <v>945</v>
+      </c>
+      <c r="C49" t="s">
+        <v>965</v>
+      </c>
+      <c r="E49" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>967</v>
+      </c>
+      <c r="B50" t="s">
+        <v>945</v>
+      </c>
+      <c r="C50" t="s">
+        <v>968</v>
+      </c>
+      <c r="E50" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>970</v>
+      </c>
+      <c r="B51" t="s">
+        <v>945</v>
+      </c>
+      <c r="C51" t="s">
+        <v>971</v>
+      </c>
+      <c r="E51" t="s">
+        <v>972</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -4,18 +4,19 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="-2" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="-1" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="2021-02-24-english" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="2021-02-24-chinese" state="visible" r:id="rId5"/>
+    <sheet sheetId="2" name="2021-02-24-chinese" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="2021-02-24-english" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="2021-02-25-chinese" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="9">
   <si>
     <t>标题</t>
   </si>
@@ -30,6 +31,18 @@
   </si>
   <si>
     <t>链接</t>
+  </si>
+  <si>
+    <t>Creating React components with TypeScript</t>
+  </si>
+  <si>
+    <t>React Status</t>
+  </si>
+  <si>
+    <t>2021-02-24</t>
+  </si>
+  <si>
+    <t>https://react.statuscode.com/issues/227</t>
   </si>
 </sst>
 </file>
@@ -406,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -431,6 +444,20 @@
       </c>
       <c r="E1" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -470,6 +497,41 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -4,19 +4,20 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="-1" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet sheetId="2" name="2021-02-24-chinese" state="visible" r:id="rId4"/>
     <sheet sheetId="1" name="2021-02-24-english" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="2021-02-25-chinese" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="2021-02-25-english" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="9">
   <si>
     <t>标题</t>
   </si>
@@ -532,6 +533,41 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -9,15 +9,15 @@
   <sheets>
     <sheet sheetId="2" name="2021-02-24-chinese" state="visible" r:id="rId4"/>
     <sheet sheetId="1" name="2021-02-24-english" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="2021-02-25-chinese" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="2021-02-25-english" state="visible" r:id="rId7"/>
+    <sheet sheetId="4" name="2021-02-25-english" state="visible" r:id="rId6"/>
+    <sheet sheetId="3" name="2021-02-25-chinese" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="13">
   <si>
     <t>标题</t>
   </si>
@@ -44,6 +44,18 @@
   </si>
   <si>
     <t>https://react.statuscode.com/issues/227</t>
+  </si>
+  <si>
+    <t>数十亿用户数据，上千个用户标签维度，用户分析怎么做？</t>
+  </si>
+  <si>
+    <t>infoq</t>
+  </si>
+  <si>
+    <t>2021-02-25</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/xZYe1DUopNA9CzLwau3O</t>
   </si>
 </sst>
 </file>
@@ -504,7 +516,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -531,9 +543,23 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -568,6 +594,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -9,15 +9,15 @@
   <sheets>
     <sheet sheetId="2" name="2021-02-24-chinese" state="visible" r:id="rId4"/>
     <sheet sheetId="1" name="2021-02-24-english" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="2021-02-25-chinese" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="2021-02-25-english" state="visible" r:id="rId7"/>
+    <sheet sheetId="4" name="2021-02-25-english" state="visible" r:id="rId6"/>
+    <sheet sheetId="3" name="2021-02-25-chinese" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="982">
   <si>
     <t>标题</t>
   </si>
@@ -44,6 +44,2925 @@
   </si>
   <si>
     <t>https://react.statuscode.com/issues/227</t>
+  </si>
+  <si>
+    <t>数十亿用户数据，上千个用户标签维度，用户分析怎么做？</t>
+  </si>
+  <si>
+    <t>infoq</t>
+  </si>
+  <si>
+    <t>2021-02-25</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/xZYe1DUopNA9CzLwau3O</t>
+  </si>
+  <si>
+    <t>4个强大JavaScript运算符</t>
+  </si>
+  <si>
+    <t>2021-02-22</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/KsSFAkrZ36hMZ6HMp0Ay</t>
+  </si>
+  <si>
+    <t>可能是最全的 “文本溢出截断省略” 方案合集</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/olxj0Q3uji9YvGw1JMx0</t>
+  </si>
+  <si>
+    <t>用 typescript 写一个工具函数库</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/r58umq8iJZGLA1wW3teU</t>
+  </si>
+  <si>
+    <t>闲鱼源码页面SSR最佳实践</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/kBFYqqwjRXkhgEYk1abx</t>
+  </si>
+  <si>
+    <t>移动应用不再是初创企业的好主意</t>
+  </si>
+  <si>
+    <t>2021-02-21</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/mkD8q4IQDlVUUXTsQ1tS</t>
+  </si>
+  <si>
+    <t>Deno现能够编译为独立的自包含二进制文件</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/0lsGR6lGWctq5NogpNrw</t>
+  </si>
+  <si>
+    <t>15 个常见的 Node.js 面试问题及答案</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/qbjXf0413REecA2EXGWd</t>
+  </si>
+  <si>
+    <t>2021年前端发展预测</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/qZ5gKxoS8VZDKOcyedjR</t>
+  </si>
+  <si>
+    <t>大数据+云：Kylin/Spark/Clickhouse/Hudi 的大佬们怎么看？</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/BjovMJUOiIzESTv1fgoZ</t>
+  </si>
+  <si>
+    <t>干货 | 前端跨端业务整合的探索与实践</t>
+  </si>
+  <si>
+    <t>2021-02-20</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/dsBDeLEohK3IHe8MblFB</t>
+  </si>
+  <si>
+    <t>抛弃V8参数适配器框架：JavaScript调用提速40%的实践</t>
+  </si>
+  <si>
+    <t>2021-02-19</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/xJ6f3Uu2M7hEglEqmyNa</t>
+  </si>
+  <si>
+    <t>Deno 2020 年大事记</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/PFW9j6TzIZpNd0tJ24JG</t>
+  </si>
+  <si>
+    <t>从推荐算法到前端开发，这是字节跳动技术Leader们最中意的40项学习资源 ｜ 资源推荐</t>
+  </si>
+  <si>
+    <t>2021-02-10</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/oO4VrzEj5XQtzLZSR2WA</t>
+  </si>
+  <si>
+    <t>无意间发现 Google 代码模板，分享给大家！</t>
+  </si>
+  <si>
+    <t>2021-02-07</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/1c0e4bb1b146ed0ffd55ce05e</t>
+  </si>
+  <si>
+    <t>长篇总结之JavaScript，巩固前端基础</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/b6a6b31fa2d890d5e89fee4cb</t>
+  </si>
+  <si>
+    <t>Vuex 4 正式发布：打包现在与 Vue 3 一致</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/MAXNFlc24wNh80hIhsSv</t>
+  </si>
+  <si>
+    <t>CSS开发过程中的20个快速提升技巧</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/9a34581102d4b7b38070b83b1</t>
+  </si>
+  <si>
+    <t>Wasmer发布GA版本的WebAssembly运行时</t>
+  </si>
+  <si>
+    <t>2021-02-03</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/f2Vml9f1KHIfTwGi5g1b</t>
+  </si>
+  <si>
+    <t>爱奇艺知识WEB前端组件化实践</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/5HirT1NNZYZmVwOUHaJG</t>
+  </si>
+  <si>
+    <t>浅析 Node 进程与线程</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/gF5xh4zt6mNwirLBSKpE</t>
+  </si>
+  <si>
+    <t>前阿里P8专家winter：怎么打造一支能力过硬的前端团队？</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/lvUOrbAu4PjdkSMRZOIQ</t>
+  </si>
+  <si>
+    <t>茶余饭后聊聊 Vue3.0 响应式数据那些事儿</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/HzMBaOLyEQANup0ycpzX</t>
+  </si>
+  <si>
+    <t>乾坤大挪移！React 也能 “用上” computed 属性</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/vCgBfwGCayKVIHoZ2i1s</t>
+  </si>
+  <si>
+    <t>webpack | 谈谈webpack的本质</t>
+  </si>
+  <si>
+    <t>2021-01-30</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/c48403d68f6b75356c02edb69</t>
+  </si>
+  <si>
+    <t>读2020年Javascript趋势报告展望ES2020</t>
+  </si>
+  <si>
+    <t>2021-01-31</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/8779819d0cd6ed24140f0e9b9</t>
+  </si>
+  <si>
+    <t>0到1：闲鱼高复杂度高性能社区圈子开发实录</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/RaGWMMAhkBl0DIqyCZpS</t>
+  </si>
+  <si>
+    <t>一种简单无副作用的同源跨页面数据同步方案</t>
+  </si>
+  <si>
+    <t>2021-01-29</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/oNphTLBXC1EVwJzGjQBb</t>
+  </si>
+  <si>
+    <t>浏览器里的本地数据库：IndexedDB</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/jglgydX0S0OMRlANvzXP</t>
+  </si>
+  <si>
+    <t>DIY VSCode 插件，让你的开发效率突飞猛进</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/gMil7xj0JPBBhcYZHfWW</t>
+  </si>
+  <si>
+    <t>凹凸技术揭秘 · 技术精进与业务发展两不误</t>
+  </si>
+  <si>
+    <t>凹凸实验室</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2021/02/01/both-tech-n-biz/</t>
+  </si>
+  <si>
+    <t>凹凸技术揭秘 · Taro · 开放式跨端跨框架之路</t>
+  </si>
+  <si>
+    <t>2021-01-14</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2021/01/14/taro-history/</t>
+  </si>
+  <si>
+    <t>凹凸技术揭秘 · 基础服务体系 · 构筑服务端技术中枢</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2021/01/14/exa-server/</t>
+  </si>
+  <si>
+    <t>凹凸技术揭秘 · Tide 研发平台 · 布局研发新基建</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2021/01/06/taro-ide-n-tide/</t>
+  </si>
+  <si>
+    <t>凹凸技术揭秘 · 夸克设计资产 · 打造全矩阵优质物料</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2021/01/06/quark-design-asset/</t>
+  </si>
+  <si>
+    <t>凹凸技术揭秘 · Deco 智能代码 · 开启产研效率革命</t>
+  </si>
+  <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/12/31/deco/</t>
+  </si>
+  <si>
+    <t>凹凸技术揭秘·羚珑页面可视化·成长蜕变之路</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/12/31/ling-atom-design/</t>
+  </si>
+  <si>
+    <t>凹凸技术揭秘·羚珑智能设计平台·逐梦设计数智化</t>
+  </si>
+  <si>
+    <t>2020-12-25</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/12/25/ling-ai-design/</t>
+  </si>
+  <si>
+    <t>凹凸实验室的过去与未来</t>
+  </si>
+  <si>
+    <t>2020-12-24</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/12/24/aotu-5-year/</t>
+  </si>
+  <si>
+    <t>京喜小程序首页瘦身实践</t>
+  </si>
+  <si>
+    <t>2020-11-30</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/11/30/jx-code-slim/</t>
+  </si>
+  <si>
+    <t>因为 Vue Ref 提案，我又刷了遍 label 语法</t>
+  </si>
+  <si>
+    <t>2020-11-23</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/11/23/vue-ref-sugar-javascript-label/</t>
+  </si>
+  <si>
+    <t>MongoDB 副本集之入门篇</t>
+  </si>
+  <si>
+    <t>2020-11-12</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/11/12/mongo-replica-set/</t>
+  </si>
+  <si>
+    <t>React 入门儿</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/11/12/react-indoor/</t>
+  </si>
+  <si>
+    <t>EaseJs 中 regX / regY 的用法</t>
+  </si>
+  <si>
+    <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/11/05/easeJs-center-setting/</t>
+  </si>
+  <si>
+    <t>node.js 沙盒逃逸分析</t>
+  </si>
+  <si>
+    <t>2020-10-28</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/10/28/node-sandbox-escape-analysis/</t>
+  </si>
+  <si>
+    <t>从浏览器渲染层面解析css3动效优化原理</t>
+  </si>
+  <si>
+    <t>2020-10-13</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/10/13/css3-optimization/</t>
+  </si>
+  <si>
+    <t>Flutter 性能优化：图片占位符、预缓存和禁用导航过渡动画</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/10/13/improving-perceived-performance-with-image-placeholders-precaching-and-disabled-navigation/</t>
+  </si>
+  <si>
+    <t>Flutter 性能优化：tree shaking 和延迟加载</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/10/13/optimizing-performance-in-flutter-web-apps-with-tree-shaking-and-deferred-loading/</t>
+  </si>
+  <si>
+    <t>Flutter 性能优化：打造高性能 widget</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/10/13/build-performant-flutter-widget/</t>
+  </si>
+  <si>
+    <t>你可能不知道的Animation动画技巧与细节</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/10/13/animation-skill/</t>
+  </si>
+  <si>
+    <t>使用 Vue3 开发小程序</t>
+  </si>
+  <si>
+    <t>2020-09-28</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/09/28/taro-vue3/</t>
+  </si>
+  <si>
+    <t>京喜小程序首页无障碍优化实践</t>
+  </si>
+  <si>
+    <t>2020-09-21</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/09/21/jx-weapp-accessible/</t>
+  </si>
+  <si>
+    <t>规范GIT代码提交信息&amp;自动化版本管理</t>
+  </si>
+  <si>
+    <t>2020-09-10</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/09/10/git-commit-control/</t>
+  </si>
+  <si>
+    <t>硬核看房利器——Web 全景的实现</t>
+  </si>
+  <si>
+    <t>2020-09-08</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/09/08/web-vr/</t>
+  </si>
+  <si>
+    <t>羚珑视频编辑器开发总结</t>
+  </si>
+  <si>
+    <t>2020-09-01</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/09/01/video-editor-summary/</t>
+  </si>
+  <si>
+    <t>Taro 版本升级权威指南</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/08/31/taro-versions/</t>
+  </si>
+  <si>
+    <t>三分钟打造七夕专属的插件化脚手架</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/08/25/valentine-plugin-cli/</t>
+  </si>
+  <si>
+    <t>京喜小程序体验评分优化实践</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/08/25/jx-audit-grade-optimization/</t>
+  </si>
+  <si>
+    <t>Design Tokens —— 设计与开发碰撞的火花</t>
+  </si>
+  <si>
+    <t>2020-08-18</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/08/18/design-tokens/</t>
+  </si>
+  <si>
+    <t>使用react-docgen自动生成组件文档</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/07/27/how-to-use-react-docgen/</t>
+  </si>
+  <si>
+    <t>几种移动端多平台元素垂直居中解决方案总结</t>
+  </si>
+  <si>
+    <t>2020-07-24</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/07/24/line-height-in-all-hardware/</t>
+  </si>
+  <si>
+    <t>如何使用Grid Layout</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/07/23/how-to-use-grid-layout/</t>
+  </si>
+  <si>
+    <t>移动端吸顶导航组件的实现</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/07/23/mobile-top-nav/</t>
+  </si>
+  <si>
+    <t>618前端竞品分析研究（互动篇）</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/07/21/618-what-taobao-do/</t>
+  </si>
+  <si>
+    <t>Webpack原理浅析</t>
+  </si>
+  <si>
+    <t>2020-07-17</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/07/17/webpack-analize/</t>
+  </si>
+  <si>
+    <t>京喜前端自动化测试之路(小程序篇)</t>
+  </si>
+  <si>
+    <t>2020-07-13</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/07/13/jx-automated-testing-weapp/</t>
+  </si>
+  <si>
+    <t>Taro 3 正式版发布：开放式跨端跨框架解决方案</t>
+  </si>
+  <si>
+    <t>2020-06-30</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/06/30/taro-3-0-0/</t>
+  </si>
+  <si>
+    <t>手把手教你写个小程序定时器管理库</t>
+  </si>
+  <si>
+    <t>2020-06-22</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/06/22/timer-miniprogram/</t>
+  </si>
+  <si>
+    <t>图形处理：给 Canvas 文本填充线性渐变</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/06/22/linearGradient/</t>
+  </si>
+  <si>
+    <t>向强大的SVG迈进</t>
+  </si>
+  <si>
+    <t>2020-06-09</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/06/09/strong-svg/</t>
+  </si>
+  <si>
+    <t>前端也要懂物理 —— 惯性滚动篇</t>
+  </si>
+  <si>
+    <t>2020-06-08</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/06/08/momentum-scrolling/</t>
+  </si>
+  <si>
+    <t>从 SQL 到 MongoDB 之聚合篇</t>
+  </si>
+  <si>
+    <t>2020-06-07</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/06/07/sql-to-mongo-2/</t>
+  </si>
+  <si>
+    <t>从 SQL 到 MongoDB 之概念篇</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/06/07/sql-to-mongo-1/</t>
+  </si>
+  <si>
+    <t>Taro 3.0 RC：React/Vue/Nerv 任你选</t>
+  </si>
+  <si>
+    <t>2020-05-25</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/05/25/taro-3-rc/</t>
+  </si>
+  <si>
+    <t>一个学习 Koa 源码的例子</t>
+  </si>
+  <si>
+    <t>2020-05-18</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/05/18/koa-demo/</t>
+  </si>
+  <si>
+    <t>大规格文件的上传优化</t>
+  </si>
+  <si>
+    <t>2020-05-12</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/05/12/file-upload/</t>
+  </si>
+  <si>
+    <t>京喜前端自动化测试之路</t>
+  </si>
+  <si>
+    <t>2020-05-06</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/05/06/jingxi-automated-testing/</t>
+  </si>
+  <si>
+    <t>京东小程序 Taro 开发对比原生开发测评</t>
+  </si>
+  <si>
+    <t>2020-04-27</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/04/27/taro-vs-jd/</t>
+  </si>
+  <si>
+    <t>使用 Taro 快速开发京东小程序</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/04/27/taro-build-jd/</t>
+  </si>
+  <si>
+    <t>智能可视化搭建系统 Atom 服务架构演变</t>
+  </si>
+  <si>
+    <t>2020-04-21</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/04/21/atom-services-upgrade/</t>
+  </si>
+  <si>
+    <t>Taro Next H5 跨框架组件库实践</t>
+  </si>
+  <si>
+    <t>2020-04-13</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/04/13/2020-4-13-taro-components/</t>
+  </si>
+  <si>
+    <t>Electron 在 Taro IDE 的开发实践</t>
+  </si>
+  <si>
+    <t>2020-04-07</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/04/07/electron-in-taro-ide/</t>
+  </si>
+  <si>
+    <t>如何打造高性能小程序门户</t>
+  </si>
+  <si>
+    <t>2020-03-25</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/03/25/high-performance-miniprogram/</t>
+  </si>
+  <si>
+    <t>直播回顾·程序媛的成长蜕变</t>
+  </si>
+  <si>
+    <t>2020-03-17</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/03/17/technological-growth/</t>
+  </si>
+  <si>
+    <t>Web 中文字体处理总结</t>
+  </si>
+  <si>
+    <t>2020-02-28</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/02/28/webfont-processing/</t>
+  </si>
+  <si>
+    <t>JDRD开发小结</t>
+  </si>
+  <si>
+    <t>2020-02-21</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/02/21/jdrd-summary/</t>
+  </si>
+  <si>
+    <t>Taro Next 发布预览版：同时支持 React / Vue / Nerv</t>
+  </si>
+  <si>
+    <t>2020-02-03</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/02/03/taro-next-alpha/</t>
+  </si>
+  <si>
+    <t>Taro 2.0：拥抱社区，拥抱变化</t>
+  </si>
+  <si>
+    <t>2020-01-08</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/01/08/taro-2-0/</t>
+  </si>
+  <si>
+    <t>GMTC |《小程序跨框架开发的探索与实践》演讲全文</t>
+  </si>
+  <si>
+    <t>2020-01-02</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2020/01/02/gmtc/</t>
+  </si>
+  <si>
+    <t>羚珑项目自动化测试方案实践</t>
+  </si>
+  <si>
+    <t>2019-12-05</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2019/12/05/ling-testing-project/</t>
+  </si>
+  <si>
+    <t>前端也要懂一点 MongoDB Schema 设计</t>
+  </si>
+  <si>
+    <t>2019-12-04</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2019/12/04/6-Rules-of-Thumb-for-MongoDB-Schema-Design/</t>
+  </si>
+  <si>
+    <t>京喜首页（微信购物入口）跨端开发与优化实践</t>
+  </si>
+  <si>
+    <t>2019-12-03</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2019/12/03/jingxi-index/</t>
+  </si>
+  <si>
+    <t>Sketch 插件开发实践</t>
+  </si>
+  <si>
+    <t>2019-10-31</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2019/10/31/sketch-plugin/</t>
+  </si>
+  <si>
+    <t>2019年，你是否可以抛弃 CSS 预处理器？</t>
+  </si>
+  <si>
+    <t>2019-10-29</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2019/10/29/css-preprocessor/</t>
+  </si>
+  <si>
+    <t>Mongoose-modified-at 时间自动记录插件介绍</t>
+  </si>
+  <si>
+    <t>2019-10-28</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2019/10/28/modified-at/</t>
+  </si>
+  <si>
+    <t>Taro 邀你加入社区共建 — 社区共建倡议书</t>
+  </si>
+  <si>
+    <t>2019-10-24</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2019/10/24/taro-open/</t>
+  </si>
+  <si>
+    <t>玩转 Taro 跨端之 flex 布局篇</t>
+  </si>
+  <si>
+    <t>2019-09-25</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2019/09/25/taro-flex/</t>
+  </si>
+  <si>
+    <t>从程序媛角度去看项目管理</t>
+  </si>
+  <si>
+    <t>2019-09-11</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2019/09/11/project-management-of-programmer/</t>
+  </si>
+  <si>
+    <t>京东 PC 首页 2019 改版前端总结</t>
+  </si>
+  <si>
+    <t>2019-08-26</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2019/08/26/jdindex_2019/</t>
+  </si>
+  <si>
+    <t>serverless</t>
+  </si>
+  <si>
+    <t>2019-08-05</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2019/08/05/serverless/</t>
+  </si>
+  <si>
+    <t>使用 React Hooks 重构你的小程序</t>
+  </si>
+  <si>
+    <t>2019-07-10</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2019/07/10/taro-hooks/</t>
+  </si>
+  <si>
+    <t>邀您参加「Taro x 小程序·云开发」物料开发竞赛</t>
+  </si>
+  <si>
+    <t>2019-07-01</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2019/07/01/taro-ext-action/</t>
+  </si>
+  <si>
+    <t>Taro 「物料市场」及「交流社区」 惊喜上线</t>
+  </si>
+  <si>
+    <t>2019-06-21</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2019/06/21/taro-ext-club/</t>
+  </si>
+  <si>
+    <t>Taro 1.3 震撼升级：全面支持 JSX 语法和 HOOKS</t>
+  </si>
+  <si>
+    <t>2019-06-13</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2019/06/13/taro-1-3/</t>
+  </si>
+  <si>
+    <t>小程序框架全面测评</t>
+  </si>
+  <si>
+    <t>2019-03-12</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2019/03/12/mini-program-framework-full-review/</t>
+  </si>
+  <si>
+    <t>决战性能之巅 - Taro H5 转换与优化升级</t>
+  </si>
+  <si>
+    <t>2019-02-28</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2019/02/28/taro-h5-optimize/</t>
+  </si>
+  <si>
+    <t>Taro UI 2.0 发布：新增自定义主题功能，适配更多小程序</t>
+  </si>
+  <si>
+    <t>2019-02-25</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2019/02/25/taro-ui-2.0/</t>
+  </si>
+  <si>
+    <t>全新 Phaser 3 游戏引擎特性一览</t>
+  </si>
+  <si>
+    <t>2018-12-23</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2018/12/23/phaser3/</t>
+  </si>
+  <si>
+    <t>Taro 1.2：将已有微信小程序转换为多端应用</t>
+  </si>
+  <si>
+    <t>2018-12-17</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2018/12/17/taro-1-2/</t>
+  </si>
+  <si>
+    <t>Taro深度开发实践</t>
+  </si>
+  <si>
+    <t>2018-11-30</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2018/11/30/taro_practice/</t>
+  </si>
+  <si>
+    <t>SVG vs Image, SVG vs Iconfont</t>
+  </si>
+  <si>
+    <t>2018-11-23</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2018/11/23/SVG_vs_Image_vs_iconfont/</t>
+  </si>
+  <si>
+    <t>Taro 1.1 发布，全面支持微信/百度/支付宝 小程序</t>
+  </si>
+  <si>
+    <t>2018-11-05</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2018/11/05/taro-1-1/</t>
+  </si>
+  <si>
+    <t>单屏页面响应式适配玩法</t>
+  </si>
+  <si>
+    <t>2018-10-22</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2018/10/22/Responsive-single-screen-design/</t>
+  </si>
+  <si>
+    <t>十分钟打造 3D 物理世界</t>
+  </si>
+  <si>
+    <t>2018-10-18</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2018/10/18/cannonjs/</t>
+  </si>
+  <si>
+    <t>多端统一开发框架 Taro 1.0 正式发布</t>
+  </si>
+  <si>
+    <t>2018-09-18</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2018/09/18/taro-1-0-0/</t>
+  </si>
+  <si>
+    <t>Taro 在京东购物小程序上的实践</t>
+  </si>
+  <si>
+    <t>2018-09-11</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2018/09/11/taro-in-jd/</t>
+  </si>
+  <si>
+    <t>首个多端 UI 组件库 - Taro UI 发布</t>
+  </si>
+  <si>
+    <t>2018-08-27</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2018/08/27/the-birth-of-taro-ui/</t>
+  </si>
+  <si>
+    <t>为何我们要用 React 来写小程序 - Taro 诞生记</t>
+  </si>
+  <si>
+    <t>2018-06-25</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2018/06/25/the-birth-of-taro/</t>
+  </si>
+  <si>
+    <t>多端统一开发框架 - Taro</t>
+  </si>
+  <si>
+    <t>2018-06-07</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2018/06/07/Taro/</t>
+  </si>
+  <si>
+    <t>图像处理 - ImageMagick 简单介绍与案例</t>
+  </si>
+  <si>
+    <t>2018-06-06</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2018/06/06/ImageMagick_intro/</t>
+  </si>
+  <si>
+    <t>Nerv实战 - 京东首页改版小结</t>
+  </si>
+  <si>
+    <t>2018-04-24</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2018/04/24/jdindex_2017/</t>
+  </si>
+  <si>
+    <t>Nerv - 京东高性能前端框架</t>
+  </si>
+  <si>
+    <t>2018-03-22</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2018/03/22/nerv/</t>
+  </si>
+  <si>
+    <t>动画：从 AE 到 Web</t>
+  </si>
+  <si>
+    <t>2018-03-06</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2018/03/06/ae2web/</t>
+  </si>
+  <si>
+    <t>H5游戏开发：FC小蜜蜂</t>
+  </si>
+  <si>
+    <t>2018-01-28</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2018/01/28/galaxian/</t>
+  </si>
+  <si>
+    <t>H5游戏开发：消灭星星</t>
+  </si>
+  <si>
+    <t>2018-01-17</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2018/01/17/popstar/</t>
+  </si>
+  <si>
+    <t>波动均分算法</t>
+  </si>
+  <si>
+    <t>2018-01-11</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2018/01/11/waveaverage/</t>
+  </si>
+  <si>
+    <t>H5游戏开发：套圈圈</t>
+  </si>
+  <si>
+    <t>2018-01-04</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2018/01/04/waterful/</t>
+  </si>
+  <si>
+    <t>H5游戏开发：游戏引擎入门推荐</t>
+  </si>
+  <si>
+    <t>2017-12-27</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/12/27/h5-game-engine-recommend/</t>
+  </si>
+  <si>
+    <t>GraphQL 使用介绍</t>
+  </si>
+  <si>
+    <t>2017-12-15</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/12/15/graphql-use/</t>
+  </si>
+  <si>
+    <t>H5游戏开发：指尖大冒险</t>
+  </si>
+  <si>
+    <t>2017-11-28</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/11/28/h5_game_jumping/</t>
+  </si>
+  <si>
+    <t>网页适配 iPhoneX，就是这么简单</t>
+  </si>
+  <si>
+    <t>2017-11-27</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/11/27/iphonex/</t>
+  </si>
+  <si>
+    <t>H5游戏开发：决胜三分球</t>
+  </si>
+  <si>
+    <t>2017-11-16</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/11/16/basketball/</t>
+  </si>
+  <si>
+    <t>H5游戏开发：推金币</t>
+  </si>
+  <si>
+    <t>2017-11-06</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/11/06/coindozer/</t>
+  </si>
+  <si>
+    <t>H5动画：轨迹移动</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/11/06/path-animation/</t>
+  </si>
+  <si>
+    <t>H5游戏开发：一笔画</t>
+  </si>
+  <si>
+    <t>2017-11-02</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/11/02/onestroke/</t>
+  </si>
+  <si>
+    <t>H5游戏开发：横屏适配</t>
+  </si>
+  <si>
+    <t>2017-10-18</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/10/18/landscape_mode_in_html5_game/</t>
+  </si>
+  <si>
+    <t>js创建一条通用链表</t>
+  </si>
+  <si>
+    <t>2017-10-13</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/10/13/make-a-chain-class/</t>
+  </si>
+  <si>
+    <t>wxapp-market 小程序营销组件</t>
+  </si>
+  <si>
+    <t>2017-09-28</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/09/28/wxapp-market/</t>
+  </si>
+  <si>
+    <t>实现 setTimeout &amp; setInterval 暂停的方案</t>
+  </si>
+  <si>
+    <t>2017-09-25</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/09/25/manage-setTimeout-an-setInterval/</t>
+  </si>
+  <si>
+    <t>H5游戏开发：贪吃蛇</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/09/25/h5game-snake/</t>
+  </si>
+  <si>
+    <t>whistle 使用实践</t>
+  </si>
+  <si>
+    <t>2017-08-29</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/08/29/an-introduction-to-whistle/</t>
+  </si>
+  <si>
+    <t>Three.js 现学现卖</t>
+  </si>
+  <si>
+    <t>2017-08-28</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/08/28/getting-started-with-threejs/</t>
+  </si>
+  <si>
+    <t>AT - 前端 UI 组件库</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/08/28/at-ui/</t>
+  </si>
+  <si>
+    <t>CSS技巧：逐帧动画抖动解决方案</t>
+  </si>
+  <si>
+    <t>2017-08-14</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/08/14/fix-sprite-anim/</t>
+  </si>
+  <si>
+    <t>这里有你对 Web 游戏的疑问吗？</t>
+  </si>
+  <si>
+    <t>2017-07-23</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/07/23/some-doubts-about-web-games/</t>
+  </si>
+  <si>
+    <t>一篇文章带你快速入门 CreateJS</t>
+  </si>
+  <si>
+    <t>2017-07-19</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/07/19/createjs/</t>
+  </si>
+  <si>
+    <t>Vue 探索与实践</t>
+  </si>
+  <si>
+    <t>2017-07-17</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/07/17/The-Exploration-and-Practice-of-Vue/</t>
+  </si>
+  <si>
+    <t>实现一个 Swiper</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/07/17/design-a-swiper/</t>
+  </si>
+  <si>
+    <t>2D圆形随机分布</t>
+  </si>
+  <si>
+    <t>2017-07-10</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/07/10/Random-Circles/</t>
+  </si>
+  <si>
+    <t>用Web技术实现移动监测</t>
+  </si>
+  <si>
+    <t>2017-06-29</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/06/29/motion-detection/</t>
+  </si>
+  <si>
+    <t>流式分页方案探索</t>
+  </si>
+  <si>
+    <t>2017-06-27</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/06/27/infinite-scrolling/</t>
+  </si>
+  <si>
+    <t>URL编码的奥秘</t>
+  </si>
+  <si>
+    <t>2017-06-15</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/06/15/The-mystery-of-URL-encoding/</t>
+  </si>
+  <si>
+    <t>10个你可能不知道的前端PS技巧</t>
+  </si>
+  <si>
+    <t>2017-06-09</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/06/09/ps-tricks/</t>
+  </si>
+  <si>
+    <t>canvas 图像旋转与翻转姿势解锁</t>
+  </si>
+  <si>
+    <t>2017-05-25</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/05/25/canvas-img-rotate-and-flip/</t>
+  </si>
+  <si>
+    <t>一个例子上手SVG动画</t>
+  </si>
+  <si>
+    <t>2017-05-04</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/05/04/example-for-svg-animation/</t>
+  </si>
+  <si>
+    <t>利用视口单位实现适配布局</t>
+  </si>
+  <si>
+    <t>2017-04-28</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/04/28/2017-4-28-CSS-viewport-units/</t>
+  </si>
+  <si>
+    <t>【译】关于 Node.js 里 ES6 Modules 的一次更新说明</t>
+  </si>
+  <si>
+    <t>2017-04-22</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/04/22/an-update-on-es6-modules-in-node-js/</t>
+  </si>
+  <si>
+    <t>Matter.js 2D 物理引擎试玩报告</t>
+  </si>
+  <si>
+    <t>2017-04-17</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/04/17/Matter-js/</t>
+  </si>
+  <si>
+    <t>Sticky Footer，完美的绝对底部</t>
+  </si>
+  <si>
+    <t>2017-04-13</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/04/13/Sticky-footer/</t>
+  </si>
+  <si>
+    <t>GPU加速是什么</t>
+  </si>
+  <si>
+    <t>2017-04-11</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/04/11/GPU/</t>
+  </si>
+  <si>
+    <t>了解 Fetch API</t>
+  </si>
+  <si>
+    <t>2017-04-10</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/04/10/fetch-API/</t>
+  </si>
+  <si>
+    <t>用 Git 钩子进行简单自动部署</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/04/10/githooks/</t>
+  </si>
+  <si>
+    <t>实现一个简单但有趣的AR效果（Web）</t>
+  </si>
+  <si>
+    <t>2017-03-24</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/03/24/webar/</t>
+  </si>
+  <si>
+    <t>轻氧 - React Native 安卓版 V1.0</t>
+  </si>
+  <si>
+    <t>2017-03-03</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/03/03/liteo2-android/</t>
+  </si>
+  <si>
+    <t>移动端真机调试指南</t>
+  </si>
+  <si>
+    <t>2017-02-24</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/02/24/Mobile-debug/</t>
+  </si>
+  <si>
+    <t>“等一下，我碰！”——常见的2D碰撞检测</t>
+  </si>
+  <si>
+    <t>2017-02-16</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/02/16/2d-collision-detection/</t>
+  </si>
+  <si>
+    <t>探讨判断横竖屏的最佳实现</t>
+  </si>
+  <si>
+    <t>2017-01-31</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/01/31/detect-orientation/</t>
+  </si>
+  <si>
+    <t>使用 Snap.svg 制作动画</t>
+  </si>
+  <si>
+    <t>2017-01-22</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/01/22/snapsvg/</t>
+  </si>
+  <si>
+    <t>sass-svg 一个内联 SVG 的 SASS 库</t>
+  </si>
+  <si>
+    <t>2017-01-19</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/01/19/sass-svg/</t>
+  </si>
+  <si>
+    <t>微信小程序跨页面通信解决思路</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/01/19/wxapp-event/</t>
+  </si>
+  <si>
+    <t>ELF - 灵活可扩展的 HTML5 构建工具</t>
+  </si>
+  <si>
+    <t>2017-01-17</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/01/17/elf/</t>
+  </si>
+  <si>
+    <t>聊聊 SVG 基本形状转换那些事</t>
+  </si>
+  <si>
+    <t>2017-01-16</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/01/16/base-shapes-to-path/</t>
+  </si>
+  <si>
+    <t>视频H5のVideo标签在微信里的坑和技巧</t>
+  </si>
+  <si>
+    <t>2017-01-11</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/01/11/mobile-video/</t>
+  </si>
+  <si>
+    <t>在微信小程序里实现图片预加载组件</t>
+  </si>
+  <si>
+    <t>2017-01-06</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/01/06/wxapp-img-loader/</t>
+  </si>
+  <si>
+    <t>第2季极客沙龙资料分享 - 知行·前端体验主题交流会</t>
+  </si>
+  <si>
+    <t>2017-01-04</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2017/01/04/geek-talks-s2/</t>
+  </si>
+  <si>
+    <t>一个栗子实践vue2.0与1.0的区别</t>
+  </si>
+  <si>
+    <t>2016-12-28</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/12/28/vue-clock/</t>
+  </si>
+  <si>
+    <t>京东2016版首页改版前端总结</t>
+  </si>
+  <si>
+    <t>2016-12-26</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/12/26/jd-index-2016-summary/</t>
+  </si>
+  <si>
+    <t>vim给代码行尾加分号的几种方法</t>
+  </si>
+  <si>
+    <t>2016-12-08</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/12/08/vim-4/</t>
+  </si>
+  <si>
+    <t>正则表达式实践篇</t>
+  </si>
+  <si>
+    <t>2016-12-07</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/12/07/regexp-practice/</t>
+  </si>
+  <si>
+    <t>源码赏析 - 1K的Firewatch游戏</t>
+  </si>
+  <si>
+    <t>2016-12-04</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/12/04/firewatcher-appreciation/</t>
+  </si>
+  <si>
+    <t>项目心得 -- 京东云改版</t>
+  </si>
+  <si>
+    <t>2016-12-02</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/12/02/jcloud/</t>
+  </si>
+  <si>
+    <t>css3 animation 属性众妙</t>
+  </si>
+  <si>
+    <t>2016-11-28</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/11/28/css3-animation-properties/</t>
+  </si>
+  <si>
+    <t>三看 SVG Web 动效</t>
+  </si>
+  <si>
+    <t>2016-11-22</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/11/22/SVG_Web_Animation/</t>
+  </si>
+  <si>
+    <t>FIGlet初识</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/11/22/figlet/</t>
+  </si>
+  <si>
+    <t>「塔罗牌」 - 轻氧 V1.4 尝鲜体验邀请</t>
+  </si>
+  <si>
+    <t>2016-11-21</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/11/21/liteo2-app-tarots/</t>
+  </si>
+  <si>
+    <t>正则表达式理论篇</t>
+  </si>
+  <si>
+    <t>2016-11-17</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/11/17/regexp-theory/</t>
+  </si>
+  <si>
+    <t>XCel 项目总结 - Electron 与 Vue 的性能优化</t>
+  </si>
+  <si>
+    <t>2016-11-15</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/11/15/xcel/</t>
+  </si>
+  <si>
+    <t>漫漫编程路上必读的7本书</t>
+  </si>
+  <si>
+    <t>2016-11-14</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/11/14/booklist-for-every-programmer/</t>
+  </si>
+  <si>
+    <t>Webpack 实用配置技巧</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/11/14/webpack-tips/</t>
+  </si>
+  <si>
+    <t>WeUI for 小程序 - 为微信小程序量身设计</t>
+  </si>
+  <si>
+    <t>2016-11-10</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/11/10/weui-wxss/</t>
+  </si>
+  <si>
+    <t>轻氧 - 2016年末最新款互联网专业资讯 APP</t>
+  </si>
+  <si>
+    <t>2016-11-09</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/11/09/liteo2-app/</t>
+  </si>
+  <si>
+    <t>深入了解font-weight</t>
+  </si>
+  <si>
+    <t>2016-11-08</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/11/08/css3fontweight/</t>
+  </si>
+  <si>
+    <t>我的第一次移动端页面制作 — 总结与思考</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/11/08/first-mobile-rebuild/</t>
+  </si>
+  <si>
+    <t>APNG 那些事</t>
+  </si>
+  <si>
+    <t>2016-11-07</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/11/07/apng/</t>
+  </si>
+  <si>
+    <t>AdobeMax 2016回顾</t>
+  </si>
+  <si>
+    <t>2016-11-02</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/11/02/AdobeMax2016/</t>
+  </si>
+  <si>
+    <t>border-image 的正确用法</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/11/02/border-image/</t>
+  </si>
+  <si>
+    <t>Javascript 中的装饰器</t>
+  </si>
+  <si>
+    <t>2016-10-24</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/10/24/decorator/</t>
+  </si>
+  <si>
+    <t>CSS3 Mask 安利报告</t>
+  </si>
+  <si>
+    <t>2016-10-19</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/10/19/css3-mask/</t>
+  </si>
+  <si>
+    <t>Vue2.0 新手完全填坑攻略——从环境搭建到展示豆瓣的电影列表</t>
+  </si>
+  <si>
+    <t>2016-10-13</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/10/13/vue2/</t>
+  </si>
+  <si>
+    <t>H5直播起航</t>
+  </si>
+  <si>
+    <t>2016-10-09</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/10/09/HTML5-SopCast/</t>
+  </si>
+  <si>
+    <t>A-Frame WebVR试玩报告</t>
+  </si>
+  <si>
+    <t>2016-10-08</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/10/08/aframe/</t>
+  </si>
+  <si>
+    <t>在网页上实现 3D Touch 效果</t>
+  </si>
+  <si>
+    <t>2016-09-28</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/09/28/3d-touch/</t>
+  </si>
+  <si>
+    <t>HTTP 缓存</t>
+  </si>
+  <si>
+    <t>2016-09-22</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/09/22/http-caching/</t>
+  </si>
+  <si>
+    <t>通过 Babel 使用 ES6 的 import</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/09/22/es6-import-with-babel/</t>
+  </si>
+  <si>
+    <t>写给新人的call、apply、bind</t>
+  </si>
+  <si>
+    <t>2016-09-02</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/09/02/Different-Binding/</t>
+  </si>
+  <si>
+    <t>SeaJS从入门到原理</t>
+  </si>
+  <si>
+    <t>2016-08-29</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/08/29/SeaJs-From-Entry-To-The-Principle/</t>
+  </si>
+  <si>
+    <t>浅谈 WebVR</t>
+  </si>
+  <si>
+    <t>2016-08-24</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/08/24/2016-8-24-webvr/</t>
+  </si>
+  <si>
+    <t>CSS 3D Panorama - 淘宝造物节技术剖析</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/08/24/2016-8-24-css-3d-panorama/</t>
+  </si>
+  <si>
+    <t>Nginx 配置 HTTPS 服务器</t>
+  </si>
+  <si>
+    <t>2016-08-16</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/08/16/nginx-https/</t>
+  </si>
+  <si>
+    <t>跟着老司机玩转Node命令行</t>
+  </si>
+  <si>
+    <t>2016-08-09</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/08/09/command-line-development/</t>
+  </si>
+  <si>
+    <t>带机器人上设计学校</t>
+  </si>
+  <si>
+    <t>2016-08-05</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/08/05/robot-design-school/</t>
+  </si>
+  <si>
+    <t>2016年夏季蜜桃通缉令</t>
+  </si>
+  <si>
+    <t>2016-07-28</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/07/28/o2-wants-you/</t>
+  </si>
+  <si>
+    <t>Vue实战－邮箱签名设计项目</t>
+  </si>
+  <si>
+    <t>2016-07-25</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/07/25/vuejs-mailsign/</t>
+  </si>
+  <si>
+    <t>我们是如何做好前端工程化和静态资源管理</t>
+  </si>
+  <si>
+    <t>2016-07-19</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/07/19/A-little-exploration-of-front-end-engineering/</t>
+  </si>
+  <si>
+    <t>拥抱Web设计新趋势：SVG Sprites实践应用</t>
+  </si>
+  <si>
+    <t>2016-07-09</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/07/09/SVG-Symbol-component-practice/</t>
+  </si>
+  <si>
+    <t>feWorkflow - 使用electron, react, redux, immutable构建桌面App</t>
+  </si>
+  <si>
+    <t>2016-07-05</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/07/05/fe-workflow/</t>
+  </si>
+  <si>
+    <t>第二界HiFSD分享会PPT讲义下载分享</t>
+  </si>
+  <si>
+    <t>2016-07-03</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/07/03/HIFSD2-Summary/</t>
+  </si>
+  <si>
+    <t>神奇的Shadow DOM</t>
+  </si>
+  <si>
+    <t>2016-06-24</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/06/24/Shadow-DOM/</t>
+  </si>
+  <si>
+    <t>探究WebP一些事儿</t>
+  </si>
+  <si>
+    <t>2016-06-23</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/06/23/explore-something-of-webp/</t>
+  </si>
+  <si>
+    <t>让console充满情怀</t>
+  </si>
+  <si>
+    <t>2016-06-22</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/06/22/An-interesting-experience-on-console/</t>
+  </si>
+  <si>
+    <t>假如HTTP/2已经普及</t>
+  </si>
+  <si>
+    <t>2016-06-14</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/06/14/http2/</t>
+  </si>
+  <si>
+    <t>Adobe Spark试用手记</t>
+  </si>
+  <si>
+    <t>2016-05-27</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/05/27/adobe-spark/</t>
+  </si>
+  <si>
+    <t>CSS3动画之逐帧动画</t>
+  </si>
+  <si>
+    <t>2016-05-17</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/05/17/css3-animation-frame/</t>
+  </si>
+  <si>
+    <t>CSS3动画之补间动画</t>
+  </si>
+  <si>
+    <t>2016-05-06</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/05/06/Guide-To-Tween-Animation/</t>
+  </si>
+  <si>
+    <t>CSS3动画之3D动画</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/05/06/CSS3-3D-Animation/</t>
+  </si>
+  <si>
+    <t>Swift Package Manager 快速入门指引</t>
+  </si>
+  <si>
+    <t>2016-04-28</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/04/28/SPM/</t>
+  </si>
+  <si>
+    <t>如何用ArrayBuffer构造一个form请求</t>
+  </si>
+  <si>
+    <t>2016-04-21</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/04/21/form-request/</t>
+  </si>
+  <si>
+    <t>JavaScript中reduce()方法不完全指南</t>
+  </si>
+  <si>
+    <t>2016-04-14</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/04/14/js-reduce/</t>
+  </si>
+  <si>
+    <t>JavaScript中Math.random的种子设定方法</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/04/14/math-random/</t>
+  </si>
+  <si>
+    <t>Canvas虹膜消除转场</t>
+  </si>
+  <si>
+    <t>2016-04-13</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/04/13/Iris-Wipe/</t>
+  </si>
+  <si>
+    <t>前端优化实践总结</t>
+  </si>
+  <si>
+    <t>2016-04-12</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/04/12/jcloud-opt/</t>
+  </si>
+  <si>
+    <t>Node读写Excel文件探究实践</t>
+  </si>
+  <si>
+    <t>2016-04-07</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/04/07/node-excel/</t>
+  </si>
+  <si>
+    <t>提升代码的可读性系列(一)--基础篇</t>
+  </si>
+  <si>
+    <t>2016-03-31</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/03/31/readable/</t>
+  </si>
+  <si>
+    <t>如何优雅地在Storyboard中设置圆角</t>
+  </si>
+  <si>
+    <t>2016-03-30</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/03/30/cornerRadius-in-Storyboard/</t>
+  </si>
+  <si>
+    <t>前端开发与 HTTP/2 的羁绊——安利篇</t>
+  </si>
+  <si>
+    <t>2016-03-17</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/03/17/http2-char/</t>
+  </si>
+  <si>
+    <t>前端优化不完全指南</t>
+  </si>
+  <si>
+    <t>2016-03-16</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/03/16/optimization/</t>
+  </si>
+  <si>
+    <t>某超长文档的探索之路</t>
+  </si>
+  <si>
+    <t>2016-03-15</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/03/15/jcloud-sum/</t>
+  </si>
+  <si>
+    <t>让图片加载这件事儿变得更美好</t>
+  </si>
+  <si>
+    <t>2016-03-09</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/03/09/img-loading-optimization-in-mobile/</t>
+  </si>
+  <si>
+    <t>图片资源Base64化在H5页面里有用武之地吗？</t>
+  </si>
+  <si>
+    <t>2016-03-04</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/03/04/can-we-use-base64-in-h5-webapps/</t>
+  </si>
+  <si>
+    <t>createjs开发入门</t>
+  </si>
+  <si>
+    <t>2016-03-01</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/03/01/createjs-get-started/</t>
+  </si>
+  <si>
+    <t>初探Docker</t>
+  </si>
+  <si>
+    <t>2016-02-27</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/02/27/docker/</t>
+  </si>
+  <si>
+    <t>使用npm scripts替代gulp</t>
+  </si>
+  <si>
+    <t>2016-02-26</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/02/26/use-npm-script-instead-of-gulp/</t>
+  </si>
+  <si>
+    <t>Node 生产环境调试</t>
+  </si>
+  <si>
+    <t>2016-02-24</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/02/24/node-debug-in-production/</t>
+  </si>
+  <si>
+    <t>手把手教你搭建ngrok服务－轻松外网调试本机站点</t>
+  </si>
+  <si>
+    <t>2016-02-19</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/02/19/ngrok/</t>
+  </si>
+  <si>
+    <t>你所知道的3xx状态码</t>
+  </si>
+  <si>
+    <t>2016-01-28</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/01/28/3xx-of-http-status/</t>
+  </si>
+  <si>
+    <t>如何制作cocoaPods依赖库</t>
+  </si>
+  <si>
+    <t>2016-01-27</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/01/27/how-to-make-cocoapods/</t>
+  </si>
+  <si>
+    <t>如何创建私有 CocoaPods 仓库</t>
+  </si>
+  <si>
+    <t>2016-01-26</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/01/26/Private-CocoaPods-Specs-Repo/</t>
+  </si>
+  <si>
+    <t>UFT 需求提报平台回顾</t>
+  </si>
+  <si>
+    <t>2016-01-16</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/01/16/UFT/</t>
+  </si>
+  <si>
+    <t>js游戏开发初级入门</t>
+  </si>
+  <si>
+    <t>2016-01-14</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/01/14/introduction-to-JS-game-development/</t>
+  </si>
+  <si>
+    <t>Promise 实战</t>
+  </si>
+  <si>
+    <t>2016-01-08</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/01/08/promise/</t>
+  </si>
+  <si>
+    <t>使用Chrome开发工具优化Web应用</t>
+  </si>
+  <si>
+    <t>2016-01-07</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/01/07/debug-webapp-with-chrome-devtools/</t>
+  </si>
+  <si>
+    <t>使用Github的webhooks进行网站自动化部署</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/01/07/auto-deploy-website-by-webhooks-of-github/</t>
+  </si>
+  <si>
+    <t>CSS3动画实践</t>
+  </si>
+  <si>
+    <t>2016-01-04</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/01/04/css3-animation/</t>
+  </si>
+  <si>
+    <t>使用ThreeJS在浏览器中展示全景图</t>
+  </si>
+  <si>
+    <t>2016-01-02</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2016/01/02/3D-panorama/</t>
+  </si>
+  <si>
+    <t>初识Adobe After Effects效果制作</t>
+  </si>
+  <si>
+    <t>2015-12-29</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2015/12/29/ae/</t>
+  </si>
+  <si>
+    <t>Safari 9.0的新特性</t>
+  </si>
+  <si>
+    <t>2015-12-23</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2015/12/23/new-safari-9/</t>
+  </si>
+  <si>
+    <t>【译】使用Node.js创建命令行脚本工具</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2015/12/23/building-command-line-tools-with-node-js/</t>
+  </si>
+  <si>
+    <t>What Does the Foo Mean</t>
+  </si>
+  <si>
+    <t>2015-12-18</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2015/12/18/etymology-of-foobar/</t>
+  </si>
+  <si>
+    <t>【译】介绍Sass Maps：用法跟例子</t>
+  </si>
+  <si>
+    <t>2015-12-09</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2015/12/09/an-introduction-to-sass-maps/</t>
+  </si>
+  <si>
+    <t>Adobe edge animate制作HTML5动画</t>
+  </si>
+  <si>
+    <t>2015-12-04</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2015/12/04/edgeAnimate/</t>
+  </si>
+  <si>
+    <t>精致化页面重构</t>
+  </si>
+  <si>
+    <t>2015-11-24</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2015/11/24/project-summary/</t>
+  </si>
+  <si>
+    <t>使用ThreeJS在浏览器中展示3D物件</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2015/11/24/3D-CleaningCream/</t>
+  </si>
+  <si>
+    <t>以电影之眼看CSS3动画（二）</t>
+  </si>
+  <si>
+    <t>2015-11-23</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2015/11/23/css3-animation-to-movie-part_2/</t>
+  </si>
+  <si>
+    <t>以电影之眼看CSS3动画（一）</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2015/11/23/css3-animation-to-movie-part_1/</t>
+  </si>
+  <si>
+    <t>SVG I Know</t>
+  </si>
+  <si>
+    <t>2015-11-20</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2015/11/20/svg-I-know/</t>
+  </si>
+  <si>
+    <t>Git常用操作总结</t>
+  </si>
+  <si>
+    <t>2015-11-17</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2015/11/17/Git-Commands/</t>
+  </si>
+  <si>
+    <t>101%还原</t>
+  </si>
+  <si>
+    <t>2015-11-16</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2015/11/16/101-percent/</t>
+  </si>
+  <si>
+    <t>基于phantomJs的网络爬虫</t>
+  </si>
+  <si>
+    <t>2015-11-11</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2015/11/11/phantomJs-crawler/</t>
+  </si>
+  <si>
+    <t>css层叠顺序探究</t>
+  </si>
+  <si>
+    <t>2015-11-08</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2015/11/08/css-stack-order/</t>
+  </si>
+  <si>
+    <t>Service Workers：采用WebP动态响应图片</t>
+  </si>
+  <si>
+    <t>2015-11-06</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2015/11/06/webp-responsive-image/</t>
+  </si>
+  <si>
+    <t>使用Adobe FLASH CC制作Canvas动画</t>
+  </si>
+  <si>
+    <t>2015-11-02</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2015/11/02/flash-canvas/</t>
+  </si>
+  <si>
+    <t>前方有坑，请绕道——Zepto 中使用 CORS</t>
+  </si>
+  <si>
+    <t>2015-10-26</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2015/10/26/zepto-cors/</t>
+  </si>
+  <si>
+    <t>探究transform动画元素的z-index</t>
+  </si>
+  <si>
+    <t>2015-10-21</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2015/10/21/z-index-and-translate3d/</t>
+  </si>
+  <si>
+    <t>我的vim二三事</t>
+  </si>
+  <si>
+    <t>2015-10-16</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2015/10/16/vim-list/</t>
+  </si>
+  <si>
+    <t>PostCSS快速入门使用</t>
+  </si>
+  <si>
+    <t>2015-10-13</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2015/10/13/start-postcss/</t>
+  </si>
+  <si>
+    <t>凹凸实验室博客V1.0.0发布</t>
+  </si>
+  <si>
+    <t>2015-10-08</t>
+  </si>
+  <si>
+    <t>https://aotu.io/notes/2015/10/08/aotu-blog-v1/</t>
+  </si>
+  <si>
+    <t>使用CSS text-combine-upright实现字符的横向合并</t>
+  </si>
+  <si>
+    <t>张鑫旭</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>https://www.zhangxinxu.com/wordpress/2021/02/css-text-combine-upright/</t>
+  </si>
+  <si>
+    <t>CSS line-break属性与中文标点换行</t>
+  </si>
+  <si>
+    <t>https://www.zhangxinxu.com/wordpress/2021/02/css-line-break/</t>
+  </si>
+  <si>
+    <t>Chrome 88已经支持aspect-ratio属性了，学起来</t>
+  </si>
+  <si>
+    <t>2021-02-17</t>
+  </si>
+  <si>
+    <t>https://www.zhangxinxu.com/wordpress/2021/02/css-aspect-ratio/</t>
+  </si>
+  <si>
+    <t>好消息，CSS text-underline-offset可以用起来了</t>
+  </si>
+  <si>
+    <t>https://www.zhangxinxu.com/wordpress/2021/02/css-text-underline-offset/</t>
+  </si>
+  <si>
+    <t>CSS ::marker伪元素简介</t>
+  </si>
+  <si>
+    <t>2021-02-16</t>
+  </si>
+  <si>
+    <t>https://www.zhangxinxu.com/wordpress/2021/02/css-marker-pseudo-element/#respond</t>
+  </si>
+  <si>
+    <t>盘点HTML字符串转DOM的各种方法及细节</t>
+  </si>
+  <si>
+    <t>https://www.zhangxinxu.com/wordpress/2021/02/html-string-dom/</t>
+  </si>
+  <si>
+    <t>如何使用JS检测用户是否缩放了页面？</t>
+  </si>
+  <si>
+    <t>2021-02-15</t>
+  </si>
+  <si>
+    <t>https://www.zhangxinxu.com/wordpress/2021/02/js-if-page-zoom/</t>
+  </si>
+  <si>
+    <t>直线等图形从中间穿过元素或文字的CSS实现</t>
+  </si>
+  <si>
+    <t>2021-02-14</t>
+  </si>
+  <si>
+    <t>https://www.zhangxinxu.com/wordpress/2021/02/css-3d-through/#respond</t>
+  </si>
+  <si>
+    <t>了解CSS revert全局关键字</t>
+  </si>
+  <si>
+    <t>https://www.zhangxinxu.com/wordpress/2021/02/css-revert/</t>
+  </si>
+  <si>
+    <t>Web Components中引入外部CSS的3种方法</t>
+  </si>
+  <si>
+    <t>2021-02-13</t>
+  </si>
+  <si>
+    <t>https://www.zhangxinxu.com/wordpress/2021/02/web-components-import-css/</t>
+  </si>
+  <si>
+    <t>前端智能化实践— P2C 从需求文档生成代码</t>
+  </si>
+  <si>
+    <t>Taobao FED | 淘系前端团队</t>
+  </si>
+  <si>
+    <t>https://fed.taobao.org/blog/taofed/do71ct/ffeogu</t>
+  </si>
+  <si>
+    <t>舒文：浅谈阿里前端的多样化</t>
+  </si>
+  <si>
+    <t>2020-12-10</t>
+  </si>
+  <si>
+    <t>https://fed.taobao.org/blog/taofed/do71ct/krg5m9</t>
+  </si>
+  <si>
+    <t>CodeReview 下一代：基于 KAITIAN 的纯前端 CR IDE</t>
+  </si>
+  <si>
+    <t>2020-12-02</t>
+  </si>
+  <si>
+    <t>https://fed.taobao.org/blog/taofed/do71ct/uyaxag</t>
+  </si>
+  <si>
+    <t>Pick 阿里巴巴前端练习生计划，成为专业前端人！</t>
+  </si>
+  <si>
+    <t>2020-11-27</t>
+  </si>
+  <si>
+    <t>https://fed.taobao.org/blog/taofed/do71ct/fiayw0</t>
+  </si>
+  <si>
+    <t>4982亿背后的前端技术—2020天猫双11前端体系大揭秘</t>
+  </si>
+  <si>
+    <t>2020-11-16</t>
+  </si>
+  <si>
+    <t>https://fed.taobao.org/blog/taofed/do71ct/egg54e</t>
+  </si>
+  <si>
+    <t>用SVG实现一个优雅的提示框</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>https://fed.taobao.org/blog/taofed/do71ct/ghpnlx</t>
+  </si>
+  <si>
+    <t>淘系前端互动引擎EVAJS架构与生态实现</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>https://fed.taobao.org/blog/taofed/do71ct/pg45el</t>
+  </si>
+  <si>
+    <t>10 个你可能还不知道 VS Code 使用技巧</t>
+  </si>
+  <si>
+    <t>2020-09-09</t>
+  </si>
+  <si>
+    <t>https://fed.taobao.org/blog/taofed/do71ct/eonv5x</t>
+  </si>
+  <si>
+    <t>我的前端成长之路： 在阿里七年，我的成长和迷茫</t>
+  </si>
+  <si>
+    <t>2020-09-04</t>
+  </si>
+  <si>
+    <t>https://fed.taobao.org/blog/taofed/do71ct/ttpk5r</t>
+  </si>
+  <si>
+    <t>JavaScript 深度学习 - Hello World</t>
+  </si>
+  <si>
+    <t>https://fed.taobao.org/blog/taofed/do71ct/er55la</t>
+  </si>
+  <si>
+    <t>入职一年多的一些思考</t>
+  </si>
+  <si>
+    <t>2020-08-27</t>
+  </si>
+  <si>
+    <t>https://fed.taobao.org/blog/taofed/do71ct/sxz5ap</t>
+  </si>
+  <si>
+    <t>如何在应用架构中设计微前端方案 - icestark</t>
+  </si>
+  <si>
+    <t>https://fed.taobao.org/blog/taofed/do71ct/xgmaz3</t>
+  </si>
+  <si>
+    <t>阿里实习 90 天：从实习生的视角谈谈个人成长</t>
+  </si>
+  <si>
+    <t>2020-08-21</t>
+  </si>
+  <si>
+    <t>https://fed.taobao.org/blog/taofed/do71ct/acbnym</t>
+  </si>
+  <si>
+    <t>什么是人工智能自动编程？它只是一个噱头吗？</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>https://fed.taobao.org/blog/taofed/do71ct/clcgcc</t>
+  </si>
+  <si>
+    <t>淘系运营工作台前端体系</t>
+  </si>
+  <si>
+    <t>2020-08-16</t>
+  </si>
+  <si>
+    <t>https://fed.taobao.org/blog/taofed/do71ct/oyf9hm</t>
+  </si>
+  <si>
+    <t>一起来玩玩WebGL--第二弹</t>
+  </si>
+  <si>
+    <t>2020-08-13</t>
+  </si>
+  <si>
+    <t>https://fed.taobao.org/blog/taofed/do71ct/ghlebo</t>
+  </si>
+  <si>
+    <t>我在阿里收获的N个成长</t>
+  </si>
+  <si>
+    <t>2020-08-10</t>
+  </si>
+  <si>
+    <t>https://fed.taobao.org/blog/taofed/do71ct/reqhle</t>
+  </si>
+  <si>
+    <t>可折叠Web可能会给我们带来的变化</t>
+  </si>
+  <si>
+    <t>2020-08-01</t>
+  </si>
+  <si>
+    <t>https://fed.taobao.org/blog/taofed/do71ct/zbxacs</t>
+  </si>
+  <si>
+    <t>2020年，该如何选择小程序框架</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>https://fed.taobao.org/blog/taofed/do71ct/sz7x0q</t>
+  </si>
+  <si>
+    <t>业务前端如何突破困境</t>
+  </si>
+  <si>
+    <t>2020-07-29</t>
+  </si>
+  <si>
+    <t>https://fed.taobao.org/blog/taofed/do71ct/front-end-problems</t>
+  </si>
+  <si>
+    <t>WKWebView 请求拦截探索与实践</t>
+  </si>
+  <si>
+    <t>知乎-网易云音乐大前端团队</t>
+  </si>
+  <si>
+    <t>2021-01-28</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/347592487</t>
+  </si>
+  <si>
+    <t>函数式编程进阶：Monad 与 异步函数的组合</t>
+  </si>
+  <si>
+    <t>2021-01-19</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/345339684</t>
+  </si>
+  <si>
+    <t>Flutter 图片控件适配之路</t>
+  </si>
+  <si>
+    <t>2021-01-13</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/343932734</t>
+  </si>
+  <si>
+    <t>剖析 lottie-web 动画实现原理</t>
+  </si>
+  <si>
+    <t>2021-01-07</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/342477231</t>
+  </si>
+  <si>
+    <t>Poplayer 云音乐优化实践</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/340595290</t>
+  </si>
+  <si>
+    <t>React 事件系统工作原理</t>
+  </si>
+  <si>
+    <t>2020-12-23</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/338904728</t>
+  </si>
+  <si>
+    <t>漫谈 React Fiber</t>
+  </si>
+  <si>
+    <t>2020-12-16</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/337275795</t>
+  </si>
+  <si>
+    <t>云音乐 Android 视频「无缝」播放实现总结</t>
+  </si>
+  <si>
+    <t>2020-12-09</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/335015746</t>
+  </si>
+  <si>
+    <t>聊聊 RN 中 Android 提供 View 的那些坑</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/325802528</t>
+  </si>
+  <si>
+    <t>如何基于 TypeScript 实现控制反转</t>
+  </si>
+  <si>
+    <t>2020-11-25</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/311184005</t>
+  </si>
+  <si>
+    <t>Node开发实践总结-定时脚本的设计与实现</t>
+  </si>
+  <si>
+    <t>知乎-IMWeb前端社区</t>
+  </si>
+  <si>
+    <t>2021-01-05</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/342090208</t>
+  </si>
+  <si>
+    <t>看前端如何通过WebAssembly实现播放器预览能力</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/341001951</t>
+  </si>
+  <si>
+    <t>2020年大前端技术趋势解读</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/338813991</t>
+  </si>
+  <si>
+    <t>【前端实时音视频系列】WebRTC入门概览</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/163280838</t>
+  </si>
+  <si>
+    <t>Serverless 中文社区采访</t>
+  </si>
+  <si>
+    <t>2020-06-24</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/150510751</t>
+  </si>
+  <si>
+    <t>SVG 菜鸟的 Recharts 自定义图表实战</t>
+  </si>
+  <si>
+    <t>2020-04-01</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/122477905</t>
+  </si>
+  <si>
+    <t>十分钟了解git那些“不常用”命令</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/122474549</t>
+  </si>
+  <si>
+    <t>nohost — 远程环境配置及抓包调试最佳实践</t>
+  </si>
+  <si>
+    <t>2019-12-27</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/99811711</t>
+  </si>
+  <si>
+    <t>企鹅辅导H5直播点播实践</t>
+  </si>
+  <si>
+    <t>2019-10-30</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/89301347</t>
+  </si>
+  <si>
+    <t>【TWeb前端盛会】腾讯前端技术大会，11月16日重磅来袭！</t>
+  </si>
+  <si>
+    <t>2019-10-16</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/86939486</t>
+  </si>
+  <si>
+    <t>畅销书《深入浅出Vue.js》作者，在阿里淘系6个月的收获成长</t>
+  </si>
+  <si>
+    <t>知乎-淘系前端团队</t>
+  </si>
+  <si>
+    <t>2020-12-08</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/334665881</t>
+  </si>
+  <si>
+    <t>Serverless ：让「前端开发者」走向「应用研发者」</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/340299272</t>
+  </si>
+  <si>
+    <t>从V8源码分析一个JS 数组的内存占用问题</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/342042184</t>
+  </si>
+  <si>
+    <t>2020天猫双11前端体系的建设与挑战</t>
+  </si>
+  <si>
+    <t>2020-11-17</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/297672686</t>
+  </si>
+  <si>
+    <t>在 Node.js 中 ”相对可靠” 的高效执行可信三方的代码</t>
+  </si>
+  <si>
+    <t>2020-11-11</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/285808027</t>
+  </si>
+  <si>
+    <t>2020年10月 Chrome 86 重要更新解读</t>
+  </si>
+  <si>
+    <t>2020-11-09</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/281009581</t>
+  </si>
+  <si>
+    <t>5个角度对比拆解 Flutter Widget 和 CSS 布局原理的差异</t>
+  </si>
+  <si>
+    <t>2020-11-04</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/273557876</t>
+  </si>
+  <si>
+    <t>一篇看完2020年CSS的24个新特性</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/267381937</t>
+  </si>
+  <si>
+    <t>Node.js AsyncHooks 与异步回调上下文</t>
+  </si>
+  <si>
+    <t>2020-10-09</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/263529297</t>
+  </si>
+  <si>
+    <t>混搭 TypeScript + GraphQL + Decorator 风格写 Node.js 应用</t>
+  </si>
+  <si>
+    <t>2020-09-29</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/260399804</t>
+  </si>
+  <si>
+    <t>前端工程师所需要了解的WebView</t>
+  </si>
+  <si>
+    <t>掘金-腾讯IMWeb团队</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6932083257286590477</t>
+  </si>
+  <si>
+    <t>关于双列瀑布流布局的优化思考</t>
+  </si>
+  <si>
+    <t>2021-01-25</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6921636695423057933</t>
+  </si>
+  <si>
+    <t>代码规模飙升，前端如何走好工程化之路？</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6917588945991630861</t>
+  </si>
+  <si>
+    <t>全栈大潮下，前端工程师如何走向全栈之路？</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6917448336022700046</t>
+  </si>
+  <si>
+    <t>大前端时代，低代码的潜力如何挖掘？</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6916860696131174413</t>
+  </si>
+  <si>
+    <t>视频应用井喷，前端音视频发展前景如何？</t>
+  </si>
+  <si>
+    <t>2021-01-12</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6916860661130199047</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6914213540572168205</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6912339953812766728</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6908713513271689224</t>
+  </si>
+  <si>
+    <t>IMWEB 一站式 Serverless 开发解决方案</t>
+  </si>
+  <si>
+    <t>2020-11-22</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6897112374541549581</t>
   </si>
 </sst>
 </file>
@@ -504,7 +3423,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E347"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -531,9 +3450,4853 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" t="s">
+        <v>60</v>
+      </c>
+      <c r="E24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" t="s">
+        <v>72</v>
+      </c>
+      <c r="E27" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" t="s">
+        <v>77</v>
+      </c>
+      <c r="E29" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>79</v>
+      </c>
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" t="s">
+        <v>77</v>
+      </c>
+      <c r="E30" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>81</v>
+      </c>
+      <c r="B31" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" t="s">
+        <v>77</v>
+      </c>
+      <c r="E31" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>83</v>
+      </c>
+      <c r="B32" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E32" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" t="s">
+        <v>87</v>
+      </c>
+      <c r="E33" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>89</v>
+      </c>
+      <c r="B34" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" t="s">
+        <v>87</v>
+      </c>
+      <c r="E34" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>91</v>
+      </c>
+      <c r="B35" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35" t="s">
+        <v>92</v>
+      </c>
+      <c r="E35" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>94</v>
+      </c>
+      <c r="B36" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" t="s">
+        <v>92</v>
+      </c>
+      <c r="E36" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>96</v>
+      </c>
+      <c r="B37" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" t="s">
+        <v>97</v>
+      </c>
+      <c r="E37" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>99</v>
+      </c>
+      <c r="B38" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" t="s">
+        <v>97</v>
+      </c>
+      <c r="E38" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>101</v>
+      </c>
+      <c r="B39" t="s">
+        <v>84</v>
+      </c>
+      <c r="C39" t="s">
+        <v>102</v>
+      </c>
+      <c r="E39" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>104</v>
+      </c>
+      <c r="B40" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" t="s">
+        <v>105</v>
+      </c>
+      <c r="E40" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>107</v>
+      </c>
+      <c r="B41" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" t="s">
+        <v>108</v>
+      </c>
+      <c r="E41" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>110</v>
+      </c>
+      <c r="B42" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" t="s">
+        <v>111</v>
+      </c>
+      <c r="E42" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>113</v>
+      </c>
+      <c r="B43" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" t="s">
+        <v>114</v>
+      </c>
+      <c r="E43" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>116</v>
+      </c>
+      <c r="B44" t="s">
+        <v>84</v>
+      </c>
+      <c r="C44" t="s">
+        <v>114</v>
+      </c>
+      <c r="E44" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>118</v>
+      </c>
+      <c r="B45" t="s">
+        <v>84</v>
+      </c>
+      <c r="C45" t="s">
+        <v>119</v>
+      </c>
+      <c r="E45" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>121</v>
+      </c>
+      <c r="B46" t="s">
+        <v>84</v>
+      </c>
+      <c r="C46" t="s">
+        <v>122</v>
+      </c>
+      <c r="E46" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>124</v>
+      </c>
+      <c r="B47" t="s">
+        <v>84</v>
+      </c>
+      <c r="C47" t="s">
+        <v>125</v>
+      </c>
+      <c r="E47" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>127</v>
+      </c>
+      <c r="B48" t="s">
+        <v>84</v>
+      </c>
+      <c r="C48" t="s">
+        <v>125</v>
+      </c>
+      <c r="E48" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" t="s">
+        <v>84</v>
+      </c>
+      <c r="C49" t="s">
+        <v>125</v>
+      </c>
+      <c r="E49" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>131</v>
+      </c>
+      <c r="B50" t="s">
+        <v>84</v>
+      </c>
+      <c r="C50" t="s">
+        <v>125</v>
+      </c>
+      <c r="E50" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>133</v>
+      </c>
+      <c r="B51" t="s">
+        <v>84</v>
+      </c>
+      <c r="C51" t="s">
+        <v>125</v>
+      </c>
+      <c r="E51" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>135</v>
+      </c>
+      <c r="B52" t="s">
+        <v>84</v>
+      </c>
+      <c r="C52" t="s">
+        <v>136</v>
+      </c>
+      <c r="E52" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>138</v>
+      </c>
+      <c r="B53" t="s">
+        <v>84</v>
+      </c>
+      <c r="C53" t="s">
+        <v>139</v>
+      </c>
+      <c r="E53" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>141</v>
+      </c>
+      <c r="B54" t="s">
+        <v>84</v>
+      </c>
+      <c r="C54" t="s">
+        <v>142</v>
+      </c>
+      <c r="E54" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>144</v>
+      </c>
+      <c r="B55" t="s">
+        <v>84</v>
+      </c>
+      <c r="C55" t="s">
+        <v>145</v>
+      </c>
+      <c r="E55" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>147</v>
+      </c>
+      <c r="B56" t="s">
+        <v>84</v>
+      </c>
+      <c r="C56" t="s">
+        <v>148</v>
+      </c>
+      <c r="E56" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>150</v>
+      </c>
+      <c r="B57" t="s">
+        <v>84</v>
+      </c>
+      <c r="C57" t="s">
+        <v>151</v>
+      </c>
+      <c r="E57" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>153</v>
+      </c>
+      <c r="B58" t="s">
+        <v>84</v>
+      </c>
+      <c r="C58" t="s">
+        <v>154</v>
+      </c>
+      <c r="E58" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>156</v>
+      </c>
+      <c r="B59" t="s">
+        <v>84</v>
+      </c>
+      <c r="C59" t="s">
+        <v>154</v>
+      </c>
+      <c r="E59" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>158</v>
+      </c>
+      <c r="B60" t="s">
+        <v>84</v>
+      </c>
+      <c r="C60" t="s">
+        <v>159</v>
+      </c>
+      <c r="E60" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>161</v>
+      </c>
+      <c r="B61" t="s">
+        <v>84</v>
+      </c>
+      <c r="C61" t="s">
+        <v>162</v>
+      </c>
+      <c r="E61" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>164</v>
+      </c>
+      <c r="B62" t="s">
+        <v>84</v>
+      </c>
+      <c r="C62" t="s">
+        <v>165</v>
+      </c>
+      <c r="E62" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>167</v>
+      </c>
+      <c r="B63" t="s">
+        <v>84</v>
+      </c>
+      <c r="C63" t="s">
+        <v>168</v>
+      </c>
+      <c r="E63" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>170</v>
+      </c>
+      <c r="B64" t="s">
+        <v>84</v>
+      </c>
+      <c r="C64" t="s">
+        <v>168</v>
+      </c>
+      <c r="E64" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>172</v>
+      </c>
+      <c r="B65" t="s">
+        <v>84</v>
+      </c>
+      <c r="C65" t="s">
+        <v>173</v>
+      </c>
+      <c r="E65" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>175</v>
+      </c>
+      <c r="B66" t="s">
+        <v>84</v>
+      </c>
+      <c r="C66" t="s">
+        <v>176</v>
+      </c>
+      <c r="E66" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>178</v>
+      </c>
+      <c r="B67" t="s">
+        <v>84</v>
+      </c>
+      <c r="C67" t="s">
+        <v>179</v>
+      </c>
+      <c r="E67" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>181</v>
+      </c>
+      <c r="B68" t="s">
+        <v>84</v>
+      </c>
+      <c r="C68" t="s">
+        <v>182</v>
+      </c>
+      <c r="E68" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>184</v>
+      </c>
+      <c r="B69" t="s">
+        <v>84</v>
+      </c>
+      <c r="C69" t="s">
+        <v>185</v>
+      </c>
+      <c r="E69" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>187</v>
+      </c>
+      <c r="B70" t="s">
+        <v>84</v>
+      </c>
+      <c r="C70" t="s">
+        <v>185</v>
+      </c>
+      <c r="E70" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>189</v>
+      </c>
+      <c r="B71" t="s">
+        <v>84</v>
+      </c>
+      <c r="C71" t="s">
+        <v>190</v>
+      </c>
+      <c r="E71" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>192</v>
+      </c>
+      <c r="B72" t="s">
+        <v>84</v>
+      </c>
+      <c r="C72" t="s">
+        <v>193</v>
+      </c>
+      <c r="E72" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>195</v>
+      </c>
+      <c r="B73" t="s">
+        <v>84</v>
+      </c>
+      <c r="C73" t="s">
+        <v>196</v>
+      </c>
+      <c r="E73" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>198</v>
+      </c>
+      <c r="B74" t="s">
+        <v>84</v>
+      </c>
+      <c r="C74" t="s">
+        <v>196</v>
+      </c>
+      <c r="E74" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>200</v>
+      </c>
+      <c r="B75" t="s">
+        <v>84</v>
+      </c>
+      <c r="C75" t="s">
+        <v>201</v>
+      </c>
+      <c r="E75" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>203</v>
+      </c>
+      <c r="B76" t="s">
+        <v>84</v>
+      </c>
+      <c r="C76" t="s">
+        <v>204</v>
+      </c>
+      <c r="E76" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>206</v>
+      </c>
+      <c r="B77" t="s">
+        <v>84</v>
+      </c>
+      <c r="C77" t="s">
+        <v>207</v>
+      </c>
+      <c r="E77" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>209</v>
+      </c>
+      <c r="B78" t="s">
+        <v>84</v>
+      </c>
+      <c r="C78" t="s">
+        <v>210</v>
+      </c>
+      <c r="E78" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>212</v>
+      </c>
+      <c r="B79" t="s">
+        <v>84</v>
+      </c>
+      <c r="C79" t="s">
+        <v>213</v>
+      </c>
+      <c r="E79" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>215</v>
+      </c>
+      <c r="B80" t="s">
+        <v>84</v>
+      </c>
+      <c r="C80" t="s">
+        <v>213</v>
+      </c>
+      <c r="E80" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>217</v>
+      </c>
+      <c r="B81" t="s">
+        <v>84</v>
+      </c>
+      <c r="C81" t="s">
+        <v>218</v>
+      </c>
+      <c r="E81" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>220</v>
+      </c>
+      <c r="B82" t="s">
+        <v>84</v>
+      </c>
+      <c r="C82" t="s">
+        <v>221</v>
+      </c>
+      <c r="E82" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>223</v>
+      </c>
+      <c r="B83" t="s">
+        <v>84</v>
+      </c>
+      <c r="C83" t="s">
+        <v>224</v>
+      </c>
+      <c r="E83" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>226</v>
+      </c>
+      <c r="B84" t="s">
+        <v>84</v>
+      </c>
+      <c r="C84" t="s">
+        <v>227</v>
+      </c>
+      <c r="E84" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>229</v>
+      </c>
+      <c r="B85" t="s">
+        <v>84</v>
+      </c>
+      <c r="C85" t="s">
+        <v>230</v>
+      </c>
+      <c r="E85" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>232</v>
+      </c>
+      <c r="B86" t="s">
+        <v>84</v>
+      </c>
+      <c r="C86" t="s">
+        <v>233</v>
+      </c>
+      <c r="E86" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>235</v>
+      </c>
+      <c r="B87" t="s">
+        <v>84</v>
+      </c>
+      <c r="C87" t="s">
+        <v>236</v>
+      </c>
+      <c r="E87" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>238</v>
+      </c>
+      <c r="B88" t="s">
+        <v>84</v>
+      </c>
+      <c r="C88" t="s">
+        <v>239</v>
+      </c>
+      <c r="E88" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>241</v>
+      </c>
+      <c r="B89" t="s">
+        <v>84</v>
+      </c>
+      <c r="C89" t="s">
+        <v>242</v>
+      </c>
+      <c r="E89" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>244</v>
+      </c>
+      <c r="B90" t="s">
+        <v>84</v>
+      </c>
+      <c r="C90" t="s">
+        <v>245</v>
+      </c>
+      <c r="E90" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>247</v>
+      </c>
+      <c r="B91" t="s">
+        <v>84</v>
+      </c>
+      <c r="C91" t="s">
+        <v>248</v>
+      </c>
+      <c r="E91" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>250</v>
+      </c>
+      <c r="B92" t="s">
+        <v>84</v>
+      </c>
+      <c r="C92" t="s">
+        <v>251</v>
+      </c>
+      <c r="E92" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>253</v>
+      </c>
+      <c r="B93" t="s">
+        <v>84</v>
+      </c>
+      <c r="C93" t="s">
+        <v>254</v>
+      </c>
+      <c r="E93" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>256</v>
+      </c>
+      <c r="B94" t="s">
+        <v>84</v>
+      </c>
+      <c r="C94" t="s">
+        <v>257</v>
+      </c>
+      <c r="E94" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>259</v>
+      </c>
+      <c r="B95" t="s">
+        <v>84</v>
+      </c>
+      <c r="C95" t="s">
+        <v>260</v>
+      </c>
+      <c r="E95" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>262</v>
+      </c>
+      <c r="B96" t="s">
+        <v>84</v>
+      </c>
+      <c r="C96" t="s">
+        <v>263</v>
+      </c>
+      <c r="E96" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>265</v>
+      </c>
+      <c r="B97" t="s">
+        <v>84</v>
+      </c>
+      <c r="C97" t="s">
+        <v>266</v>
+      </c>
+      <c r="E97" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>268</v>
+      </c>
+      <c r="B98" t="s">
+        <v>84</v>
+      </c>
+      <c r="C98" t="s">
+        <v>269</v>
+      </c>
+      <c r="E98" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>271</v>
+      </c>
+      <c r="B99" t="s">
+        <v>84</v>
+      </c>
+      <c r="C99" t="s">
+        <v>272</v>
+      </c>
+      <c r="E99" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>274</v>
+      </c>
+      <c r="B100" t="s">
+        <v>84</v>
+      </c>
+      <c r="C100" t="s">
+        <v>275</v>
+      </c>
+      <c r="E100" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>277</v>
+      </c>
+      <c r="B101" t="s">
+        <v>84</v>
+      </c>
+      <c r="C101" t="s">
+        <v>278</v>
+      </c>
+      <c r="E101" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>280</v>
+      </c>
+      <c r="B102" t="s">
+        <v>84</v>
+      </c>
+      <c r="C102" t="s">
+        <v>281</v>
+      </c>
+      <c r="E102" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>283</v>
+      </c>
+      <c r="B103" t="s">
+        <v>84</v>
+      </c>
+      <c r="C103" t="s">
+        <v>284</v>
+      </c>
+      <c r="E103" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>286</v>
+      </c>
+      <c r="B104" t="s">
+        <v>84</v>
+      </c>
+      <c r="C104" t="s">
+        <v>287</v>
+      </c>
+      <c r="E104" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>289</v>
+      </c>
+      <c r="B105" t="s">
+        <v>84</v>
+      </c>
+      <c r="C105" t="s">
+        <v>290</v>
+      </c>
+      <c r="E105" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>292</v>
+      </c>
+      <c r="B106" t="s">
+        <v>84</v>
+      </c>
+      <c r="C106" t="s">
+        <v>293</v>
+      </c>
+      <c r="E106" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>295</v>
+      </c>
+      <c r="B107" t="s">
+        <v>84</v>
+      </c>
+      <c r="C107" t="s">
+        <v>296</v>
+      </c>
+      <c r="E107" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>298</v>
+      </c>
+      <c r="B108" t="s">
+        <v>84</v>
+      </c>
+      <c r="C108" t="s">
+        <v>299</v>
+      </c>
+      <c r="E108" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>301</v>
+      </c>
+      <c r="B109" t="s">
+        <v>84</v>
+      </c>
+      <c r="C109" t="s">
+        <v>302</v>
+      </c>
+      <c r="E109" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>304</v>
+      </c>
+      <c r="B110" t="s">
+        <v>84</v>
+      </c>
+      <c r="C110" t="s">
+        <v>305</v>
+      </c>
+      <c r="E110" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>307</v>
+      </c>
+      <c r="B111" t="s">
+        <v>84</v>
+      </c>
+      <c r="C111" t="s">
+        <v>308</v>
+      </c>
+      <c r="E111" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>310</v>
+      </c>
+      <c r="B112" t="s">
+        <v>84</v>
+      </c>
+      <c r="C112" t="s">
+        <v>311</v>
+      </c>
+      <c r="E112" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>313</v>
+      </c>
+      <c r="B113" t="s">
+        <v>84</v>
+      </c>
+      <c r="C113" t="s">
+        <v>314</v>
+      </c>
+      <c r="E113" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>316</v>
+      </c>
+      <c r="B114" t="s">
+        <v>84</v>
+      </c>
+      <c r="C114" t="s">
+        <v>317</v>
+      </c>
+      <c r="E114" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>319</v>
+      </c>
+      <c r="B115" t="s">
+        <v>84</v>
+      </c>
+      <c r="C115" t="s">
+        <v>320</v>
+      </c>
+      <c r="E115" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>322</v>
+      </c>
+      <c r="B116" t="s">
+        <v>84</v>
+      </c>
+      <c r="C116" t="s">
+        <v>323</v>
+      </c>
+      <c r="E116" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>325</v>
+      </c>
+      <c r="B117" t="s">
+        <v>84</v>
+      </c>
+      <c r="C117" t="s">
+        <v>326</v>
+      </c>
+      <c r="E117" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>328</v>
+      </c>
+      <c r="B118" t="s">
+        <v>84</v>
+      </c>
+      <c r="C118" t="s">
+        <v>329</v>
+      </c>
+      <c r="E118" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>331</v>
+      </c>
+      <c r="B119" t="s">
+        <v>84</v>
+      </c>
+      <c r="C119" t="s">
+        <v>332</v>
+      </c>
+      <c r="E119" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>334</v>
+      </c>
+      <c r="B120" t="s">
+        <v>84</v>
+      </c>
+      <c r="C120" t="s">
+        <v>335</v>
+      </c>
+      <c r="E120" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>337</v>
+      </c>
+      <c r="B121" t="s">
+        <v>84</v>
+      </c>
+      <c r="C121" t="s">
+        <v>338</v>
+      </c>
+      <c r="E121" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>340</v>
+      </c>
+      <c r="B122" t="s">
+        <v>84</v>
+      </c>
+      <c r="C122" t="s">
+        <v>341</v>
+      </c>
+      <c r="E122" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>343</v>
+      </c>
+      <c r="B123" t="s">
+        <v>84</v>
+      </c>
+      <c r="C123" t="s">
+        <v>344</v>
+      </c>
+      <c r="E123" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>346</v>
+      </c>
+      <c r="B124" t="s">
+        <v>84</v>
+      </c>
+      <c r="C124" t="s">
+        <v>347</v>
+      </c>
+      <c r="E124" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>349</v>
+      </c>
+      <c r="B125" t="s">
+        <v>84</v>
+      </c>
+      <c r="C125" t="s">
+        <v>350</v>
+      </c>
+      <c r="E125" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>352</v>
+      </c>
+      <c r="B126" t="s">
+        <v>84</v>
+      </c>
+      <c r="C126" t="s">
+        <v>353</v>
+      </c>
+      <c r="E126" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>355</v>
+      </c>
+      <c r="B127" t="s">
+        <v>84</v>
+      </c>
+      <c r="C127" t="s">
+        <v>356</v>
+      </c>
+      <c r="E127" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>358</v>
+      </c>
+      <c r="B128" t="s">
+        <v>84</v>
+      </c>
+      <c r="C128" t="s">
+        <v>359</v>
+      </c>
+      <c r="E128" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>361</v>
+      </c>
+      <c r="B129" t="s">
+        <v>84</v>
+      </c>
+      <c r="C129" t="s">
+        <v>362</v>
+      </c>
+      <c r="E129" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>364</v>
+      </c>
+      <c r="B130" t="s">
+        <v>84</v>
+      </c>
+      <c r="C130" t="s">
+        <v>365</v>
+      </c>
+      <c r="E130" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>367</v>
+      </c>
+      <c r="B131" t="s">
+        <v>84</v>
+      </c>
+      <c r="C131" t="s">
+        <v>368</v>
+      </c>
+      <c r="E131" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>370</v>
+      </c>
+      <c r="B132" t="s">
+        <v>84</v>
+      </c>
+      <c r="C132" t="s">
+        <v>371</v>
+      </c>
+      <c r="E132" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>373</v>
+      </c>
+      <c r="B133" t="s">
+        <v>84</v>
+      </c>
+      <c r="C133" t="s">
+        <v>374</v>
+      </c>
+      <c r="E133" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>376</v>
+      </c>
+      <c r="B134" t="s">
+        <v>84</v>
+      </c>
+      <c r="C134" t="s">
+        <v>377</v>
+      </c>
+      <c r="E134" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>379</v>
+      </c>
+      <c r="B135" t="s">
+        <v>84</v>
+      </c>
+      <c r="C135" t="s">
+        <v>377</v>
+      </c>
+      <c r="E135" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>381</v>
+      </c>
+      <c r="B136" t="s">
+        <v>84</v>
+      </c>
+      <c r="C136" t="s">
+        <v>382</v>
+      </c>
+      <c r="E136" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>384</v>
+      </c>
+      <c r="B137" t="s">
+        <v>84</v>
+      </c>
+      <c r="C137" t="s">
+        <v>385</v>
+      </c>
+      <c r="E137" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>387</v>
+      </c>
+      <c r="B138" t="s">
+        <v>84</v>
+      </c>
+      <c r="C138" t="s">
+        <v>388</v>
+      </c>
+      <c r="E138" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>390</v>
+      </c>
+      <c r="B139" t="s">
+        <v>84</v>
+      </c>
+      <c r="C139" t="s">
+        <v>391</v>
+      </c>
+      <c r="E139" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>393</v>
+      </c>
+      <c r="B140" t="s">
+        <v>84</v>
+      </c>
+      <c r="C140" t="s">
+        <v>394</v>
+      </c>
+      <c r="E140" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>396</v>
+      </c>
+      <c r="B141" t="s">
+        <v>84</v>
+      </c>
+      <c r="C141" t="s">
+        <v>394</v>
+      </c>
+      <c r="E141" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>398</v>
+      </c>
+      <c r="B142" t="s">
+        <v>84</v>
+      </c>
+      <c r="C142" t="s">
+        <v>399</v>
+      </c>
+      <c r="E142" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>401</v>
+      </c>
+      <c r="B143" t="s">
+        <v>84</v>
+      </c>
+      <c r="C143" t="s">
+        <v>402</v>
+      </c>
+      <c r="E143" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>404</v>
+      </c>
+      <c r="B144" t="s">
+        <v>84</v>
+      </c>
+      <c r="C144" t="s">
+        <v>402</v>
+      </c>
+      <c r="E144" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>406</v>
+      </c>
+      <c r="B145" t="s">
+        <v>84</v>
+      </c>
+      <c r="C145" t="s">
+        <v>407</v>
+      </c>
+      <c r="E145" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>409</v>
+      </c>
+      <c r="B146" t="s">
+        <v>84</v>
+      </c>
+      <c r="C146" t="s">
+        <v>410</v>
+      </c>
+      <c r="E146" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>412</v>
+      </c>
+      <c r="B147" t="s">
+        <v>84</v>
+      </c>
+      <c r="C147" t="s">
+        <v>413</v>
+      </c>
+      <c r="E147" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>415</v>
+      </c>
+      <c r="B148" t="s">
+        <v>84</v>
+      </c>
+      <c r="C148" t="s">
+        <v>416</v>
+      </c>
+      <c r="E148" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>418</v>
+      </c>
+      <c r="B149" t="s">
+        <v>84</v>
+      </c>
+      <c r="C149" t="s">
+        <v>416</v>
+      </c>
+      <c r="E149" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>420</v>
+      </c>
+      <c r="B150" t="s">
+        <v>84</v>
+      </c>
+      <c r="C150" t="s">
+        <v>421</v>
+      </c>
+      <c r="E150" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>423</v>
+      </c>
+      <c r="B151" t="s">
+        <v>84</v>
+      </c>
+      <c r="C151" t="s">
+        <v>424</v>
+      </c>
+      <c r="E151" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>426</v>
+      </c>
+      <c r="B152" t="s">
+        <v>84</v>
+      </c>
+      <c r="C152" t="s">
+        <v>427</v>
+      </c>
+      <c r="E152" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>429</v>
+      </c>
+      <c r="B153" t="s">
+        <v>84</v>
+      </c>
+      <c r="C153" t="s">
+        <v>430</v>
+      </c>
+      <c r="E153" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>432</v>
+      </c>
+      <c r="B154" t="s">
+        <v>84</v>
+      </c>
+      <c r="C154" t="s">
+        <v>433</v>
+      </c>
+      <c r="E154" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>435</v>
+      </c>
+      <c r="B155" t="s">
+        <v>84</v>
+      </c>
+      <c r="C155" t="s">
+        <v>436</v>
+      </c>
+      <c r="E155" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>438</v>
+      </c>
+      <c r="B156" t="s">
+        <v>84</v>
+      </c>
+      <c r="C156" t="s">
+        <v>439</v>
+      </c>
+      <c r="E156" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>441</v>
+      </c>
+      <c r="B157" t="s">
+        <v>84</v>
+      </c>
+      <c r="C157" t="s">
+        <v>442</v>
+      </c>
+      <c r="E157" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>444</v>
+      </c>
+      <c r="B158" t="s">
+        <v>84</v>
+      </c>
+      <c r="C158" t="s">
+        <v>445</v>
+      </c>
+      <c r="E158" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>447</v>
+      </c>
+      <c r="B159" t="s">
+        <v>84</v>
+      </c>
+      <c r="C159" t="s">
+        <v>448</v>
+      </c>
+      <c r="E159" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>450</v>
+      </c>
+      <c r="B160" t="s">
+        <v>84</v>
+      </c>
+      <c r="C160" t="s">
+        <v>451</v>
+      </c>
+      <c r="E160" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>453</v>
+      </c>
+      <c r="B161" t="s">
+        <v>84</v>
+      </c>
+      <c r="C161" t="s">
+        <v>454</v>
+      </c>
+      <c r="E161" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>456</v>
+      </c>
+      <c r="B162" t="s">
+        <v>84</v>
+      </c>
+      <c r="C162" t="s">
+        <v>457</v>
+      </c>
+      <c r="E162" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>459</v>
+      </c>
+      <c r="B163" t="s">
+        <v>84</v>
+      </c>
+      <c r="C163" t="s">
+        <v>457</v>
+      </c>
+      <c r="E163" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>461</v>
+      </c>
+      <c r="B164" t="s">
+        <v>84</v>
+      </c>
+      <c r="C164" t="s">
+        <v>462</v>
+      </c>
+      <c r="E164" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>464</v>
+      </c>
+      <c r="B165" t="s">
+        <v>84</v>
+      </c>
+      <c r="C165" t="s">
+        <v>465</v>
+      </c>
+      <c r="E165" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>467</v>
+      </c>
+      <c r="B166" t="s">
+        <v>84</v>
+      </c>
+      <c r="C166" t="s">
+        <v>468</v>
+      </c>
+      <c r="E166" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>470</v>
+      </c>
+      <c r="B167" t="s">
+        <v>84</v>
+      </c>
+      <c r="C167" t="s">
+        <v>471</v>
+      </c>
+      <c r="E167" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>473</v>
+      </c>
+      <c r="B168" t="s">
+        <v>84</v>
+      </c>
+      <c r="C168" t="s">
+        <v>474</v>
+      </c>
+      <c r="E168" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>476</v>
+      </c>
+      <c r="B169" t="s">
+        <v>84</v>
+      </c>
+      <c r="C169" t="s">
+        <v>477</v>
+      </c>
+      <c r="E169" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>479</v>
+      </c>
+      <c r="B170" t="s">
+        <v>84</v>
+      </c>
+      <c r="C170" t="s">
+        <v>480</v>
+      </c>
+      <c r="E170" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>482</v>
+      </c>
+      <c r="B171" t="s">
+        <v>84</v>
+      </c>
+      <c r="C171" t="s">
+        <v>480</v>
+      </c>
+      <c r="E171" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>484</v>
+      </c>
+      <c r="B172" t="s">
+        <v>84</v>
+      </c>
+      <c r="C172" t="s">
+        <v>485</v>
+      </c>
+      <c r="E172" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>487</v>
+      </c>
+      <c r="B173" t="s">
+        <v>84</v>
+      </c>
+      <c r="C173" t="s">
+        <v>488</v>
+      </c>
+      <c r="E173" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>490</v>
+      </c>
+      <c r="B174" t="s">
+        <v>84</v>
+      </c>
+      <c r="C174" t="s">
+        <v>491</v>
+      </c>
+      <c r="E174" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>493</v>
+      </c>
+      <c r="B175" t="s">
+        <v>84</v>
+      </c>
+      <c r="C175" t="s">
+        <v>494</v>
+      </c>
+      <c r="E175" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>496</v>
+      </c>
+      <c r="B176" t="s">
+        <v>84</v>
+      </c>
+      <c r="C176" t="s">
+        <v>497</v>
+      </c>
+      <c r="E176" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>499</v>
+      </c>
+      <c r="B177" t="s">
+        <v>84</v>
+      </c>
+      <c r="C177" t="s">
+        <v>500</v>
+      </c>
+      <c r="E177" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>502</v>
+      </c>
+      <c r="B178" t="s">
+        <v>84</v>
+      </c>
+      <c r="C178" t="s">
+        <v>503</v>
+      </c>
+      <c r="E178" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>505</v>
+      </c>
+      <c r="B179" t="s">
+        <v>84</v>
+      </c>
+      <c r="C179" t="s">
+        <v>506</v>
+      </c>
+      <c r="E179" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>508</v>
+      </c>
+      <c r="B180" t="s">
+        <v>84</v>
+      </c>
+      <c r="C180" t="s">
+        <v>509</v>
+      </c>
+      <c r="E180" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>511</v>
+      </c>
+      <c r="B181" t="s">
+        <v>84</v>
+      </c>
+      <c r="C181" t="s">
+        <v>512</v>
+      </c>
+      <c r="E181" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>514</v>
+      </c>
+      <c r="B182" t="s">
+        <v>84</v>
+      </c>
+      <c r="C182" t="s">
+        <v>515</v>
+      </c>
+      <c r="E182" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>517</v>
+      </c>
+      <c r="B183" t="s">
+        <v>84</v>
+      </c>
+      <c r="C183" t="s">
+        <v>518</v>
+      </c>
+      <c r="E183" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>520</v>
+      </c>
+      <c r="B184" t="s">
+        <v>84</v>
+      </c>
+      <c r="C184" t="s">
+        <v>521</v>
+      </c>
+      <c r="E184" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>523</v>
+      </c>
+      <c r="B185" t="s">
+        <v>84</v>
+      </c>
+      <c r="C185" t="s">
+        <v>521</v>
+      </c>
+      <c r="E185" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>525</v>
+      </c>
+      <c r="B186" t="s">
+        <v>84</v>
+      </c>
+      <c r="C186" t="s">
+        <v>526</v>
+      </c>
+      <c r="E186" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>528</v>
+      </c>
+      <c r="B187" t="s">
+        <v>84</v>
+      </c>
+      <c r="C187" t="s">
+        <v>529</v>
+      </c>
+      <c r="E187" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>531</v>
+      </c>
+      <c r="B188" t="s">
+        <v>84</v>
+      </c>
+      <c r="C188" t="s">
+        <v>532</v>
+      </c>
+      <c r="E188" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>534</v>
+      </c>
+      <c r="B189" t="s">
+        <v>84</v>
+      </c>
+      <c r="C189" t="s">
+        <v>535</v>
+      </c>
+      <c r="E189" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>537</v>
+      </c>
+      <c r="B190" t="s">
+        <v>84</v>
+      </c>
+      <c r="C190" t="s">
+        <v>535</v>
+      </c>
+      <c r="E190" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>539</v>
+      </c>
+      <c r="B191" t="s">
+        <v>84</v>
+      </c>
+      <c r="C191" t="s">
+        <v>540</v>
+      </c>
+      <c r="E191" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>542</v>
+      </c>
+      <c r="B192" t="s">
+        <v>84</v>
+      </c>
+      <c r="C192" t="s">
+        <v>543</v>
+      </c>
+      <c r="E192" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>545</v>
+      </c>
+      <c r="B193" t="s">
+        <v>84</v>
+      </c>
+      <c r="C193" t="s">
+        <v>546</v>
+      </c>
+      <c r="E193" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>548</v>
+      </c>
+      <c r="B194" t="s">
+        <v>84</v>
+      </c>
+      <c r="C194" t="s">
+        <v>546</v>
+      </c>
+      <c r="E194" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>550</v>
+      </c>
+      <c r="B195" t="s">
+        <v>84</v>
+      </c>
+      <c r="C195" t="s">
+        <v>551</v>
+      </c>
+      <c r="E195" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>553</v>
+      </c>
+      <c r="B196" t="s">
+        <v>84</v>
+      </c>
+      <c r="C196" t="s">
+        <v>554</v>
+      </c>
+      <c r="E196" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>556</v>
+      </c>
+      <c r="B197" t="s">
+        <v>84</v>
+      </c>
+      <c r="C197" t="s">
+        <v>554</v>
+      </c>
+      <c r="E197" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>558</v>
+      </c>
+      <c r="B198" t="s">
+        <v>84</v>
+      </c>
+      <c r="C198" t="s">
+        <v>559</v>
+      </c>
+      <c r="E198" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>561</v>
+      </c>
+      <c r="B199" t="s">
+        <v>84</v>
+      </c>
+      <c r="C199" t="s">
+        <v>562</v>
+      </c>
+      <c r="E199" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>564</v>
+      </c>
+      <c r="B200" t="s">
+        <v>84</v>
+      </c>
+      <c r="C200" t="s">
+        <v>565</v>
+      </c>
+      <c r="E200" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>567</v>
+      </c>
+      <c r="B201" t="s">
+        <v>84</v>
+      </c>
+      <c r="C201" t="s">
+        <v>568</v>
+      </c>
+      <c r="E201" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>570</v>
+      </c>
+      <c r="B202" t="s">
+        <v>84</v>
+      </c>
+      <c r="C202" t="s">
+        <v>571</v>
+      </c>
+      <c r="E202" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>573</v>
+      </c>
+      <c r="B203" t="s">
+        <v>84</v>
+      </c>
+      <c r="C203" t="s">
+        <v>574</v>
+      </c>
+      <c r="E203" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>576</v>
+      </c>
+      <c r="B204" t="s">
+        <v>84</v>
+      </c>
+      <c r="C204" t="s">
+        <v>577</v>
+      </c>
+      <c r="E204" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>579</v>
+      </c>
+      <c r="B205" t="s">
+        <v>84</v>
+      </c>
+      <c r="C205" t="s">
+        <v>577</v>
+      </c>
+      <c r="E205" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>581</v>
+      </c>
+      <c r="B206" t="s">
+        <v>84</v>
+      </c>
+      <c r="C206" t="s">
+        <v>582</v>
+      </c>
+      <c r="E206" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>584</v>
+      </c>
+      <c r="B207" t="s">
+        <v>84</v>
+      </c>
+      <c r="C207" t="s">
+        <v>585</v>
+      </c>
+      <c r="E207" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>587</v>
+      </c>
+      <c r="B208" t="s">
+        <v>84</v>
+      </c>
+      <c r="C208" t="s">
+        <v>588</v>
+      </c>
+      <c r="E208" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>590</v>
+      </c>
+      <c r="B209" t="s">
+        <v>84</v>
+      </c>
+      <c r="C209" t="s">
+        <v>588</v>
+      </c>
+      <c r="E209" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>592</v>
+      </c>
+      <c r="B210" t="s">
+        <v>84</v>
+      </c>
+      <c r="C210" t="s">
+        <v>593</v>
+      </c>
+      <c r="E210" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>595</v>
+      </c>
+      <c r="B211" t="s">
+        <v>84</v>
+      </c>
+      <c r="C211" t="s">
+        <v>596</v>
+      </c>
+      <c r="E211" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>598</v>
+      </c>
+      <c r="B212" t="s">
+        <v>84</v>
+      </c>
+      <c r="C212" t="s">
+        <v>599</v>
+      </c>
+      <c r="E212" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>601</v>
+      </c>
+      <c r="B213" t="s">
+        <v>84</v>
+      </c>
+      <c r="C213" t="s">
+        <v>602</v>
+      </c>
+      <c r="E213" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>604</v>
+      </c>
+      <c r="B214" t="s">
+        <v>84</v>
+      </c>
+      <c r="C214" t="s">
+        <v>605</v>
+      </c>
+      <c r="E214" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>607</v>
+      </c>
+      <c r="B215" t="s">
+        <v>84</v>
+      </c>
+      <c r="C215" t="s">
+        <v>608</v>
+      </c>
+      <c r="E215" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>610</v>
+      </c>
+      <c r="B216" t="s">
+        <v>84</v>
+      </c>
+      <c r="C216" t="s">
+        <v>611</v>
+      </c>
+      <c r="E216" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>613</v>
+      </c>
+      <c r="B217" t="s">
+        <v>84</v>
+      </c>
+      <c r="C217" t="s">
+        <v>614</v>
+      </c>
+      <c r="E217" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>616</v>
+      </c>
+      <c r="B218" t="s">
+        <v>84</v>
+      </c>
+      <c r="C218" t="s">
+        <v>617</v>
+      </c>
+      <c r="E218" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>619</v>
+      </c>
+      <c r="B219" t="s">
+        <v>84</v>
+      </c>
+      <c r="C219" t="s">
+        <v>620</v>
+      </c>
+      <c r="E219" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>622</v>
+      </c>
+      <c r="B220" t="s">
+        <v>84</v>
+      </c>
+      <c r="C220" t="s">
+        <v>623</v>
+      </c>
+      <c r="E220" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>625</v>
+      </c>
+      <c r="B221" t="s">
+        <v>84</v>
+      </c>
+      <c r="C221" t="s">
+        <v>626</v>
+      </c>
+      <c r="E221" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>628</v>
+      </c>
+      <c r="B222" t="s">
+        <v>84</v>
+      </c>
+      <c r="C222" t="s">
+        <v>629</v>
+      </c>
+      <c r="E222" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>631</v>
+      </c>
+      <c r="B223" t="s">
+        <v>84</v>
+      </c>
+      <c r="C223" t="s">
+        <v>632</v>
+      </c>
+      <c r="E223" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>634</v>
+      </c>
+      <c r="B224" t="s">
+        <v>84</v>
+      </c>
+      <c r="C224" t="s">
+        <v>635</v>
+      </c>
+      <c r="E224" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>637</v>
+      </c>
+      <c r="B225" t="s">
+        <v>84</v>
+      </c>
+      <c r="C225" t="s">
+        <v>638</v>
+      </c>
+      <c r="E225" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>640</v>
+      </c>
+      <c r="B226" t="s">
+        <v>84</v>
+      </c>
+      <c r="C226" t="s">
+        <v>638</v>
+      </c>
+      <c r="E226" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>642</v>
+      </c>
+      <c r="B227" t="s">
+        <v>84</v>
+      </c>
+      <c r="C227" t="s">
+        <v>643</v>
+      </c>
+      <c r="E227" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>645</v>
+      </c>
+      <c r="B228" t="s">
+        <v>84</v>
+      </c>
+      <c r="C228" t="s">
+        <v>646</v>
+      </c>
+      <c r="E228" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>648</v>
+      </c>
+      <c r="B229" t="s">
+        <v>84</v>
+      </c>
+      <c r="C229" t="s">
+        <v>649</v>
+      </c>
+      <c r="E229" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>651</v>
+      </c>
+      <c r="B230" t="s">
+        <v>84</v>
+      </c>
+      <c r="C230" t="s">
+        <v>649</v>
+      </c>
+      <c r="E230" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>653</v>
+      </c>
+      <c r="B231" t="s">
+        <v>84</v>
+      </c>
+      <c r="C231" t="s">
+        <v>654</v>
+      </c>
+      <c r="E231" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>656</v>
+      </c>
+      <c r="B232" t="s">
+        <v>84</v>
+      </c>
+      <c r="C232" t="s">
+        <v>657</v>
+      </c>
+      <c r="E232" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>659</v>
+      </c>
+      <c r="B233" t="s">
+        <v>84</v>
+      </c>
+      <c r="C233" t="s">
+        <v>660</v>
+      </c>
+      <c r="E233" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>662</v>
+      </c>
+      <c r="B234" t="s">
+        <v>84</v>
+      </c>
+      <c r="C234" t="s">
+        <v>663</v>
+      </c>
+      <c r="E234" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>665</v>
+      </c>
+      <c r="B235" t="s">
+        <v>84</v>
+      </c>
+      <c r="C235" t="s">
+        <v>666</v>
+      </c>
+      <c r="E235" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>668</v>
+      </c>
+      <c r="B236" t="s">
+        <v>84</v>
+      </c>
+      <c r="C236" t="s">
+        <v>669</v>
+      </c>
+      <c r="E236" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>671</v>
+      </c>
+      <c r="B237" t="s">
+        <v>84</v>
+      </c>
+      <c r="C237" t="s">
+        <v>672</v>
+      </c>
+      <c r="E237" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>674</v>
+      </c>
+      <c r="B238" t="s">
+        <v>84</v>
+      </c>
+      <c r="C238" t="s">
+        <v>675</v>
+      </c>
+      <c r="E238" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>677</v>
+      </c>
+      <c r="B239" t="s">
+        <v>84</v>
+      </c>
+      <c r="C239" t="s">
+        <v>678</v>
+      </c>
+      <c r="E239" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>680</v>
+      </c>
+      <c r="B240" t="s">
+        <v>84</v>
+      </c>
+      <c r="C240" t="s">
+        <v>681</v>
+      </c>
+      <c r="E240" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>683</v>
+      </c>
+      <c r="B241" t="s">
+        <v>84</v>
+      </c>
+      <c r="C241" t="s">
+        <v>684</v>
+      </c>
+      <c r="E241" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>686</v>
+      </c>
+      <c r="B242" t="s">
+        <v>84</v>
+      </c>
+      <c r="C242" t="s">
+        <v>687</v>
+      </c>
+      <c r="E242" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>689</v>
+      </c>
+      <c r="B243" t="s">
+        <v>84</v>
+      </c>
+      <c r="C243" t="s">
+        <v>690</v>
+      </c>
+      <c r="E243" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>692</v>
+      </c>
+      <c r="B244" t="s">
+        <v>84</v>
+      </c>
+      <c r="C244" t="s">
+        <v>693</v>
+      </c>
+      <c r="E244" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>695</v>
+      </c>
+      <c r="B245" t="s">
+        <v>84</v>
+      </c>
+      <c r="C245" t="s">
+        <v>696</v>
+      </c>
+      <c r="E245" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>698</v>
+      </c>
+      <c r="B246" t="s">
+        <v>84</v>
+      </c>
+      <c r="C246" t="s">
+        <v>699</v>
+      </c>
+      <c r="E246" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>701</v>
+      </c>
+      <c r="B247" t="s">
+        <v>84</v>
+      </c>
+      <c r="C247" t="s">
+        <v>702</v>
+      </c>
+      <c r="E247" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>704</v>
+      </c>
+      <c r="B248" t="s">
+        <v>84</v>
+      </c>
+      <c r="C248" t="s">
+        <v>705</v>
+      </c>
+      <c r="E248" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>707</v>
+      </c>
+      <c r="B249" t="s">
+        <v>84</v>
+      </c>
+      <c r="C249" t="s">
+        <v>708</v>
+      </c>
+      <c r="E249" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>710</v>
+      </c>
+      <c r="B250" t="s">
+        <v>84</v>
+      </c>
+      <c r="C250" t="s">
+        <v>711</v>
+      </c>
+      <c r="E250" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>713</v>
+      </c>
+      <c r="B251" t="s">
+        <v>84</v>
+      </c>
+      <c r="C251" t="s">
+        <v>714</v>
+      </c>
+      <c r="E251" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>716</v>
+      </c>
+      <c r="B252" t="s">
+        <v>84</v>
+      </c>
+      <c r="C252" t="s">
+        <v>717</v>
+      </c>
+      <c r="E252" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>719</v>
+      </c>
+      <c r="B253" t="s">
+        <v>84</v>
+      </c>
+      <c r="C253" t="s">
+        <v>717</v>
+      </c>
+      <c r="E253" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>721</v>
+      </c>
+      <c r="B254" t="s">
+        <v>84</v>
+      </c>
+      <c r="C254" t="s">
+        <v>722</v>
+      </c>
+      <c r="E254" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>724</v>
+      </c>
+      <c r="B255" t="s">
+        <v>84</v>
+      </c>
+      <c r="C255" t="s">
+        <v>725</v>
+      </c>
+      <c r="E255" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>727</v>
+      </c>
+      <c r="B256" t="s">
+        <v>84</v>
+      </c>
+      <c r="C256" t="s">
+        <v>728</v>
+      </c>
+      <c r="E256" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>730</v>
+      </c>
+      <c r="B257" t="s">
+        <v>84</v>
+      </c>
+      <c r="C257" t="s">
+        <v>731</v>
+      </c>
+      <c r="E257" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>733</v>
+      </c>
+      <c r="B258" t="s">
+        <v>84</v>
+      </c>
+      <c r="C258" t="s">
+        <v>731</v>
+      </c>
+      <c r="E258" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>735</v>
+      </c>
+      <c r="B259" t="s">
+        <v>84</v>
+      </c>
+      <c r="C259" t="s">
+        <v>736</v>
+      </c>
+      <c r="E259" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>738</v>
+      </c>
+      <c r="B260" t="s">
+        <v>84</v>
+      </c>
+      <c r="C260" t="s">
+        <v>739</v>
+      </c>
+      <c r="E260" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>741</v>
+      </c>
+      <c r="B261" t="s">
+        <v>84</v>
+      </c>
+      <c r="C261" t="s">
+        <v>742</v>
+      </c>
+      <c r="E261" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>744</v>
+      </c>
+      <c r="B262" t="s">
+        <v>84</v>
+      </c>
+      <c r="C262" t="s">
+        <v>745</v>
+      </c>
+      <c r="E262" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>747</v>
+      </c>
+      <c r="B263" t="s">
+        <v>84</v>
+      </c>
+      <c r="C263" t="s">
+        <v>745</v>
+      </c>
+      <c r="E263" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>749</v>
+      </c>
+      <c r="B264" t="s">
+        <v>84</v>
+      </c>
+      <c r="C264" t="s">
+        <v>750</v>
+      </c>
+      <c r="E264" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>752</v>
+      </c>
+      <c r="B265" t="s">
+        <v>84</v>
+      </c>
+      <c r="C265" t="s">
+        <v>750</v>
+      </c>
+      <c r="E265" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>754</v>
+      </c>
+      <c r="B266" t="s">
+        <v>84</v>
+      </c>
+      <c r="C266" t="s">
+        <v>755</v>
+      </c>
+      <c r="E266" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>757</v>
+      </c>
+      <c r="B267" t="s">
+        <v>84</v>
+      </c>
+      <c r="C267" t="s">
+        <v>758</v>
+      </c>
+      <c r="E267" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>760</v>
+      </c>
+      <c r="B268" t="s">
+        <v>84</v>
+      </c>
+      <c r="C268" t="s">
+        <v>761</v>
+      </c>
+      <c r="E268" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>763</v>
+      </c>
+      <c r="B269" t="s">
+        <v>84</v>
+      </c>
+      <c r="C269" t="s">
+        <v>764</v>
+      </c>
+      <c r="E269" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>766</v>
+      </c>
+      <c r="B270" t="s">
+        <v>84</v>
+      </c>
+      <c r="C270" t="s">
+        <v>767</v>
+      </c>
+      <c r="E270" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>769</v>
+      </c>
+      <c r="B271" t="s">
+        <v>84</v>
+      </c>
+      <c r="C271" t="s">
+        <v>770</v>
+      </c>
+      <c r="E271" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>772</v>
+      </c>
+      <c r="B272" t="s">
+        <v>84</v>
+      </c>
+      <c r="C272" t="s">
+        <v>773</v>
+      </c>
+      <c r="E272" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>775</v>
+      </c>
+      <c r="B273" t="s">
+        <v>84</v>
+      </c>
+      <c r="C273" t="s">
+        <v>776</v>
+      </c>
+      <c r="E273" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>778</v>
+      </c>
+      <c r="B274" t="s">
+        <v>84</v>
+      </c>
+      <c r="C274" t="s">
+        <v>779</v>
+      </c>
+      <c r="E274" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>781</v>
+      </c>
+      <c r="B275" t="s">
+        <v>84</v>
+      </c>
+      <c r="C275" t="s">
+        <v>782</v>
+      </c>
+      <c r="E275" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>784</v>
+      </c>
+      <c r="B276" t="s">
+        <v>84</v>
+      </c>
+      <c r="C276" t="s">
+        <v>785</v>
+      </c>
+      <c r="E276" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>787</v>
+      </c>
+      <c r="B277" t="s">
+        <v>84</v>
+      </c>
+      <c r="C277" t="s">
+        <v>788</v>
+      </c>
+      <c r="E277" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>790</v>
+      </c>
+      <c r="B278" t="s">
+        <v>791</v>
+      </c>
+      <c r="C278" t="s">
+        <v>792</v>
+      </c>
+      <c r="E278" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>794</v>
+      </c>
+      <c r="B279" t="s">
+        <v>791</v>
+      </c>
+      <c r="C279" t="s">
+        <v>792</v>
+      </c>
+      <c r="E279" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>796</v>
+      </c>
+      <c r="B280" t="s">
+        <v>791</v>
+      </c>
+      <c r="C280" t="s">
+        <v>797</v>
+      </c>
+      <c r="E280" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>799</v>
+      </c>
+      <c r="B281" t="s">
+        <v>791</v>
+      </c>
+      <c r="C281" t="s">
+        <v>797</v>
+      </c>
+      <c r="E281" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>801</v>
+      </c>
+      <c r="B282" t="s">
+        <v>791</v>
+      </c>
+      <c r="C282" t="s">
+        <v>802</v>
+      </c>
+      <c r="E282" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>804</v>
+      </c>
+      <c r="B283" t="s">
+        <v>791</v>
+      </c>
+      <c r="C283" t="s">
+        <v>802</v>
+      </c>
+      <c r="E283" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>806</v>
+      </c>
+      <c r="B284" t="s">
+        <v>791</v>
+      </c>
+      <c r="C284" t="s">
+        <v>807</v>
+      </c>
+      <c r="E284" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>809</v>
+      </c>
+      <c r="B285" t="s">
+        <v>791</v>
+      </c>
+      <c r="C285" t="s">
+        <v>810</v>
+      </c>
+      <c r="E285" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>812</v>
+      </c>
+      <c r="B286" t="s">
+        <v>791</v>
+      </c>
+      <c r="C286" t="s">
+        <v>810</v>
+      </c>
+      <c r="E286" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>814</v>
+      </c>
+      <c r="B287" t="s">
+        <v>791</v>
+      </c>
+      <c r="C287" t="s">
+        <v>815</v>
+      </c>
+      <c r="E287" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>817</v>
+      </c>
+      <c r="B288" t="s">
+        <v>818</v>
+      </c>
+      <c r="C288" t="s">
+        <v>97</v>
+      </c>
+      <c r="E288" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>820</v>
+      </c>
+      <c r="B289" t="s">
+        <v>818</v>
+      </c>
+      <c r="C289" t="s">
+        <v>821</v>
+      </c>
+      <c r="E289" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>823</v>
+      </c>
+      <c r="B290" t="s">
+        <v>818</v>
+      </c>
+      <c r="C290" t="s">
+        <v>824</v>
+      </c>
+      <c r="E290" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>826</v>
+      </c>
+      <c r="B291" t="s">
+        <v>818</v>
+      </c>
+      <c r="C291" t="s">
+        <v>827</v>
+      </c>
+      <c r="E291" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>829</v>
+      </c>
+      <c r="B292" t="s">
+        <v>818</v>
+      </c>
+      <c r="C292" t="s">
+        <v>830</v>
+      </c>
+      <c r="E292" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>832</v>
+      </c>
+      <c r="B293" t="s">
+        <v>818</v>
+      </c>
+      <c r="C293" t="s">
+        <v>833</v>
+      </c>
+      <c r="E293" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>835</v>
+      </c>
+      <c r="B294" t="s">
+        <v>818</v>
+      </c>
+      <c r="C294" t="s">
+        <v>836</v>
+      </c>
+      <c r="E294" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>838</v>
+      </c>
+      <c r="B295" t="s">
+        <v>818</v>
+      </c>
+      <c r="C295" t="s">
+        <v>839</v>
+      </c>
+      <c r="E295" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>841</v>
+      </c>
+      <c r="B296" t="s">
+        <v>818</v>
+      </c>
+      <c r="C296" t="s">
+        <v>842</v>
+      </c>
+      <c r="E296" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>844</v>
+      </c>
+      <c r="B297" t="s">
+        <v>818</v>
+      </c>
+      <c r="C297" t="s">
+        <v>148</v>
+      </c>
+      <c r="E297" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>846</v>
+      </c>
+      <c r="B298" t="s">
+        <v>818</v>
+      </c>
+      <c r="C298" t="s">
+        <v>847</v>
+      </c>
+      <c r="E298" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>849</v>
+      </c>
+      <c r="B299" t="s">
+        <v>818</v>
+      </c>
+      <c r="C299" t="s">
+        <v>154</v>
+      </c>
+      <c r="E299" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>851</v>
+      </c>
+      <c r="B300" t="s">
+        <v>818</v>
+      </c>
+      <c r="C300" t="s">
+        <v>852</v>
+      </c>
+      <c r="E300" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>854</v>
+      </c>
+      <c r="B301" t="s">
+        <v>818</v>
+      </c>
+      <c r="C301" t="s">
+        <v>855</v>
+      </c>
+      <c r="E301" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>857</v>
+      </c>
+      <c r="B302" t="s">
+        <v>818</v>
+      </c>
+      <c r="C302" t="s">
+        <v>858</v>
+      </c>
+      <c r="E302" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>860</v>
+      </c>
+      <c r="B303" t="s">
+        <v>818</v>
+      </c>
+      <c r="C303" t="s">
+        <v>861</v>
+      </c>
+      <c r="E303" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>863</v>
+      </c>
+      <c r="B304" t="s">
+        <v>818</v>
+      </c>
+      <c r="C304" t="s">
+        <v>864</v>
+      </c>
+      <c r="E304" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>866</v>
+      </c>
+      <c r="B305" t="s">
+        <v>818</v>
+      </c>
+      <c r="C305" t="s">
+        <v>867</v>
+      </c>
+      <c r="E305" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>869</v>
+      </c>
+      <c r="B306" t="s">
+        <v>818</v>
+      </c>
+      <c r="C306" t="s">
+        <v>870</v>
+      </c>
+      <c r="E306" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>872</v>
+      </c>
+      <c r="B307" t="s">
+        <v>818</v>
+      </c>
+      <c r="C307" t="s">
+        <v>873</v>
+      </c>
+      <c r="E307" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>875</v>
+      </c>
+      <c r="B308" t="s">
+        <v>876</v>
+      </c>
+      <c r="C308" t="s">
+        <v>877</v>
+      </c>
+      <c r="E308" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>879</v>
+      </c>
+      <c r="B309" t="s">
+        <v>876</v>
+      </c>
+      <c r="C309" t="s">
+        <v>880</v>
+      </c>
+      <c r="E309" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>882</v>
+      </c>
+      <c r="B310" t="s">
+        <v>876</v>
+      </c>
+      <c r="C310" t="s">
+        <v>883</v>
+      </c>
+      <c r="E310" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>885</v>
+      </c>
+      <c r="B311" t="s">
+        <v>876</v>
+      </c>
+      <c r="C311" t="s">
+        <v>886</v>
+      </c>
+      <c r="E311" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>888</v>
+      </c>
+      <c r="B312" t="s">
+        <v>876</v>
+      </c>
+      <c r="C312" t="s">
+        <v>889</v>
+      </c>
+      <c r="E312" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>891</v>
+      </c>
+      <c r="B313" t="s">
+        <v>876</v>
+      </c>
+      <c r="C313" t="s">
+        <v>892</v>
+      </c>
+      <c r="E313" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>894</v>
+      </c>
+      <c r="B314" t="s">
+        <v>876</v>
+      </c>
+      <c r="C314" t="s">
+        <v>895</v>
+      </c>
+      <c r="E314" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>897</v>
+      </c>
+      <c r="B315" t="s">
+        <v>876</v>
+      </c>
+      <c r="C315" t="s">
+        <v>898</v>
+      </c>
+      <c r="E315" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>900</v>
+      </c>
+      <c r="B316" t="s">
+        <v>876</v>
+      </c>
+      <c r="C316" t="s">
+        <v>824</v>
+      </c>
+      <c r="E316" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>902</v>
+      </c>
+      <c r="B317" t="s">
+        <v>876</v>
+      </c>
+      <c r="C317" t="s">
+        <v>903</v>
+      </c>
+      <c r="E317" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>905</v>
+      </c>
+      <c r="B318" t="s">
+        <v>906</v>
+      </c>
+      <c r="C318" t="s">
+        <v>907</v>
+      </c>
+      <c r="E318" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>909</v>
+      </c>
+      <c r="B319" t="s">
+        <v>906</v>
+      </c>
+      <c r="C319" t="s">
+        <v>97</v>
+      </c>
+      <c r="E319" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>911</v>
+      </c>
+      <c r="B320" t="s">
+        <v>906</v>
+      </c>
+      <c r="C320" t="s">
+        <v>912</v>
+      </c>
+      <c r="E320" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>914</v>
+      </c>
+      <c r="B321" t="s">
+        <v>906</v>
+      </c>
+      <c r="C321" t="s">
+        <v>168</v>
+      </c>
+      <c r="E321" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>916</v>
+      </c>
+      <c r="B322" t="s">
+        <v>906</v>
+      </c>
+      <c r="C322" t="s">
+        <v>917</v>
+      </c>
+      <c r="E322" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>919</v>
+      </c>
+      <c r="B323" t="s">
+        <v>906</v>
+      </c>
+      <c r="C323" t="s">
+        <v>920</v>
+      </c>
+      <c r="E323" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>922</v>
+      </c>
+      <c r="B324" t="s">
+        <v>906</v>
+      </c>
+      <c r="C324" t="s">
+        <v>920</v>
+      </c>
+      <c r="E324" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>924</v>
+      </c>
+      <c r="B325" t="s">
+        <v>906</v>
+      </c>
+      <c r="C325" t="s">
+        <v>925</v>
+      </c>
+      <c r="E325" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>927</v>
+      </c>
+      <c r="B326" t="s">
+        <v>906</v>
+      </c>
+      <c r="C326" t="s">
+        <v>928</v>
+      </c>
+      <c r="E326" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>930</v>
+      </c>
+      <c r="B327" t="s">
+        <v>906</v>
+      </c>
+      <c r="C327" t="s">
+        <v>931</v>
+      </c>
+      <c r="E327" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>933</v>
+      </c>
+      <c r="B328" t="s">
+        <v>934</v>
+      </c>
+      <c r="C328" t="s">
+        <v>935</v>
+      </c>
+      <c r="E328" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>937</v>
+      </c>
+      <c r="B329" t="s">
+        <v>934</v>
+      </c>
+      <c r="C329" t="s">
+        <v>889</v>
+      </c>
+      <c r="E329" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>939</v>
+      </c>
+      <c r="B330" t="s">
+        <v>934</v>
+      </c>
+      <c r="C330" t="s">
+        <v>907</v>
+      </c>
+      <c r="E330" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>941</v>
+      </c>
+      <c r="B331" t="s">
+        <v>934</v>
+      </c>
+      <c r="C331" t="s">
+        <v>942</v>
+      </c>
+      <c r="E331" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>944</v>
+      </c>
+      <c r="B332" t="s">
+        <v>934</v>
+      </c>
+      <c r="C332" t="s">
+        <v>945</v>
+      </c>
+      <c r="E332" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>947</v>
+      </c>
+      <c r="B333" t="s">
+        <v>934</v>
+      </c>
+      <c r="C333" t="s">
+        <v>948</v>
+      </c>
+      <c r="E333" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>950</v>
+      </c>
+      <c r="B334" t="s">
+        <v>934</v>
+      </c>
+      <c r="C334" t="s">
+        <v>951</v>
+      </c>
+      <c r="E334" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>953</v>
+      </c>
+      <c r="B335" t="s">
+        <v>934</v>
+      </c>
+      <c r="C335" t="s">
+        <v>122</v>
+      </c>
+      <c r="E335" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>955</v>
+      </c>
+      <c r="B336" t="s">
+        <v>934</v>
+      </c>
+      <c r="C336" t="s">
+        <v>956</v>
+      </c>
+      <c r="E336" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>958</v>
+      </c>
+      <c r="B337" t="s">
+        <v>934</v>
+      </c>
+      <c r="C337" t="s">
+        <v>959</v>
+      </c>
+      <c r="E337" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>961</v>
+      </c>
+      <c r="B338" t="s">
+        <v>962</v>
+      </c>
+      <c r="C338" t="s">
+        <v>14</v>
+      </c>
+      <c r="E338" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>964</v>
+      </c>
+      <c r="B339" t="s">
+        <v>962</v>
+      </c>
+      <c r="C339" t="s">
+        <v>965</v>
+      </c>
+      <c r="E339" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>967</v>
+      </c>
+      <c r="B340" t="s">
+        <v>962</v>
+      </c>
+      <c r="C340" t="s">
+        <v>87</v>
+      </c>
+      <c r="E340" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>969</v>
+      </c>
+      <c r="B341" t="s">
+        <v>962</v>
+      </c>
+      <c r="C341" t="s">
+        <v>87</v>
+      </c>
+      <c r="E341" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>971</v>
+      </c>
+      <c r="B342" t="s">
+        <v>962</v>
+      </c>
+      <c r="C342" t="s">
+        <v>883</v>
+      </c>
+      <c r="E342" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>973</v>
+      </c>
+      <c r="B343" t="s">
+        <v>962</v>
+      </c>
+      <c r="C343" t="s">
+        <v>974</v>
+      </c>
+      <c r="E343" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>905</v>
+      </c>
+      <c r="B344" t="s">
+        <v>962</v>
+      </c>
+      <c r="C344" t="s">
+        <v>907</v>
+      </c>
+      <c r="E344" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>909</v>
+      </c>
+      <c r="B345" t="s">
+        <v>962</v>
+      </c>
+      <c r="C345" t="s">
+        <v>97</v>
+      </c>
+      <c r="E345" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>911</v>
+      </c>
+      <c r="B346" t="s">
+        <v>962</v>
+      </c>
+      <c r="C346" t="s">
+        <v>97</v>
+      </c>
+      <c r="E346" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>979</v>
+      </c>
+      <c r="B347" t="s">
+        <v>962</v>
+      </c>
+      <c r="C347" t="s">
+        <v>980</v>
+      </c>
+      <c r="E347" t="s">
+        <v>981</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -568,6 +8331,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -9,15 +9,15 @@
   <sheets>
     <sheet sheetId="2" name="2021-02-24-chinese" state="visible" r:id="rId4"/>
     <sheet sheetId="1" name="2021-02-24-english" state="visible" r:id="rId5"/>
-    <sheet sheetId="4" name="2021-02-25-english" state="visible" r:id="rId6"/>
-    <sheet sheetId="3" name="2021-02-25-chinese" state="visible" r:id="rId7"/>
+    <sheet sheetId="3" name="2021-02-25-chinese" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="2021-02-25-english" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
   <si>
     <t>标题</t>
   </si>
@@ -56,6 +56,21 @@
   </si>
   <si>
     <t>https://www.infoq.cn/article/xZYe1DUopNA9CzLwau3O</t>
+  </si>
+  <si>
+    <t>How We Improved the Accessibility of Our Single Page App Menu</t>
+  </si>
+  <si>
+    <t>css-tricks</t>
+  </si>
+  <si>
+    <t>https://css-tricks.com/how-we-improved-the-accessibility-of-our-single-page-app-menu/</t>
+  </si>
+  <si>
+    <t>Boost app engagement with chat, voice, and video APIs</t>
+  </si>
+  <si>
+    <t>https://css-tricks.com/boost-app-engagement-with-chat-voice-and-video-apis/</t>
   </si>
 </sst>
 </file>
@@ -559,13 +574,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -592,8 +607,36 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -4,20 +4,21 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="0" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="1" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet sheetId="2" name="2021-02-24-chinese" state="visible" r:id="rId4"/>
     <sheet sheetId="1" name="2021-02-24-english" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="2021-02-25-chinese" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="2021-02-25-english" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="2021-02-26-chinese" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="22">
   <si>
     <t>标题</t>
   </si>
@@ -71,6 +72,18 @@
   </si>
   <si>
     <t>https://css-tricks.com/boost-app-engagement-with-chat-voice-and-video-apis/</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 奇舞周刊第 386 期 </t>
+  </si>
+  <si>
+    <t>奇舞周刊</t>
+  </si>
+  <si>
+    <t>2021-02-26</t>
+  </si>
+  <si>
+    <t>https://weekly.75.team/issue386.html</t>
   </si>
 </sst>
 </file>
@@ -637,6 +650,55 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="1" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="2" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet sheetId="2" name="2021-02-24-chinese" state="visible" r:id="rId4"/>
@@ -12,13 +12,14 @@
     <sheet sheetId="3" name="2021-02-25-chinese" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="2021-02-25-english" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="2021-02-26-chinese" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="2021-02-26-english" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="24">
   <si>
     <t>标题</t>
   </si>
@@ -84,6 +85,12 @@
   </si>
   <si>
     <t>https://weekly.75.team/issue386.html</t>
+  </si>
+  <si>
+    <t>A definitive guide to streams</t>
+  </si>
+  <si>
+    <t>https://javascriptweekly.com/issues/527</t>
   </si>
 </sst>
 </file>
@@ -699,6 +706,55 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="26">
   <si>
     <t>标题</t>
   </si>
@@ -91,6 +91,12 @@
   </si>
   <si>
     <t>https://javascriptweekly.com/issues/527</t>
+  </si>
+  <si>
+    <t>The Things I Add to Tailwind CSS Right Out of the Box</t>
+  </si>
+  <si>
+    <t>https://css-tricks.com/custom-tailwind-css/</t>
   </si>
 </sst>
 </file>
@@ -712,7 +718,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -753,6 +759,20 @@
         <v>23</v>
       </c>
     </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="28">
   <si>
     <t>标题</t>
   </si>
@@ -91,6 +91,12 @@
   </si>
   <si>
     <t>https://javascriptweekly.com/issues/527</t>
+  </si>
+  <si>
+    <t>Weekly Platform News: Reduced Motion, CORS, WhiteHouse.gov, popups, and 100vw</t>
+  </si>
+  <si>
+    <t>https://css-tricks.com/weekly-platform-news-reduced-motion-cors-whitehouse-gov-popups-and-100vw/</t>
   </si>
   <si>
     <t>The Things I Add to Tailwind CSS Right Out of the Box</t>
@@ -718,7 +724,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -773,6 +779,20 @@
         <v>25</v>
       </c>
     </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="22">
   <si>
     <t>标题</t>
   </si>
@@ -85,24 +85,6 @@
   </si>
   <si>
     <t>https://weekly.75.team/issue386.html</t>
-  </si>
-  <si>
-    <t>A definitive guide to streams</t>
-  </si>
-  <si>
-    <t>https://javascriptweekly.com/issues/527</t>
-  </si>
-  <si>
-    <t>Weekly Platform News: Reduced Motion, CORS, WhiteHouse.gov, popups, and 100vw</t>
-  </si>
-  <si>
-    <t>https://css-tricks.com/weekly-platform-news-reduced-motion-cors-whitehouse-gov-popups-and-100vw/</t>
-  </si>
-  <si>
-    <t>The Things I Add to Tailwind CSS Right Out of the Box</t>
-  </si>
-  <si>
-    <t>https://css-tricks.com/custom-tailwind-css/</t>
   </si>
 </sst>
 </file>
@@ -724,7 +706,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -751,48 +733,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>27</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -11,15 +11,15 @@
     <sheet sheetId="1" name="2021-02-24-english" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="2021-02-25-chinese" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="2021-02-25-english" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="2021-02-26-chinese" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="2021-02-26-english" state="visible" r:id="rId9"/>
+    <sheet sheetId="6" name="2021-02-26-english" state="visible" r:id="rId8"/>
+    <sheet sheetId="5" name="2021-02-26-chinese" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
   <si>
     <t>标题</t>
   </si>
@@ -73,18 +73,6 @@
   </si>
   <si>
     <t>https://css-tricks.com/boost-app-engagement-with-chat-voice-and-video-apis/</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 奇舞周刊第 386 期 </t>
-  </si>
-  <si>
-    <t>奇舞周刊</t>
-  </si>
-  <si>
-    <t>2021-02-26</t>
-  </si>
-  <si>
-    <t>https://weekly.75.team/issue386.html</t>
   </si>
 </sst>
 </file>
@@ -657,7 +645,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -684,23 +672,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -735,6 +709,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -11,15 +11,15 @@
     <sheet sheetId="1" name="2021-02-24-english" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="2021-02-25-chinese" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="2021-02-25-english" state="visible" r:id="rId7"/>
-    <sheet sheetId="6" name="2021-02-26-english" state="visible" r:id="rId8"/>
-    <sheet sheetId="5" name="2021-02-26-chinese" state="visible" r:id="rId9"/>
+    <sheet sheetId="5" name="2021-02-26-chinese" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="2021-02-26-english" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="22">
   <si>
     <t>标题</t>
   </si>
@@ -73,6 +73,18 @@
   </si>
   <si>
     <t>https://css-tricks.com/boost-app-engagement-with-chat-voice-and-video-apis/</t>
+  </si>
+  <si>
+    <t>CSS-in-JS support in DevTools</t>
+  </si>
+  <si>
+    <t>Chrome</t>
+  </si>
+  <si>
+    <t>2021-02-26</t>
+  </si>
+  <si>
+    <t>https://developers.google.com/web/updates/2021/02/css-in-js?utm_source=feed&amp;utm_medium=feed&amp;utm_campaign=updates_feed</t>
   </si>
 </sst>
 </file>
@@ -674,13 +686,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -707,8 +719,22 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -11,15 +11,15 @@
     <sheet sheetId="1" name="2021-02-24-english" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="2021-02-25-chinese" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="2021-02-25-english" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="2021-02-26-chinese" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="2021-02-26-english" state="visible" r:id="rId9"/>
+    <sheet sheetId="6" name="2021-02-26-english" state="visible" r:id="rId8"/>
+    <sheet sheetId="5" name="2021-02-26-chinese" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="25">
   <si>
     <t>标题</t>
   </si>
@@ -85,6 +85,15 @@
   </si>
   <si>
     <t>https://developers.google.com/web/updates/2021/02/css-in-js?utm_source=feed&amp;utm_medium=feed&amp;utm_campaign=updates_feed</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 奇舞周刊第 386 期 </t>
+  </si>
+  <si>
+    <t>奇舞周刊</t>
+  </si>
+  <si>
+    <t>https://weekly.75.team/issue386.html</t>
   </si>
 </sst>
 </file>
@@ -657,7 +666,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -684,9 +693,23 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -735,6 +758,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -11,15 +11,15 @@
     <sheet sheetId="1" name="2021-02-24-english" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="2021-02-25-chinese" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="2021-02-25-english" state="visible" r:id="rId7"/>
-    <sheet sheetId="6" name="2021-02-26-english" state="visible" r:id="rId8"/>
-    <sheet sheetId="5" name="2021-02-26-chinese" state="visible" r:id="rId9"/>
+    <sheet sheetId="5" name="2021-02-26-chinese" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="2021-02-26-english" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="31">
   <si>
     <t>标题</t>
   </si>
@@ -75,25 +75,43 @@
     <t>https://css-tricks.com/boost-app-engagement-with-chat-voice-and-video-apis/</t>
   </si>
   <si>
+    <t xml:space="preserve"> 奇舞周刊第 386 期 </t>
+  </si>
+  <si>
+    <t>奇舞周刊</t>
+  </si>
+  <si>
+    <t>2021-02-26</t>
+  </si>
+  <si>
+    <t>https://weekly.75.team/issue386.html</t>
+  </si>
+  <si>
     <t>CSS-in-JS support in DevTools</t>
   </si>
   <si>
     <t>Chrome</t>
   </si>
   <si>
-    <t>2021-02-26</t>
-  </si>
-  <si>
     <t>https://developers.google.com/web/updates/2021/02/css-in-js?utm_source=feed&amp;utm_medium=feed&amp;utm_campaign=updates_feed</t>
   </si>
   <si>
-    <t xml:space="preserve"> 奇舞周刊第 386 期 </t>
-  </si>
-  <si>
-    <t>奇舞周刊</t>
-  </si>
-  <si>
-    <t>https://weekly.75.team/issue386.html</t>
+    <t>A definitive guide to streams</t>
+  </si>
+  <si>
+    <t>https://javascriptweekly.com/issues/527</t>
+  </si>
+  <si>
+    <t>Weekly Platform News: Reduced Motion, CORS, WhiteHouse.gov, popups, and 100vw</t>
+  </si>
+  <si>
+    <t>https://css-tricks.com/weekly-platform-news-reduced-motion-cors-whitehouse-gov-popups-and-100vw/</t>
+  </si>
+  <si>
+    <t>The Things I Add to Tailwind CSS Right Out of the Box</t>
+  </si>
+  <si>
+    <t>https://css-tricks.com/custom-tailwind-css/</t>
   </si>
 </sst>
 </file>
@@ -695,27 +713,27 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -744,20 +762,62 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="2" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="3" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet sheetId="2" name="2021-02-24-chinese" state="visible" r:id="rId4"/>
@@ -13,13 +13,14 @@
     <sheet sheetId="4" name="2021-02-25-english" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="2021-02-26-chinese" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="2021-02-26-english" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="2021-02-28-english" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="36">
   <si>
     <t>标题</t>
   </si>
@@ -112,6 +113,21 @@
   </si>
   <si>
     <t>https://css-tricks.com/custom-tailwind-css/</t>
+  </si>
+  <si>
+    <t>CSS Border Font</t>
+  </si>
+  <si>
+    <t>2021-02-28</t>
+  </si>
+  <si>
+    <t>https://davorsuljic.github.io/css-border-font.html</t>
+  </si>
+  <si>
+    <t>Next.js on Netlify</t>
+  </si>
+  <si>
+    <t>https://netlify.zoom.us/webinar/register/8216142699391/WN_jLox66kvToOCHB29NUhDsQ</t>
   </si>
 </sst>
 </file>
@@ -818,6 +834,69 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="3" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="5" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet sheetId="2" name="2021-02-24-chinese" state="visible" r:id="rId4"/>
@@ -14,13 +14,15 @@
     <sheet sheetId="5" name="2021-02-26-chinese" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="2021-02-26-english" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="2021-02-28-english" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="2021-03-01-english" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="2021-03-01-chinese" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="47">
   <si>
     <t>标题</t>
   </si>
@@ -128,6 +130,39 @@
   </si>
   <si>
     <t>https://netlify.zoom.us/webinar/register/8216142699391/WN_jLox66kvToOCHB29NUhDsQ</t>
+  </si>
+  <si>
+    <t>The “Gray Dead Zone” of Gradients</t>
+  </si>
+  <si>
+    <t>2021-03-01</t>
+  </si>
+  <si>
+    <t>https://css-tricks.com/the-gray-dead-zone-of-gradients/</t>
+  </si>
+  <si>
+    <t>How to Map Mouse Position in CSS</t>
+  </si>
+  <si>
+    <t>https://css-tricks.com/how-to-map-mouse-position-in-css/</t>
+  </si>
+  <si>
+    <t>ZooTeam 前端周刊｜第 121 期</t>
+  </si>
+  <si>
+    <t>掘金-政采云前端团队</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6934607774789681159</t>
+  </si>
+  <si>
+    <t>高性能 JavaScript 引擎 V8 - 垃圾回收</t>
+  </si>
+  <si>
+    <t>掘金-微医大前端技术</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6934638688563363853</t>
   </si>
 </sst>
 </file>
@@ -897,6 +932,132 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="5" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="7" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet sheetId="2" name="2021-02-24-chinese" state="visible" r:id="rId4"/>
@@ -16,13 +16,15 @@
     <sheet sheetId="7" name="2021-02-28-english" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="2021-03-01-english" state="visible" r:id="rId11"/>
     <sheet sheetId="9" name="2021-03-01-chinese" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="2021-03-02-english" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="2021-03-02-chinese" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="55">
   <si>
     <t>标题</t>
   </si>
@@ -163,6 +165,30 @@
   </si>
   <si>
     <t>https://juejin.cn/post/6934638688563363853</t>
+  </si>
+  <si>
+    <t>How to Animate the Details Element</t>
+  </si>
+  <si>
+    <t>2021-03-02</t>
+  </si>
+  <si>
+    <t>https://css-tricks.com/how-to-animate-the-details-element/</t>
+  </si>
+  <si>
+    <t>The Best Font Loading Strategies and How to Execute Them</t>
+  </si>
+  <si>
+    <t>https://css-tricks.com/the-best-font-loading-strategies-and-how-to-execute-them/</t>
+  </si>
+  <si>
+    <t>手把手教你接入前端热门抓包神器 - whistle</t>
+  </si>
+  <si>
+    <t>掘金-腾讯IMWeb团队</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6934888303841771527</t>
   </si>
 </sst>
 </file>
@@ -586,6 +612,118 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E1"/>
@@ -1058,6 +1196,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="7" activeTab="10"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="9" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet sheetId="2" name="2021-02-24-chinese" state="visible" r:id="rId4"/>
@@ -18,13 +18,15 @@
     <sheet sheetId="9" name="2021-03-01-chinese" state="visible" r:id="rId12"/>
     <sheet sheetId="10" name="2021-03-02-english" state="visible" r:id="rId13"/>
     <sheet sheetId="11" name="2021-03-02-chinese" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="2021-03-03-english" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="2021-03-03-chinese" state="visible" r:id="rId16"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="71">
   <si>
     <t>标题</t>
   </si>
@@ -189,6 +191,54 @@
   </si>
   <si>
     <t>https://juejin.cn/post/6934888303841771527</t>
+  </si>
+  <si>
+    <t>Before you reach for memoization..</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>https://react.statuscode.com/issues/228</t>
+  </si>
+  <si>
+    <t>A Bare-Bones Approach to Versatile and Reusable Skeleton Loaders</t>
+  </si>
+  <si>
+    <t>https://css-tricks.com/a-bare-bones-approach-to-versatile-and-reusable-skeleton-loaders/</t>
+  </si>
+  <si>
+    <t>React Without Build Tools</t>
+  </si>
+  <si>
+    <t>https://blog.jim-nielsen.com/2020/react-without-build-tools/</t>
+  </si>
+  <si>
+    <t>六种Web验证方法大揭秘</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/XEIrmzbSCWXjoYc3HFLV</t>
+  </si>
+  <si>
+    <t>Deno 1.8 正式发布：附带完整的 ICU 支持；deno lsp 和导入映射均已稳定</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/zsRyZ9mXL3ljEEV50HNf</t>
+  </si>
+  <si>
+    <t>前端单元测试技术方案总结</t>
+  </si>
+  <si>
+    <t>知乎-网易云音乐大前端团队</t>
+  </si>
+  <si>
+    <t>https://zhuanlan.zhihu.com/p/354206188</t>
+  </si>
+  <si>
+    <t>如何用 JS 实现二叉堆</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6935226614020046878</t>
   </si>
 </sst>
 </file>
@@ -720,6 +770,174 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>

--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="9" activeTab="12"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="11" activeTab="14"/>
   </bookViews>
   <sheets>
     <sheet sheetId="2" name="2021-02-24-chinese" state="visible" r:id="rId4"/>
@@ -20,13 +20,15 @@
     <sheet sheetId="11" name="2021-03-02-chinese" state="visible" r:id="rId14"/>
     <sheet sheetId="12" name="2021-03-03-english" state="visible" r:id="rId15"/>
     <sheet sheetId="13" name="2021-03-03-chinese" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="2021-03-04-english" state="visible" r:id="rId17"/>
+    <sheet sheetId="15" name="2021-03-04-chinese" state="visible" r:id="rId18"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="93">
   <si>
     <t>标题</t>
   </si>
@@ -239,6 +241,72 @@
   </si>
   <si>
     <t>https://juejin.cn/post/6935226614020046878</t>
+  </si>
+  <si>
+    <t>Faster releases</t>
+  </si>
+  <si>
+    <t>v8.dev</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>https://v8.dev/blog/faster-releases</t>
+  </si>
+  <si>
+    <t>Through the pipeline: An exploration of front-end bundlers</t>
+  </si>
+  <si>
+    <t>https://css-tricks.com/through-the-pipeline-an-exploration-of-front-end-bundlers/</t>
+  </si>
+  <si>
+    <t>Weekly Platform News: Focus Rings, Donut Scope, Ditching em Units, and Global Privacy Control</t>
+  </si>
+  <si>
+    <t>https://css-tricks.com/weekly-platform-news-focus-rings-donut-scope-ditching-em-units-and-global-privacy-control/</t>
+  </si>
+  <si>
+    <t>Exploring @property and its Animating Powers</t>
+  </si>
+  <si>
+    <t>https://css-tricks.com/exploring-property-and-its-animating-powers/</t>
+  </si>
+  <si>
+    <t>How to Develop and Test a Mobile-First Design in 2021</t>
+  </si>
+  <si>
+    <t>https://css-tricks.com/how-to-develop-and-test-a-mobile-first-design-in-2021/</t>
+  </si>
+  <si>
+    <t>Flutter 2 来了：专为 Web、移动与台式机环境构建</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/A1kuPWmvRLZgykVe7qXb</t>
+  </si>
+  <si>
+    <t>Java真的要没落了？</t>
+  </si>
+  <si>
+    <t>掘金-阿里巴巴淘系技术</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6935605290289070088</t>
+  </si>
+  <si>
+    <t>回顾：Spring框架发展史</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6935603312485990437</t>
+  </si>
+  <si>
+    <t>鬼才｜闲鱼PMO的年终总结</t>
+  </si>
+  <si>
+    <t>掘金-闲鱼技术</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6935643533290242084</t>
   </si>
 </sst>
 </file>
@@ -938,6 +1006,202 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>

--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="96">
   <si>
     <t>标题</t>
   </si>
@@ -307,6 +307,15 @@
   </si>
   <si>
     <t>https://juejin.cn/post/6935643533290242084</t>
+  </si>
+  <si>
+    <t>聊聊编程范式</t>
+  </si>
+  <si>
+    <t>掘金-字节前端</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6935681018649116703</t>
   </si>
 </sst>
 </file>
@@ -1117,7 +1126,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -1198,6 +1207,20 @@
       </c>
       <c r="E5" t="s">
         <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="11" activeTab="14"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="13" activeTab="16"/>
   </bookViews>
   <sheets>
     <sheet sheetId="2" name="2021-02-24-chinese" state="visible" r:id="rId4"/>
@@ -22,13 +22,15 @@
     <sheet sheetId="13" name="2021-03-03-chinese" state="visible" r:id="rId16"/>
     <sheet sheetId="14" name="2021-03-04-english" state="visible" r:id="rId17"/>
     <sheet sheetId="15" name="2021-03-04-chinese" state="visible" r:id="rId18"/>
+    <sheet sheetId="16" name="2021-03-05-english" state="visible" r:id="rId19"/>
+    <sheet sheetId="17" name="2021-03-05-chinese" state="visible" r:id="rId20"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="119">
   <si>
     <t>标题</t>
   </si>
@@ -316,6 +318,75 @@
   </si>
   <si>
     <t>https://juejin.cn/post/6935681018649116703</t>
+  </si>
+  <si>
+    <t>Announcing the New TypeScript Handbook</t>
+  </si>
+  <si>
+    <t>Typescript</t>
+  </si>
+  <si>
+    <t>2021-03-05</t>
+  </si>
+  <si>
+    <t>https://devblogs.microsoft.com/typescript/announcing-the-new-typescript-handbook/</t>
+  </si>
+  <si>
+    <t>V8 stepping up to four-week release cycle</t>
+  </si>
+  <si>
+    <t>Javascript Weekly</t>
+  </si>
+  <si>
+    <t>https://javascriptweekly.com/issues/528</t>
+  </si>
+  <si>
+    <t>A Super Flexible CSS Carousel, Enhanced With JavaScript Navigation</t>
+  </si>
+  <si>
+    <t>https://css-tricks.com/a-super-flexible-css-carousel-enhanced-with-javascript-navigation/</t>
+  </si>
+  <si>
+    <t>基于 Vue 的两层吸顶踩坑总结</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/pMZZ1L1Ee188fST4MeFC</t>
+  </si>
+  <si>
+    <t>让你的组件千变万化，Vue slot 剖玄析微</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/wyYxVlmD87yOFpiTeAR9</t>
+  </si>
+  <si>
+    <t>为你重新系统梳理下， Web 体验优化中和图有关的那些事（万字长文）</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/b6gbExG4WMIQgs66H99Q</t>
+  </si>
+  <si>
+    <t>React的未来：服务端组件</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/TVoT14RM3KOSHkfDjHGg</t>
+  </si>
+  <si>
+    <t>ZooTeam 前端周刊｜第 124 期</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6936095733837725727</t>
+  </si>
+  <si>
+    <t>技术周报 · 2021-03-05</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6936045260363530248</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 奇舞周刊第 387 期 </t>
+  </si>
+  <si>
+    <t>https://weekly.75.team/issue387.html</t>
   </si>
 </sst>
 </file>
@@ -1225,6 +1296,230 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>117</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>

--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="13" activeTab="16"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="15" activeTab="18"/>
   </bookViews>
   <sheets>
     <sheet sheetId="2" name="2021-02-24-chinese" state="visible" r:id="rId4"/>
@@ -24,13 +24,15 @@
     <sheet sheetId="15" name="2021-03-04-chinese" state="visible" r:id="rId18"/>
     <sheet sheetId="16" name="2021-03-05-english" state="visible" r:id="rId19"/>
     <sheet sheetId="17" name="2021-03-05-chinese" state="visible" r:id="rId20"/>
+    <sheet sheetId="18" name="2021-03-06-english" state="visible" r:id="rId21"/>
+    <sheet sheetId="19" name="2021-03-06-chinese" state="visible" r:id="rId22"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="126">
   <si>
     <t>标题</t>
   </si>
@@ -387,6 +389,27 @@
   </si>
   <si>
     <t>https://weekly.75.team/issue387.html</t>
+  </si>
+  <si>
+    <t>CSS-Tricks Chronicle XXXIX</t>
+  </si>
+  <si>
+    <t>2021-03-06</t>
+  </si>
+  <si>
+    <t>https://css-tricks.com/css-tricks-chronicle-xxxix/</t>
+  </si>
+  <si>
+    <t>纯 JS 实现放大缩小拖拽采坑之旅</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/8ItfqyhX1mWGxCh1Skdo</t>
+  </si>
+  <si>
+    <t>Lyft如何将100+前端微服务迁移到Next.js</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/4lfWX4LI7QGXssjCMXQy</t>
   </si>
 </sst>
 </file>
@@ -1520,6 +1543,118 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>

--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="15" activeTab="18"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="16" activeTab="19"/>
   </bookViews>
   <sheets>
     <sheet sheetId="2" name="2021-02-24-chinese" state="visible" r:id="rId4"/>
@@ -26,13 +26,14 @@
     <sheet sheetId="17" name="2021-03-05-chinese" state="visible" r:id="rId20"/>
     <sheet sheetId="18" name="2021-03-06-english" state="visible" r:id="rId21"/>
     <sheet sheetId="19" name="2021-03-06-chinese" state="visible" r:id="rId22"/>
+    <sheet sheetId="20" name="2021-03-07-chinese" state="visible" r:id="rId23"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="130">
   <si>
     <t>标题</t>
   </si>
@@ -410,6 +411,18 @@
   </si>
   <si>
     <t>https://www.infoq.cn/article/4lfWX4LI7QGXssjCMXQy</t>
+  </si>
+  <si>
+    <t>性能！！让你的 React 组件跑得再快一点</t>
+  </si>
+  <si>
+    <t>2021-03-07</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/8550yiCs92ttMOTQEFPU</t>
+  </si>
+  <si>
+    <t>ZooTeam 前端周刊｜第 123 期</t>
   </si>
 </sst>
 </file>
@@ -1655,7 +1668,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1694,6 +1707,69 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>

--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="16" activeTab="19"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="18" activeTab="21"/>
   </bookViews>
   <sheets>
     <sheet sheetId="2" name="2021-02-24-chinese" state="visible" r:id="rId4"/>
@@ -27,13 +27,15 @@
     <sheet sheetId="18" name="2021-03-06-english" state="visible" r:id="rId21"/>
     <sheet sheetId="19" name="2021-03-06-chinese" state="visible" r:id="rId22"/>
     <sheet sheetId="20" name="2021-03-07-chinese" state="visible" r:id="rId23"/>
+    <sheet sheetId="21" name="2021-03-08-english" state="visible" r:id="rId24"/>
+    <sheet sheetId="22" name="2021-03-08-chinese" state="visible" r:id="rId25"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="153">
   <si>
     <t>标题</t>
   </si>
@@ -423,6 +425,75 @@
   </si>
   <si>
     <t>ZooTeam 前端周刊｜第 123 期</t>
+  </si>
+  <si>
+    <t>Web Components Are Easier Than You Think</t>
+  </si>
+  <si>
+    <t>2021-03-08</t>
+  </si>
+  <si>
+    <t>https://css-tricks.com/web-components-are-easier-than-you-think/</t>
+  </si>
+  <si>
+    <t>如何在 React 中优雅的写 CSS</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/FtLPPDeFO27PRgqHLO5a</t>
+  </si>
+  <si>
+    <t>自建图床应用，我只推荐 Serverless</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/XE6LpWvPMvmFiNCo8i4u</t>
+  </si>
+  <si>
+    <t>又被限速，我决定用 Serverless 搭建一款私人网盘</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/yhWJ8fybKGcOgpo1aU6r</t>
+  </si>
+  <si>
+    <t>去哪儿网 ReactNative 跨小程序多端方案介绍</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/hKoIHlwvmxwRo2u94e9I</t>
+  </si>
+  <si>
+    <t>学会这招，使你也可以使商品准确率提升50%</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6932296367947988999</t>
+  </si>
+  <si>
+    <t>Webpack 案例 —— vue-loader 原理分析</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6937125495439900685</t>
+  </si>
+  <si>
+    <t>飞猪技术部 2022 届校园招聘开始啦~</t>
+  </si>
+  <si>
+    <t>掘金-飞猪前端</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6937256619763826718</t>
+  </si>
+  <si>
+    <t>飞猪Flutter技术演进及业务改造的实践与思考总结</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6937254156776243231</t>
+  </si>
+  <si>
+    <t>iOS 稳定性问题治理：卡死崩溃监控原理及最佳实践</t>
+  </si>
+  <si>
+    <t>掘金-字节跳动技术团队</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6937091641656721438</t>
   </si>
 </sst>
 </file>
@@ -1766,6 +1837,216 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>131</v>
+      </c>
+      <c r="E5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C8" t="s">
+        <v>131</v>
+      </c>
+      <c r="E8" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>150</v>
+      </c>
+      <c r="B10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C10" t="s">
+        <v>131</v>
+      </c>
+      <c r="E10" t="s">
+        <v>152</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>

--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="18" activeTab="21"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="20" activeTab="23"/>
   </bookViews>
   <sheets>
     <sheet sheetId="2" name="2021-02-24-chinese" state="visible" r:id="rId4"/>
@@ -29,13 +29,15 @@
     <sheet sheetId="20" name="2021-03-07-chinese" state="visible" r:id="rId23"/>
     <sheet sheetId="21" name="2021-03-08-english" state="visible" r:id="rId24"/>
     <sheet sheetId="22" name="2021-03-08-chinese" state="visible" r:id="rId25"/>
+    <sheet sheetId="23" name="2021-03-09-english" state="visible" r:id="rId26"/>
+    <sheet sheetId="24" name="2021-03-09-chinese" state="visible" r:id="rId27"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="180">
   <si>
     <t>标题</t>
   </si>
@@ -494,6 +496,87 @@
   </si>
   <si>
     <t>https://juejin.cn/post/6937091641656721438</t>
+  </si>
+  <si>
+    <t>Adding Rank Magnitude to the CrUX Report in BigQuery.</t>
+  </si>
+  <si>
+    <t>2021-03-09</t>
+  </si>
+  <si>
+    <t>https://developers.google.com/web/updates/2021/03/crux-rank-magnitude?utm_source=feed&amp;utm_medium=feed&amp;utm_campaign=updates_feed</t>
+  </si>
+  <si>
+    <t>Web Frameworks: Why You Don’t Always Need Them</t>
+  </si>
+  <si>
+    <t>https://thenewstack.io/case-against-web-frameworks/</t>
+  </si>
+  <si>
+    <t>Firebase Crash Course</t>
+  </si>
+  <si>
+    <t>https://css-tricks.com/firebase-crash-course/</t>
+  </si>
+  <si>
+    <t>AutomateWoo Brings Automated Communications to Bookings</t>
+  </si>
+  <si>
+    <t>https://css-tricks.com/automatewoo-brings-automated-communications-to-bookings/</t>
+  </si>
+  <si>
+    <t>Flutter 将成为未来 Ubuntu 应用程序的默认选择</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/lDBYw6pfpz2M480CyWcv</t>
+  </si>
+  <si>
+    <t>Java8 Stream 数据流，大数据量下的性能效率怎么样？</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/6521ea3ae8a36f2bdaece6e61</t>
+  </si>
+  <si>
+    <t>Midway Serverless 发布 2.0，一体化让前端研发再次提效</t>
+  </si>
+  <si>
+    <t>Taobao FED | 淘系前端团队</t>
+  </si>
+  <si>
+    <t>https://fed.taobao.org/blog/taofed/do71ct/mvd9lw</t>
+  </si>
+  <si>
+    <t>构建效率大幅提升，webpack5 在企鹅辅导的升级实践</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6937609106022727717</t>
+  </si>
+  <si>
+    <t>Electron 生命周期看这篇就够了</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6937535140222468110</t>
+  </si>
+  <si>
+    <t>闲鱼如何建设技术舆情治理体系 （多图多代码）</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6937513942914695181</t>
+  </si>
+  <si>
+    <t>如何禁止开发者操作网页上的DOM对象？</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6937572714563518478</t>
+  </si>
+  <si>
+    <t>深度分析前端构建工具：Vite2 v.s Snowpack3 v.s. Webpack5</t>
+  </si>
+  <si>
+    <t>掘金-智联大前端</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6937473044185088014</t>
   </si>
 </sst>
 </file>
@@ -2047,6 +2130,244 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>154</v>
+      </c>
+      <c r="E5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" t="s">
+        <v>154</v>
+      </c>
+      <c r="E5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>173</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>154</v>
+      </c>
+      <c r="E7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>175</v>
+      </c>
+      <c r="B8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" t="s">
+        <v>154</v>
+      </c>
+      <c r="E8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>177</v>
+      </c>
+      <c r="B9" t="s">
+        <v>178</v>
+      </c>
+      <c r="C9" t="s">
+        <v>154</v>
+      </c>
+      <c r="E9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>

--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -525,6 +525,15 @@
     <t>https://css-tricks.com/automatewoo-brings-automated-communications-to-bookings/</t>
   </si>
   <si>
+    <t>New article: “Beyond console.log() – level up your debugging skills”</t>
+  </si>
+  <si>
+    <t>Christian Heilmann</t>
+  </si>
+  <si>
+    <t>https://christianheilmann.com/2021/03/09/new-article-beyond-console-log-level-up-your-debugging-skills/</t>
+  </si>
+  <si>
     <t>Flutter 将成为未来 Ubuntu 应用程序的默认选择</t>
   </si>
   <si>
@@ -535,15 +544,6 @@
   </si>
   <si>
     <t>https://www.infoq.cn/article/6521ea3ae8a36f2bdaece6e61</t>
-  </si>
-  <si>
-    <t>Midway Serverless 发布 2.0，一体化让前端研发再次提效</t>
-  </si>
-  <si>
-    <t>Taobao FED | 淘系前端团队</t>
-  </si>
-  <si>
-    <t>https://fed.taobao.org/blog/taofed/do71ct/mvd9lw</t>
   </si>
   <si>
     <t>构建效率大幅提升，webpack5 在企鹅辅导的升级实践</t>
@@ -2136,7 +2136,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -2219,6 +2219,20 @@
         <v>161</v>
       </c>
     </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E6" t="s">
+        <v>164</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
@@ -2227,7 +2241,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -2256,7 +2270,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -2265,12 +2279,12 @@
         <v>154</v>
       </c>
       <c r="E2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
@@ -2279,90 +2293,76 @@
         <v>154</v>
       </c>
       <c r="E3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B4" t="s">
-        <v>167</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
         <v>154</v>
       </c>
       <c r="E4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
         <v>154</v>
       </c>
       <c r="E5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
         <v>154</v>
       </c>
       <c r="E6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
         <v>154</v>
       </c>
       <c r="E7" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>178</v>
       </c>
       <c r="C8" t="s">
         <v>154</v>
       </c>
       <c r="E8" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>177</v>
-      </c>
-      <c r="B9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C9" t="s">
-        <v>154</v>
-      </c>
-      <c r="E9" t="s">
         <v>179</v>
       </c>
     </row>

--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="20" activeTab="23"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="22" activeTab="25"/>
   </bookViews>
   <sheets>
     <sheet sheetId="2" name="2021-02-24-chinese" state="visible" r:id="rId4"/>
@@ -31,13 +31,15 @@
     <sheet sheetId="22" name="2021-03-08-chinese" state="visible" r:id="rId25"/>
     <sheet sheetId="23" name="2021-03-09-english" state="visible" r:id="rId26"/>
     <sheet sheetId="24" name="2021-03-09-chinese" state="visible" r:id="rId27"/>
+    <sheet sheetId="25" name="2021-03-10-english" state="visible" r:id="rId28"/>
+    <sheet sheetId="26" name="2021-03-10-chinese" state="visible" r:id="rId29"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="199">
   <si>
     <t>标题</t>
   </si>
@@ -577,6 +579,63 @@
   </si>
   <si>
     <t>https://juejin.cn/post/6937473044185088014</t>
+  </si>
+  <si>
+    <t>Dragging, dropping, counting, and uploading.</t>
+  </si>
+  <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
+    <t>https://react.statuscode.com/issues/229</t>
+  </si>
+  <si>
+    <t>The WordPress Evolution Toward Full-Site Editing</t>
+  </si>
+  <si>
+    <t>https://css-tricks.com/the-wordpress-evolution-toward-full-site-editing/</t>
+  </si>
+  <si>
+    <t>Too Many SVGs Clogging Up Your Markup? Try `use`.</t>
+  </si>
+  <si>
+    <t>https://css-tricks.com/too-many-svgs-clogging-up-your-markup-try-use/</t>
+  </si>
+  <si>
+    <t>The best font loading strategies</t>
+  </si>
+  <si>
+    <t>Frontend Focus</t>
+  </si>
+  <si>
+    <t>https://frontendfoc.us/issues/481</t>
+  </si>
+  <si>
+    <t>前端DEF部署和BUC接入的“跨域”坑</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/JXvT08i9A6WeLXH3theP</t>
+  </si>
+  <si>
+    <t>一个PHPer的Golang之路</t>
+  </si>
+  <si>
+    <t>https://www.infoq.cn/article/e7aa922ae5c5f13298513ea8d</t>
+  </si>
+  <si>
+    <t>那些与 IE 相伴的日子</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6937815094273245192</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6937939204525522951</t>
+  </si>
+  <si>
+    <t>Flutter2.0重磅发布！带你一文打尽Flutter Engage</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/post/6937486408151990309</t>
   </si>
 </sst>
 </file>
@@ -2368,6 +2427,216 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>181</v>
+      </c>
+      <c r="E4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" t="s">
+        <v>181</v>
+      </c>
+      <c r="E4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" t="s">
+        <v>181</v>
+      </c>
+      <c r="E6" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>197</v>
+      </c>
+      <c r="B7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
+        <v>181</v>
+      </c>
+      <c r="E7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>

--- a/articlelist.xlsx
+++ b/articlelist.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="22" activeTab="25"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12000" windowHeight="24000" firstSheet="23" activeTab="26"/>
   </bookViews>
   <sheets>
     <sheet sheetId="2" name="2021-02-24-chinese" state="visible" r:id="rId4"/>
@@ -33,13 +33,14 @@
     <sheet sheetId="24" name="2021-03-09-chinese" state="visible" r:id="rId27"/>
     <sheet sheetId="25" name="2021-03-10-english" state="visible" r:id="rId28"/>
     <sheet sheetId="26" name="2021-03-10-chinese" state="visible" r:id="rId29"/>
+    <sheet sheetId="27" name="2021-03-11-english" state="visible" r:id="rId30"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="206">
   <si>
     <t>标题</t>
   </si>
@@ -636,6 +637,27 @@
   </si>
   <si>
     <t>https://juejin.cn/post/6937486408151990309</t>
+  </si>
+  <si>
+    <t>Table of Contents with IntersectionObserver</t>
+  </si>
+  <si>
+    <t>2021-03-11</t>
+  </si>
+  <si>
+    <t>https://benfrain.com/building-a-table-of-contents-with-active-indicator-using-javascript-intersection-observers/</t>
+  </si>
+  <si>
+    <t>Chapter 7: Standards</t>
+  </si>
+  <si>
+    <t>https://css-tricks.com/chapter-7-standards/</t>
+  </si>
+  <si>
+    <t>How I Built my SaaS MVP With Fauna ($150 in revenue so far)</t>
+  </si>
+  <si>
+    <t>https://css-tricks.com/how-i-built-my-saas-mvp-with-fauna-150-in-revenue-so-far/</t>
   </si>
 </sst>
 </file>
@@ -2637,6 +2659,83 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>200</v>
+      </c>
+      <c r="E4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
